--- a/excel/Synthetic_Prediction_SM_out.xlsx
+++ b/excel/Synthetic_Prediction_SM_out.xlsx
@@ -433,7 +433,7 @@
         <v>178.3759813928096</v>
       </c>
       <c r="B2" t="n">
-        <v>22619.30859375</v>
+        <v>21837.978515625</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>221.3023189067494</v>
       </c>
       <c r="B3" t="n">
-        <v>4568.4921875</v>
+        <v>3518.885009765625</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>258.1126556465619</v>
       </c>
       <c r="B4" t="n">
-        <v>505.7735595703125</v>
+        <v>525.0599365234375</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +457,7 @@
         <v>194.0869090610645</v>
       </c>
       <c r="B5" t="n">
-        <v>12979.5830078125</v>
+        <v>12842.927734375</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>144.3631367800776</v>
       </c>
       <c r="B6" t="n">
-        <v>73959.140625</v>
+        <v>77693.921875</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>264.5132289875165</v>
       </c>
       <c r="B7" t="n">
-        <v>335.2922668457031</v>
+        <v>380.1519775390625</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>80.71882531626942</v>
       </c>
       <c r="B8" t="n">
-        <v>1997139.375</v>
+        <v>2294233.75</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>65.12259701908624</v>
       </c>
       <c r="B9" t="n">
-        <v>7057222</v>
+        <v>7211879</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>93.22486140097212</v>
       </c>
       <c r="B10" t="n">
-        <v>764473.25</v>
+        <v>1061071</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +505,7 @@
         <v>192.4151132936647</v>
       </c>
       <c r="B11" t="n">
-        <v>13692.8896484375</v>
+        <v>13450.2041015625</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +513,7 @@
         <v>248.0949961094556</v>
       </c>
       <c r="B12" t="n">
-        <v>920.6117553710938</v>
+        <v>873.2229614257812</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +521,7 @@
         <v>100.33226356222</v>
       </c>
       <c r="B13" t="n">
-        <v>450030.1875</v>
+        <v>737715.5625</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>216.4069673406181</v>
       </c>
       <c r="B14" t="n">
-        <v>5860.94580078125</v>
+        <v>4515.2041015625</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +537,7 @@
         <v>273.7331093164331</v>
       </c>
       <c r="B15" t="n">
-        <v>190.1720428466797</v>
+        <v>240.4764404296875</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,7 @@
         <v>116.946256443293</v>
       </c>
       <c r="B16" t="n">
-        <v>221639.828125</v>
+        <v>315420.5</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +553,7 @@
         <v>230.6526960647008</v>
       </c>
       <c r="B17" t="n">
-        <v>2612.05419921875</v>
+        <v>2163.91357421875</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +561,7 @@
         <v>169.9825035632645</v>
       </c>
       <c r="B18" t="n">
-        <v>31071.486328125</v>
+        <v>29483.70703125</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +569,7 @@
         <v>186.6129625547485</v>
       </c>
       <c r="B19" t="n">
-        <v>17016.986328125</v>
+        <v>16265.7158203125</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +577,7 @@
         <v>255.961278275202</v>
       </c>
       <c r="B20" t="n">
-        <v>575.1995849609375</v>
+        <v>585.669677734375</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +585,7 @@
         <v>138.7295919967381</v>
       </c>
       <c r="B21" t="n">
-        <v>91271.8125</v>
+        <v>103533.0546875</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>71.84509106082361</v>
       </c>
       <c r="B22" t="n">
-        <v>3954487.75</v>
+        <v>3976379</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>261.4518871486907</v>
       </c>
       <c r="B23" t="n">
-        <v>404.8494873046875</v>
+        <v>443.1693725585938</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +609,7 @@
         <v>180.1593166218452</v>
       </c>
       <c r="B24" t="n">
-        <v>21267.681640625</v>
+        <v>20488.630859375</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +617,7 @@
         <v>147.0296347377218</v>
       </c>
       <c r="B25" t="n">
-        <v>67106.8671875</v>
+        <v>67829.5625</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +625,7 @@
         <v>244.9699768926004</v>
       </c>
       <c r="B26" t="n">
-        <v>1109.740234375</v>
+        <v>1026.677612304688</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +633,7 @@
         <v>95.29729475213338</v>
       </c>
       <c r="B27" t="n">
-        <v>652005</v>
+        <v>954366.875</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +641,7 @@
         <v>167.957444864798</v>
       </c>
       <c r="B28" t="n">
-        <v>32967.89453125</v>
+        <v>31584.814453125</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +649,7 @@
         <v>162.2359925549722</v>
       </c>
       <c r="B29" t="n">
-        <v>38974.859375</v>
+        <v>36200.40625</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +657,7 @@
         <v>235.2549076556998</v>
       </c>
       <c r="B30" t="n">
-        <v>1983.725341796875</v>
+        <v>1702.763916015625</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +665,7 @@
         <v>154.1564042350602</v>
       </c>
       <c r="B31" t="n">
-        <v>51730.59765625</v>
+        <v>47185.86328125</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +673,7 @@
         <v>202.8621980567098</v>
       </c>
       <c r="B32" t="n">
-        <v>9810.4345703125</v>
+        <v>8827.7568359375</v>
       </c>
     </row>
     <row r="33">
@@ -681,7 +681,7 @@
         <v>253.4306025365051</v>
       </c>
       <c r="B33" t="n">
-        <v>669.162353515625</v>
+        <v>665.9797973632812</v>
       </c>
     </row>
     <row r="34">
@@ -689,7 +689,7 @@
         <v>270.3961161622001</v>
       </c>
       <c r="B34" t="n">
-        <v>234.616455078125</v>
+        <v>283.6763610839844</v>
       </c>
     </row>
     <row r="35">
@@ -697,7 +697,7 @@
         <v>157.0705197189901</v>
       </c>
       <c r="B35" t="n">
-        <v>46508.71484375</v>
+        <v>42647.33203125</v>
       </c>
     </row>
     <row r="36">
@@ -705,7 +705,7 @@
         <v>136.8693662306018</v>
       </c>
       <c r="B36" t="n">
-        <v>98455.8046875</v>
+        <v>113866.1328125</v>
       </c>
     </row>
     <row r="37">
@@ -713,7 +713,7 @@
         <v>210.7553969252346</v>
       </c>
       <c r="B37" t="n">
-        <v>7296.23974609375</v>
+        <v>6021.12158203125</v>
       </c>
     </row>
     <row r="38">
@@ -721,7 +721,7 @@
         <v>126.5227601931633</v>
       </c>
       <c r="B38" t="n">
-        <v>150056.484375</v>
+        <v>193283.515625</v>
       </c>
     </row>
     <row r="39">
@@ -729,7 +729,7 @@
         <v>214.5601769114003</v>
       </c>
       <c r="B39" t="n">
-        <v>6321.2880859375</v>
+        <v>4960.48583984375</v>
       </c>
     </row>
     <row r="40">
@@ -737,7 +737,7 @@
         <v>152.948964814165</v>
       </c>
       <c r="B40" t="n">
-        <v>54062.46484375</v>
+        <v>50178.11328125</v>
       </c>
     </row>
     <row r="41">
@@ -745,7 +745,7 @@
         <v>251.8713975305205</v>
       </c>
       <c r="B41" t="n">
-        <v>734.5440063476562</v>
+        <v>720.8514404296875</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +753,7 @@
         <v>176.9036020032337</v>
       </c>
       <c r="B42" t="n">
-        <v>23961.5390625</v>
+        <v>23018.763671875</v>
       </c>
     </row>
     <row r="43">
@@ -761,7 +761,7 @@
         <v>120.5222957382816</v>
       </c>
       <c r="B43" t="n">
-        <v>191599.515625</v>
+        <v>262703.3125</v>
       </c>
     </row>
     <row r="44">
@@ -769,7 +769,7 @@
         <v>145.2376721897545</v>
       </c>
       <c r="B44" t="n">
-        <v>71640.53125</v>
+        <v>74310.125</v>
       </c>
     </row>
     <row r="45">
@@ -777,7 +777,7 @@
         <v>237.1240837293851</v>
       </c>
       <c r="B45" t="n">
-        <v>1773.973510742188</v>
+        <v>1544.8291015625</v>
       </c>
     </row>
     <row r="46">
@@ -785,7 +785,7 @@
         <v>224.869217127778</v>
       </c>
       <c r="B46" t="n">
-        <v>3691.092041015625</v>
+        <v>2924.433837890625</v>
       </c>
     </row>
     <row r="47">
@@ -793,7 +793,7 @@
         <v>73.96159051890152</v>
       </c>
       <c r="B47" t="n">
-        <v>3359363.75</v>
+        <v>3487535.25</v>
       </c>
     </row>
     <row r="48">
@@ -801,7 +801,7 @@
         <v>272.4793660950597</v>
       </c>
       <c r="B48" t="n">
-        <v>205.9614868164062</v>
+        <v>255.7420349121094</v>
       </c>
     </row>
     <row r="49">
@@ -809,7 +809,7 @@
         <v>61.78737984744161</v>
       </c>
       <c r="B49" t="n">
-        <v>9787024</v>
+        <v>10946701</v>
       </c>
     </row>
     <row r="50">
@@ -817,7 +817,7 @@
         <v>267.3841354629988</v>
       </c>
       <c r="B50" t="n">
-        <v>281.6760559082031</v>
+        <v>329.544677734375</v>
       </c>
     </row>
     <row r="51">
@@ -825,7 +825,7 @@
         <v>164.2431016679457</v>
       </c>
       <c r="B51" t="n">
-        <v>36752.15625</v>
+        <v>34532.0859375</v>
       </c>
     </row>
     <row r="52">
@@ -833,7 +833,7 @@
         <v>172.9900583022094</v>
       </c>
       <c r="B52" t="n">
-        <v>28143.431640625</v>
+        <v>26476.96875</v>
       </c>
     </row>
     <row r="53">
@@ -841,7 +841,7 @@
         <v>233.3609773224634</v>
       </c>
       <c r="B53" t="n">
-        <v>2221.56591796875</v>
+        <v>1879.265991210938</v>
       </c>
     </row>
     <row r="54">
@@ -849,7 +849,7 @@
         <v>111.7433650490871</v>
       </c>
       <c r="B54" t="n">
-        <v>273954.125</v>
+        <v>411573.6875</v>
       </c>
     </row>
     <row r="55">
@@ -857,7 +857,7 @@
         <v>200.8194838298815</v>
       </c>
       <c r="B55" t="n">
-        <v>10482.662109375</v>
+        <v>9638.421875</v>
       </c>
     </row>
     <row r="56">
@@ -865,7 +865,7 @@
         <v>249.5727854508638</v>
       </c>
       <c r="B56" t="n">
-        <v>842.7611083984375</v>
+        <v>810.0950317382812</v>
       </c>
     </row>
     <row r="57">
@@ -873,7 +873,7 @@
         <v>85.11558950817977</v>
       </c>
       <c r="B57" t="n">
-        <v>1424909</v>
+        <v>1746996.125</v>
       </c>
     </row>
     <row r="58">
@@ -881,7 +881,7 @@
         <v>187.9559209665435</v>
       </c>
       <c r="B58" t="n">
-        <v>16212.796875</v>
+        <v>15502.9189453125</v>
       </c>
     </row>
     <row r="59">
@@ -889,7 +889,7 @@
         <v>276.5171945304821</v>
       </c>
       <c r="B59" t="n">
-        <v>161.8928070068359</v>
+        <v>211.5491638183594</v>
       </c>
     </row>
     <row r="60">
@@ -897,7 +897,7 @@
         <v>97.63917784003934</v>
       </c>
       <c r="B60" t="n">
-        <v>544696.4375</v>
+        <v>846648.0625</v>
       </c>
     </row>
     <row r="61">
@@ -905,7 +905,7 @@
         <v>108.7959111341657</v>
       </c>
       <c r="B61" t="n">
-        <v>308897.09375</v>
+        <v>478532.15625</v>
       </c>
     </row>
     <row r="62">
@@ -913,7 +913,7 @@
         <v>140.8681552034475</v>
       </c>
       <c r="B62" t="n">
-        <v>83999.7109375</v>
+        <v>92827.90625</v>
       </c>
     </row>
     <row r="63">
@@ -921,7 +921,7 @@
         <v>196.809388857596</v>
       </c>
       <c r="B63" t="n">
-        <v>11903.927734375</v>
+        <v>11435.5009765625</v>
       </c>
     </row>
     <row r="64">
@@ -929,7 +929,7 @@
         <v>134.4368162760082</v>
       </c>
       <c r="B64" t="n">
-        <v>108709.921875</v>
+        <v>128950.234375</v>
       </c>
     </row>
     <row r="65">
@@ -937,7 +937,7 @@
         <v>198.3770149991821</v>
       </c>
       <c r="B65" t="n">
-        <v>11326.69921875</v>
+        <v>10696.203125</v>
       </c>
     </row>
     <row r="66">
@@ -945,7 +945,7 @@
         <v>89.88000690301288</v>
       </c>
       <c r="B66" t="n">
-        <v>988336.875</v>
+        <v>1300320.375</v>
       </c>
     </row>
     <row r="67">
@@ -953,7 +953,7 @@
         <v>263.2300906491657</v>
       </c>
       <c r="B67" t="n">
-        <v>362.4471130371094</v>
+        <v>404.9070739746094</v>
       </c>
     </row>
     <row r="68">
@@ -961,7 +961,7 @@
         <v>103.3684163042322</v>
       </c>
       <c r="B68" t="n">
-        <v>385315.84375</v>
+        <v>631619.5625</v>
       </c>
     </row>
     <row r="69">
@@ -969,7 +969,7 @@
         <v>128.3565220286635</v>
       </c>
       <c r="B69" t="n">
-        <v>139257.734375</v>
+        <v>175981.1875</v>
       </c>
     </row>
     <row r="70">
@@ -977,7 +977,7 @@
         <v>242.1894129779852</v>
       </c>
       <c r="B70" t="n">
-        <v>1310.453491210938</v>
+        <v>1186.643676757812</v>
       </c>
     </row>
     <row r="71">
@@ -985,7 +985,7 @@
         <v>132.502016714437</v>
       </c>
       <c r="B71" t="n">
-        <v>117623.0078125</v>
+        <v>142362.359375</v>
       </c>
     </row>
     <row r="72">
@@ -993,7 +993,7 @@
         <v>77.49199216679486</v>
       </c>
       <c r="B72" t="n">
-        <v>2559190</v>
+        <v>2802164</v>
       </c>
     </row>
     <row r="73">
@@ -1001,7 +1001,7 @@
         <v>159.2061293235292</v>
       </c>
       <c r="B73" t="n">
-        <v>43019.7109375</v>
+        <v>39847.1796875</v>
       </c>
     </row>
     <row r="74">
@@ -1009,7 +1009,7 @@
         <v>98.27500886845283</v>
       </c>
       <c r="B74" t="n">
-        <v>518741.5625</v>
+        <v>819560.25</v>
       </c>
     </row>
     <row r="75">
@@ -1017,7 +1017,7 @@
         <v>115.1911895140945</v>
       </c>
       <c r="B75" t="n">
-        <v>238062.953125</v>
+        <v>345040.375</v>
       </c>
     </row>
     <row r="76">
@@ -1025,7 +1025,7 @@
         <v>84.49934047985072</v>
       </c>
       <c r="B76" t="n">
-        <v>1493952.875</v>
+        <v>1815014.625</v>
       </c>
     </row>
     <row r="77">
@@ -1033,7 +1033,7 @@
         <v>123.9663668832649</v>
       </c>
       <c r="B77" t="n">
-        <v>166522.609375</v>
+        <v>220278.578125</v>
       </c>
     </row>
     <row r="78">
@@ -1041,7 +1041,7 @@
         <v>223.8449969245538</v>
       </c>
       <c r="B78" t="n">
-        <v>3924.189697265625</v>
+        <v>3084.6513671875</v>
       </c>
     </row>
     <row r="79">
@@ -1049,7 +1049,7 @@
         <v>227.4675284429507</v>
       </c>
       <c r="B79" t="n">
-        <v>3160.00439453125</v>
+        <v>2554.327880859375</v>
       </c>
     </row>
     <row r="80">
@@ -1057,7 +1057,7 @@
         <v>205.4991101002029</v>
       </c>
       <c r="B80" t="n">
-        <v>8893.3857421875</v>
+        <v>7869.2509765625</v>
       </c>
     </row>
     <row r="81">
@@ -1065,7 +1065,7 @@
         <v>78.4481710287621</v>
       </c>
       <c r="B81" t="n">
-        <v>2377549.75</v>
+        <v>2640920.5</v>
       </c>
     </row>
     <row r="82">
@@ -1073,7 +1073,7 @@
         <v>105.3551942404968</v>
       </c>
       <c r="B82" t="n">
-        <v>355364.8125</v>
+        <v>570595.8125</v>
       </c>
     </row>
     <row r="83">
@@ -1081,7 +1081,7 @@
         <v>190.2926693532782</v>
       </c>
       <c r="B83" t="n">
-        <v>14807.15625</v>
+        <v>14259.9990234375</v>
       </c>
     </row>
     <row r="84">
@@ -1089,7 +1089,7 @@
         <v>109.4630809584424</v>
       </c>
       <c r="B84" t="n">
-        <v>300616.3125</v>
+        <v>462478.96875</v>
       </c>
     </row>
     <row r="85">
@@ -1097,7 +1097,7 @@
         <v>150.8619038287576</v>
       </c>
       <c r="B85" t="n">
-        <v>58343.6484375</v>
+        <v>55804.5078125</v>
       </c>
     </row>
     <row r="86">
@@ -1105,7 +1105,7 @@
         <v>239.9872813018535</v>
       </c>
       <c r="B86" t="n">
-        <v>1494.866821289062</v>
+        <v>1330.836669921875</v>
       </c>
     </row>
     <row r="87">
@@ -1113,7 +1113,7 @@
         <v>68.88796976797583</v>
       </c>
       <c r="B87" t="n">
-        <v>4966584</v>
+        <v>4804479.5</v>
       </c>
     </row>
     <row r="88">
@@ -1121,7 +1121,7 @@
         <v>165.1697676408587</v>
       </c>
       <c r="B88" t="n">
-        <v>35769.23828125</v>
+        <v>33788.0625</v>
       </c>
     </row>
     <row r="89">
@@ -1129,7 +1129,7 @@
         <v>207.930493659495</v>
       </c>
       <c r="B89" t="n">
-        <v>8116.12939453125</v>
+        <v>6952.76220703125</v>
       </c>
     </row>
     <row r="90">
@@ -1137,7 +1137,7 @@
         <v>279.6419560883936</v>
       </c>
       <c r="B90" t="n">
-        <v>135.0196075439453</v>
+        <v>183.3269348144531</v>
       </c>
     </row>
     <row r="91">
@@ -1145,7 +1145,7 @@
         <v>243.3655767160617</v>
       </c>
       <c r="B91" t="n">
-        <v>1221.46533203125</v>
+        <v>1116.142700195312</v>
       </c>
     </row>
     <row r="92">
@@ -1153,7 +1153,7 @@
         <v>219.7184052121837</v>
       </c>
       <c r="B92" t="n">
-        <v>5003.3974609375</v>
+        <v>3814.493408203125</v>
       </c>
     </row>
     <row r="93">
@@ -1161,7 +1161,7 @@
         <v>69.76209498647961</v>
       </c>
       <c r="B93" t="n">
-        <v>4643050</v>
+        <v>4536726</v>
       </c>
     </row>
     <row r="94">
@@ -1169,7 +1169,7 @@
         <v>88.07851118330052</v>
       </c>
       <c r="B94" t="n">
-        <v>1134959.25</v>
+        <v>1453923</v>
       </c>
     </row>
     <row r="95">
@@ -1177,7 +1177,7 @@
         <v>174.8080917978595</v>
       </c>
       <c r="B95" t="n">
-        <v>26116.986328125</v>
+        <v>24810.181640625</v>
       </c>
     </row>
     <row r="96">
@@ -1185,7 +1185,7 @@
         <v>130.5820622193004</v>
       </c>
       <c r="B96" t="n">
-        <v>127190.03125</v>
+        <v>157049.765625</v>
       </c>
     </row>
     <row r="97">
@@ -1193,7 +1193,7 @@
         <v>63.24832478224545</v>
       </c>
       <c r="B97" t="n">
-        <v>8480910</v>
+        <v>9117917</v>
       </c>
     </row>
     <row r="98">
@@ -1201,7 +1201,7 @@
         <v>119.3475498734636</v>
       </c>
       <c r="B98" t="n">
-        <v>200989.140625</v>
+        <v>278969.125</v>
       </c>
     </row>
     <row r="99">
@@ -1209,7 +1209,7 @@
         <v>213.2015810037535</v>
       </c>
       <c r="B99" t="n">
-        <v>6653.4833984375</v>
+        <v>5315.85986328125</v>
       </c>
     </row>
     <row r="100">
@@ -1217,7 +1217,7 @@
         <v>184.2725293515399</v>
       </c>
       <c r="B100" t="n">
-        <v>18450.2265625</v>
+        <v>17685.845703125</v>
       </c>
     </row>
     <row r="101">
@@ -1225,7 +1225,7 @@
         <v>58.07184204274785</v>
       </c>
       <c r="B101" t="n">
-        <v>14088407</v>
+        <v>17425498</v>
       </c>
     </row>
     <row r="102">
@@ -1233,7 +1233,7 @@
         <v>203.2807584375469</v>
       </c>
       <c r="B102" t="n">
-        <v>58840.8046875</v>
+        <v>42064.35546875</v>
       </c>
     </row>
     <row r="103">
@@ -1241,7 +1241,7 @@
         <v>257.9352223143529</v>
       </c>
       <c r="B103" t="n">
-        <v>9483.2421875</v>
+        <v>8880.7880859375</v>
       </c>
     </row>
     <row r="104">
@@ -1249,7 +1249,7 @@
         <v>304.8027012597865</v>
       </c>
       <c r="B104" t="n">
-        <v>870.189453125</v>
+        <v>1330.798706054688</v>
       </c>
     </row>
     <row r="105">
@@ -1257,7 +1257,7 @@
         <v>223.2841497922579</v>
       </c>
       <c r="B105" t="n">
-        <v>41587.72265625</v>
+        <v>27219.984375</v>
       </c>
     </row>
     <row r="106">
@@ -1265,7 +1265,7 @@
         <v>159.975088890726</v>
       </c>
       <c r="B106" t="n">
-        <v>113700.4765625</v>
+        <v>112231.5859375</v>
       </c>
     </row>
     <row r="107">
@@ -1273,7 +1273,7 @@
         <v>312.9520082986284</v>
       </c>
       <c r="B107" t="n">
-        <v>708.1781005859375</v>
+        <v>1081.51806640625</v>
       </c>
     </row>
     <row r="108">
@@ -1281,7 +1281,7 @@
         <v>78.94218640438388</v>
       </c>
       <c r="B108" t="n">
-        <v>1236115.75</v>
+        <v>1116838.375</v>
       </c>
     </row>
     <row r="109">
@@ -1289,7 +1289,7 @@
         <v>59.08483202827364</v>
       </c>
       <c r="B109" t="n">
-        <v>9486054</v>
+        <v>11047328</v>
       </c>
     </row>
     <row r="110">
@@ -1297,7 +1297,7 @@
         <v>94.86506119451603</v>
       </c>
       <c r="B110" t="n">
-        <v>480650.03125</v>
+        <v>526178.0625</v>
       </c>
     </row>
     <row r="111">
@@ -1305,7 +1305,7 @@
         <v>221.1555940693506</v>
       </c>
       <c r="B111" t="n">
-        <v>43152.16796875</v>
+        <v>28510.302734375</v>
       </c>
     </row>
     <row r="112">
@@ -1313,7 +1313,7 @@
         <v>292.0480652249017</v>
       </c>
       <c r="B112" t="n">
-        <v>1521.227783203125</v>
+        <v>1989.006469726562</v>
       </c>
     </row>
     <row r="113">
@@ -1321,7 +1321,7 @@
         <v>103.9143134060216</v>
       </c>
       <c r="B113" t="n">
-        <v>387197.96875</v>
+        <v>428346.6875</v>
       </c>
     </row>
     <row r="114">
@@ -1329,7 +1329,7 @@
         <v>251.702386465068</v>
       </c>
       <c r="B114" t="n">
-        <v>13196.08984375</v>
+        <v>11450.4013671875</v>
       </c>
     </row>
     <row r="115">
@@ -1337,7 +1337,7 @@
         <v>324.6908997477673</v>
       </c>
       <c r="B115" t="n">
-        <v>626.1110229492188</v>
+        <v>802.1906127929688</v>
       </c>
     </row>
     <row r="116">
@@ -1345,7 +1345,7 @@
         <v>125.0675010841748</v>
       </c>
       <c r="B116" t="n">
-        <v>233463.453125</v>
+        <v>264827.53125</v>
       </c>
     </row>
     <row r="117">
@@ -1353,7 +1353,7 @@
         <v>269.840264305131</v>
       </c>
       <c r="B117" t="n">
-        <v>4979.6396484375</v>
+        <v>5128.08203125</v>
       </c>
     </row>
     <row r="118">
@@ -1361,7 +1361,7 @@
         <v>192.5940551825423</v>
       </c>
       <c r="B118" t="n">
-        <v>70639.8203125</v>
+        <v>53003.515625</v>
       </c>
     </row>
     <row r="119">
@@ -1369,7 +1369,7 @@
         <v>213.7682077621703</v>
       </c>
       <c r="B119" t="n">
-        <v>49052.6953125</v>
+        <v>33481.953125</v>
       </c>
     </row>
     <row r="120">
@@ -1377,7 +1377,7 @@
         <v>302.0635349661286</v>
       </c>
       <c r="B120" t="n">
-        <v>964.755859375</v>
+        <v>1427.855712890625</v>
       </c>
     </row>
     <row r="121">
@@ -1385,7 +1385,7 @@
         <v>152.8023742430017</v>
       </c>
       <c r="B121" t="n">
-        <v>126099.328125</v>
+        <v>133394.3125</v>
       </c>
     </row>
     <row r="122">
@@ -1393,7 +1393,7 @@
         <v>67.64401338510068</v>
       </c>
       <c r="B122" t="n">
-        <v>3948565.75</v>
+        <v>4099820.5</v>
       </c>
     </row>
     <row r="123">
@@ -1401,7 +1401,7 @@
         <v>309.0542614458873</v>
       </c>
       <c r="B123" t="n">
-        <v>752.4104614257812</v>
+        <v>1194.310424804688</v>
       </c>
     </row>
     <row r="124">
@@ -1409,7 +1409,7 @@
         <v>205.5513278944429</v>
       </c>
       <c r="B124" t="n">
-        <v>56568.09765625</v>
+        <v>40036.67578125</v>
       </c>
     </row>
     <row r="125">
@@ -1417,7 +1417,7 @@
         <v>163.3701145263585</v>
       </c>
       <c r="B125" t="n">
-        <v>108264.671875</v>
+        <v>104035.0078125</v>
       </c>
     </row>
     <row r="126">
@@ -1425,7 +1425,7 @@
         <v>288.0692433688216</v>
       </c>
       <c r="B126" t="n">
-        <v>1933.369995117188</v>
+        <v>2383.460693359375</v>
       </c>
     </row>
     <row r="127">
@@ -1433,7 +1433,7 @@
         <v>97.50371476451485</v>
       </c>
       <c r="B127" t="n">
-        <v>451284</v>
+        <v>495545.0625</v>
       </c>
     </row>
     <row r="128">
@@ -1441,7 +1441,7 @@
         <v>190.0157197387648</v>
       </c>
       <c r="B128" t="n">
-        <v>73367.3515625</v>
+        <v>55974.85546875</v>
       </c>
     </row>
     <row r="129">
@@ -1449,7 +1449,7 @@
         <v>182.7310798952492</v>
       </c>
       <c r="B129" t="n">
-        <v>81655.8515625</v>
+        <v>65468.71875</v>
       </c>
     </row>
     <row r="130">
@@ -1457,7 +1457,7 @@
         <v>275.6998698927727</v>
       </c>
       <c r="B130" t="n">
-        <v>3622.32275390625</v>
+        <v>4031.1962890625</v>
       </c>
     </row>
     <row r="131">
@@ -1465,7 +1465,7 @@
         <v>172.4440255238696</v>
       </c>
       <c r="B131" t="n">
-        <v>94976.0078125</v>
+        <v>84196.4765625</v>
       </c>
     </row>
     <row r="132">
@@ -1473,7 +1473,7 @@
         <v>234.4569808138954</v>
       </c>
       <c r="B132" t="n">
-        <v>30537.28125</v>
+        <v>21345.537109375</v>
       </c>
     </row>
     <row r="133">
@@ -1481,7 +1481,7 @@
         <v>298.8414402393282</v>
       </c>
       <c r="B133" t="n">
-        <v>1089.362182617188</v>
+        <v>1553.178833007812</v>
       </c>
     </row>
     <row r="134">
@@ -1489,7 +1489,7 @@
         <v>320.4421894601509</v>
       </c>
       <c r="B134" t="n">
-        <v>652.9191284179688</v>
+        <v>893.8009033203125</v>
       </c>
     </row>
     <row r="135">
@@ -1497,7 +1497,7 @@
         <v>176.1543215489513</v>
       </c>
       <c r="B135" t="n">
-        <v>89940.375</v>
+        <v>76892.9765625</v>
       </c>
     </row>
     <row r="136">
@@ -1505,7 +1505,7 @@
         <v>150.4339065882667</v>
       </c>
       <c r="B136" t="n">
-        <v>131094.140625</v>
+        <v>142920.6875</v>
       </c>
     </row>
     <row r="137">
@@ -1513,7 +1513,7 @@
         <v>244.5067213092765</v>
       </c>
       <c r="B137" t="n">
-        <v>19016.787109375</v>
+        <v>14952.640625</v>
       </c>
     </row>
     <row r="138">
@@ -1521,7 +1521,7 @@
         <v>137.2604508808682</v>
       </c>
       <c r="B138" t="n">
-        <v>174326.734375</v>
+        <v>197741.6875</v>
       </c>
     </row>
     <row r="139">
@@ -1529,7 +1529,7 @@
         <v>249.3510248850372</v>
       </c>
       <c r="B139" t="n">
-        <v>14936.0361328125</v>
+        <v>12484.404296875</v>
       </c>
     </row>
     <row r="140">
@@ -1537,7 +1537,7 @@
         <v>170.9066953430379</v>
       </c>
       <c r="B140" t="n">
-        <v>97143.9609375</v>
+        <v>87422.3046875</v>
       </c>
     </row>
     <row r="141">
@@ -1545,7 +1545,7 @@
         <v>296.856236781231</v>
       </c>
       <c r="B141" t="n">
-        <v>1178.03564453125</v>
+        <v>1637.269409179688</v>
       </c>
     </row>
     <row r="142">
@@ -1553,7 +1553,7 @@
         <v>201.4061026709236</v>
       </c>
       <c r="B142" t="n">
-        <v>60785.984375</v>
+        <v>43815.64453125</v>
       </c>
     </row>
     <row r="143">
@@ -1561,7 +1561,7 @@
         <v>129.6205685432033</v>
       </c>
       <c r="B143" t="n">
-        <v>209357.953125</v>
+        <v>238712.328125</v>
       </c>
     </row>
     <row r="144">
@@ -1569,7 +1569,7 @@
         <v>161.0885606361703</v>
       </c>
       <c r="B144" t="n">
-        <v>111888.3125</v>
+        <v>109480.359375</v>
       </c>
     </row>
     <row r="145">
@@ -1577,7 +1577,7 @@
         <v>278.0797332148054</v>
       </c>
       <c r="B145" t="n">
-        <v>3262.734619140625</v>
+        <v>3655.80908203125</v>
       </c>
     </row>
     <row r="146">
@@ -1585,7 +1585,7 @@
         <v>262.4766512193962</v>
       </c>
       <c r="B146" t="n">
-        <v>7417.15478515625</v>
+        <v>7340.58251953125</v>
       </c>
     </row>
     <row r="147">
@@ -1593,7 +1593,7 @@
         <v>70.33877259066379</v>
       </c>
       <c r="B147" t="n">
-        <v>2993216.5</v>
+        <v>2825756.25</v>
       </c>
     </row>
     <row r="148">
@@ -1601,7 +1601,7 @@
         <v>323.0946148659954</v>
       </c>
       <c r="B148" t="n">
-        <v>636.0504760742188</v>
+        <v>835.453369140625</v>
       </c>
     </row>
     <row r="149">
@@ -1609,7 +1609,7 @@
         <v>54.83838294862038</v>
       </c>
       <c r="B149" t="n">
-        <v>14502878</v>
+        <v>17953592</v>
       </c>
     </row>
     <row r="150">
@@ -1617,7 +1617,7 @@
         <v>316.607289958914</v>
       </c>
       <c r="B150" t="n">
-        <v>678.0989990234375</v>
+        <v>985.43994140625</v>
       </c>
     </row>
     <row r="151">
@@ -1625,7 +1625,7 @@
         <v>185.2865616545816</v>
       </c>
       <c r="B151" t="n">
-        <v>78646.6875</v>
+        <v>61864.35546875</v>
       </c>
     </row>
     <row r="152">
@@ -1633,7 +1633,7 @@
         <v>196.4233194840636</v>
       </c>
       <c r="B152" t="n">
-        <v>66323.390625</v>
+        <v>48833.23046875</v>
       </c>
     </row>
     <row r="153">
@@ -1641,7 +1641,7 @@
         <v>273.2884890720949</v>
       </c>
       <c r="B153" t="n">
-        <v>4132.09130859375</v>
+        <v>4450.88671875</v>
       </c>
     </row>
     <row r="154">
@@ -1649,7 +1649,7 @@
         <v>118.4431008621147</v>
       </c>
       <c r="B154" t="n">
-        <v>273559.78125</v>
+        <v>307866.0625</v>
       </c>
     </row>
     <row r="155">
@@ -1657,7 +1657,7 @@
         <v>231.8561660836713</v>
       </c>
       <c r="B155" t="n">
-        <v>34017.359375</v>
+        <v>22588.3359375</v>
       </c>
     </row>
     <row r="156">
@@ -1665,7 +1665,7 @@
         <v>293.9296090242369</v>
       </c>
       <c r="B156" t="n">
-        <v>1358.178955078125</v>
+        <v>1825.9140625</v>
       </c>
     </row>
     <row r="157">
@@ -1673,7 +1673,7 @@
         <v>84.5402132480102</v>
       </c>
       <c r="B157" t="n">
-        <v>758238.875</v>
+        <v>742750.4375</v>
       </c>
     </row>
     <row r="158">
@@ -1681,7 +1681,7 @@
         <v>215.4780827772858</v>
       </c>
       <c r="B158" t="n">
-        <v>47618.8828125</v>
+        <v>32259.16796875</v>
       </c>
     </row>
     <row r="159">
@@ -1689,7 +1689,7 @@
         <v>328.2356392614</v>
       </c>
       <c r="B159" t="n">
-        <v>592.34326171875</v>
+        <v>732.9866943359375</v>
       </c>
     </row>
     <row r="160">
@@ -1697,7 +1697,7 @@
         <v>100.4854358253926</v>
       </c>
       <c r="B160" t="n">
-        <v>420253.9375</v>
+        <v>463068.875</v>
       </c>
     </row>
     <row r="161">
@@ -1705,7 +1705,7 @@
         <v>114.6903578411359</v>
       </c>
       <c r="B161" t="n">
-        <v>299257.875</v>
+        <v>335281.59375</v>
       </c>
     </row>
     <row r="162">
@@ -1713,7 +1713,7 @@
         <v>155.5252253479069</v>
       </c>
       <c r="B162" t="n">
-        <v>121240.6328125</v>
+        <v>124228.6015625</v>
       </c>
     </row>
     <row r="163">
@@ -1721,7 +1721,7 @@
         <v>226.7504523540952</v>
       </c>
       <c r="B163" t="n">
-        <v>39160.5078125</v>
+        <v>25242.453125</v>
       </c>
     </row>
     <row r="164">
@@ -1729,7 +1729,7 @@
         <v>147.3367470978096</v>
       </c>
       <c r="B164" t="n">
-        <v>139861.15625</v>
+        <v>154256.125</v>
       </c>
     </row>
     <row r="165">
@@ -1737,7 +1737,7 @@
         <v>228.7463777297421</v>
       </c>
       <c r="B165" t="n">
-        <v>37827.73046875</v>
+        <v>24169.64453125</v>
       </c>
     </row>
     <row r="166">
@@ -1745,7 +1745,7 @@
         <v>90.60634172485433</v>
       </c>
       <c r="B166" t="n">
-        <v>532127.9375</v>
+        <v>579662.875</v>
       </c>
     </row>
     <row r="167">
@@ -1753,7 +1753,7 @@
         <v>311.31829710816</v>
       </c>
       <c r="B167" t="n">
-        <v>726.392333984375</v>
+        <v>1127.435791015625</v>
       </c>
     </row>
     <row r="168">
@@ -1761,7 +1761,7 @@
         <v>107.7799891187209</v>
       </c>
       <c r="B168" t="n">
-        <v>353039.59375</v>
+        <v>392312.125</v>
       </c>
     </row>
     <row r="169">
@@ -1769,7 +1769,7 @@
         <v>139.5952242578064</v>
       </c>
       <c r="B169" t="n">
-        <v>164839.59375</v>
+        <v>186683.625</v>
       </c>
     </row>
     <row r="170">
@@ -1777,7 +1777,7 @@
         <v>284.5289872270268</v>
       </c>
       <c r="B170" t="n">
-        <v>2393.08544921875</v>
+        <v>2799.75146484375</v>
       </c>
     </row>
     <row r="171">
@@ -1785,7 +1785,7 @@
         <v>144.8733309558569</v>
       </c>
       <c r="B171" t="n">
-        <v>147251.046875</v>
+        <v>163912.109375</v>
       </c>
     </row>
     <row r="172">
@@ -1793,7 +1793,7 @@
         <v>74.83373350534104</v>
       </c>
       <c r="B172" t="n">
-        <v>1885694</v>
+        <v>1715038.625</v>
       </c>
     </row>
     <row r="173">
@@ -1801,7 +1801,7 @@
         <v>178.8734120827836</v>
       </c>
       <c r="B173" t="n">
-        <v>86417.9609375</v>
+        <v>71946.0625</v>
       </c>
     </row>
     <row r="174">
@@ -1809,7 +1809,7 @@
         <v>101.2949855327929</v>
       </c>
       <c r="B174" t="n">
-        <v>412203.1875</v>
+        <v>454626.03125</v>
       </c>
     </row>
     <row r="175">
@@ -1817,7 +1817,7 @@
         <v>122.8329232553045</v>
       </c>
       <c r="B175" t="n">
-        <v>246285.296875</v>
+        <v>278627.21875</v>
       </c>
     </row>
     <row r="176">
@@ -1825,7 +1825,7 @@
         <v>83.75559564006753</v>
       </c>
       <c r="B176" t="n">
-        <v>805450.3125</v>
+        <v>774167.5625</v>
       </c>
     </row>
     <row r="177">
@@ -1833,7 +1833,7 @@
         <v>134.0056121524214</v>
       </c>
       <c r="B177" t="n">
-        <v>188471.078125</v>
+        <v>214258.640625</v>
       </c>
     </row>
     <row r="178">
@@ -1841,7 +1841,7 @@
         <v>261.1725985249209</v>
       </c>
       <c r="B178" t="n">
-        <v>7959.40869140625</v>
+        <v>7762.33251953125</v>
       </c>
     </row>
     <row r="179">
@@ -1849,7 +1849,7 @@
         <v>265.7848605878215</v>
       </c>
       <c r="B179" t="n">
-        <v>6201.505859375</v>
+        <v>6166.853515625</v>
       </c>
     </row>
     <row r="180">
@@ -1857,7 +1857,7 @@
         <v>237.8143372149769</v>
       </c>
       <c r="B180" t="n">
-        <v>26146.509765625</v>
+        <v>19236.06640625</v>
       </c>
     </row>
     <row r="181">
@@ -1865,7 +1865,7 @@
         <v>76.05115493231891</v>
       </c>
       <c r="B181" t="n">
-        <v>1663879.125</v>
+        <v>1508489</v>
       </c>
     </row>
     <row r="182">
@@ -1873,7 +1873,7 @@
         <v>110.3095849155566</v>
       </c>
       <c r="B182" t="n">
-        <v>332327.21875</v>
+        <v>370389.625</v>
       </c>
     </row>
     <row r="183">
@@ -1881,7 +1881,7 @@
         <v>218.4532662587674</v>
       </c>
       <c r="B183" t="n">
-        <v>45223.3359375</v>
+        <v>30236.91015625</v>
       </c>
     </row>
     <row r="184">
@@ -1889,7 +1889,7 @@
         <v>115.5398085786645</v>
       </c>
       <c r="B184" t="n">
-        <v>293237.71875</v>
+        <v>328869.84375</v>
       </c>
     </row>
     <row r="185">
@@ -1897,7 +1897,7 @@
         <v>168.2494176472969</v>
       </c>
       <c r="B185" t="n">
-        <v>100938.078125</v>
+        <v>93280</v>
       </c>
     </row>
     <row r="186">
@@ -1905,7 +1905,7 @@
         <v>281.7251997828726</v>
       </c>
       <c r="B186" t="n">
-        <v>2838.259033203125</v>
+        <v>3147.4365234375</v>
       </c>
     </row>
     <row r="187">
@@ -1913,7 +1913,7 @@
         <v>63.87896171194549</v>
       </c>
       <c r="B187" t="n">
-        <v>5814610.5</v>
+        <v>6385036.5</v>
       </c>
     </row>
     <row r="188">
@@ -1921,7 +1921,7 @@
         <v>186.466406823669</v>
       </c>
       <c r="B188" t="n">
-        <v>77294.875</v>
+        <v>60339.33984375</v>
       </c>
     </row>
     <row r="189">
@@ -1929,7 +1929,7 @@
         <v>240.9100116332484</v>
       </c>
       <c r="B189" t="n">
-        <v>22565.8515625</v>
+        <v>17120.33984375</v>
       </c>
     </row>
     <row r="190">
@@ -1937,7 +1937,7 @@
         <v>332.2141330622057</v>
       </c>
       <c r="B190" t="n">
-        <v>546.9797973632812</v>
+        <v>662.3988037109375</v>
       </c>
     </row>
     <row r="191">
@@ -1945,7 +1945,7 @@
         <v>286.0264967342154</v>
       </c>
       <c r="B191" t="n">
-        <v>2186.60498046875</v>
+        <v>2615.454833984375</v>
       </c>
     </row>
     <row r="192">
@@ -1953,7 +1953,7 @@
         <v>255.9185593792607</v>
       </c>
       <c r="B192" t="n">
-        <v>10568.0283203125</v>
+        <v>9657.552734375</v>
       </c>
     </row>
     <row r="193">
@@ -1961,7 +1961,7 @@
         <v>64.99191119576777</v>
       </c>
       <c r="B193" t="n">
-        <v>5186031.5</v>
+        <v>5621999.5</v>
       </c>
     </row>
     <row r="194">
@@ -1969,7 +1969,7 @@
         <v>88.31265005583489</v>
       </c>
       <c r="B194" t="n">
-        <v>590554.25</v>
+        <v>625382.0625</v>
       </c>
     </row>
     <row r="195">
@@ -1977,7 +1977,7 @@
         <v>198.7380673001931</v>
       </c>
       <c r="B195" t="n">
-        <v>63677.37109375</v>
+        <v>46434.578125</v>
       </c>
     </row>
     <row r="196">
@@ -1985,7 +1985,7 @@
         <v>142.4288157776057</v>
       </c>
       <c r="B196" t="n">
-        <v>154970.140625</v>
+        <v>174091.09375</v>
       </c>
     </row>
     <row r="197">
@@ -1993,7 +1993,7 @@
         <v>56.69848019403084</v>
       </c>
       <c r="B197" t="n">
-        <v>12041891</v>
+        <v>14513471</v>
       </c>
     </row>
     <row r="198">
@@ -2001,7 +2001,7 @@
         <v>128.1248642937487</v>
       </c>
       <c r="B198" t="n">
-        <v>216995.421875</v>
+        <v>247047.140625</v>
       </c>
     </row>
     <row r="199">
@@ -2009,7 +2009,7 @@
         <v>247.6212399730692</v>
       </c>
       <c r="B199" t="n">
-        <v>16360.861328125</v>
+        <v>13304.2392578125</v>
       </c>
     </row>
     <row r="200">
@@ -2017,7 +2017,7 @@
         <v>210.7883327164759</v>
       </c>
       <c r="B200" t="n">
-        <v>51655.11328125</v>
+        <v>35724.80859375</v>
       </c>
     </row>
     <row r="201">
@@ -2025,7 +2025,7 @@
         <v>50.10770387161789</v>
       </c>
       <c r="B201" t="n">
-        <v>23272688</v>
+        <v>31132338</v>
       </c>
     </row>
     <row r="202">
@@ -2033,7 +2033,7 @@
         <v>140.0354883862702</v>
       </c>
       <c r="B202" t="n">
-        <v>16793.125</v>
+        <v>11374.130859375</v>
       </c>
     </row>
     <row r="203">
@@ -2041,7 +2041,7 @@
         <v>179.2702278700552</v>
       </c>
       <c r="B203" t="n">
-        <v>830.9387817382812</v>
+        <v>1088.68310546875</v>
       </c>
     </row>
     <row r="204">
@@ -2049,7 +2049,7 @@
         <v>212.9149331009158</v>
       </c>
       <c r="B204" t="n">
-        <v>35.19507217407227</v>
+        <v>78.50325775146484</v>
       </c>
     </row>
     <row r="205">
@@ -2057,7 +2057,7 @@
         <v>154.3953007954327</v>
       </c>
       <c r="B205" t="n">
-        <v>5154.27099609375</v>
+        <v>5465.52685546875</v>
       </c>
     </row>
     <row r="206">
@@ -2065,7 +2065,7 @@
         <v>108.9476953256664</v>
       </c>
       <c r="B206" t="n">
-        <v>76685.7421875</v>
+        <v>63896.01953125</v>
       </c>
     </row>
     <row r="207">
@@ -2073,7 +2073,7 @@
         <v>218.7650671240587</v>
       </c>
       <c r="B207" t="n">
-        <v>19.56618499755859</v>
+        <v>52.80207824707031</v>
       </c>
     </row>
     <row r="208">
@@ -2081,7 +2081,7 @@
         <v>50.77669531672117</v>
       </c>
       <c r="B208" t="n">
-        <v>5258720</v>
+        <v>4664490</v>
       </c>
     </row>
     <row r="209">
@@ -2089,7 +2089,7 @@
         <v>36.521718311732</v>
       </c>
       <c r="B209" t="n">
-        <v>20232512</v>
+        <v>18085318</v>
       </c>
     </row>
     <row r="210">
@@ -2097,7 +2097,7 @@
         <v>62.20723181657478</v>
       </c>
       <c r="B210" t="n">
-        <v>957667</v>
+        <v>943253.5625</v>
       </c>
     </row>
     <row r="211">
@@ -2105,7 +2105,7 @@
         <v>152.8672768548223</v>
       </c>
       <c r="B211" t="n">
-        <v>5768.572265625</v>
+        <v>5894.3583984375</v>
       </c>
     </row>
     <row r="212">
@@ -2113,7 +2113,7 @@
         <v>203.7587766492272</v>
       </c>
       <c r="B212" t="n">
-        <v>96.26335906982422</v>
+        <v>159.9148864746094</v>
       </c>
     </row>
     <row r="213">
@@ -2121,7 +2121,7 @@
         <v>68.70340848462841</v>
       </c>
       <c r="B213" t="n">
-        <v>566105.375</v>
+        <v>594955.0625</v>
       </c>
     </row>
     <row r="214">
@@ -2129,7 +2129,7 @@
         <v>174.7958688983323</v>
       </c>
       <c r="B214" t="n">
-        <v>1176.086669921875</v>
+        <v>1545.075927734375</v>
       </c>
     </row>
     <row r="215">
@@ -2137,7 +2137,7 @@
         <v>227.1920521343508</v>
       </c>
       <c r="B215" t="n">
-        <v>10.83958339691162</v>
+        <v>36.76560592651367</v>
       </c>
     </row>
     <row r="216">
@@ -2145,7 +2145,7 @@
         <v>83.88862390773959</v>
       </c>
       <c r="B216" t="n">
-        <v>248354.46875</v>
+        <v>255465.59375</v>
       </c>
     </row>
     <row r="217">
@@ -2153,7 +2153,7 @@
         <v>187.8164871857543</v>
       </c>
       <c r="B217" t="n">
-        <v>427.9551086425781</v>
+        <v>557.80126953125</v>
       </c>
     </row>
     <row r="218">
@@ -2161,7 +2161,7 @@
         <v>132.3638365501875</v>
       </c>
       <c r="B218" t="n">
-        <v>24395.35546875</v>
+        <v>17501.5234375</v>
       </c>
     </row>
     <row r="219">
@@ -2169,7 +2169,7 @@
         <v>147.5641020239134</v>
       </c>
       <c r="B219" t="n">
-        <v>8988.6669921875</v>
+        <v>7516.34716796875</v>
       </c>
     </row>
     <row r="220">
@@ -2177,7 +2177,7 @@
         <v>210.9485708257926</v>
       </c>
       <c r="B220" t="n">
-        <v>43.68454360961914</v>
+        <v>91.46369934082031</v>
       </c>
     </row>
     <row r="221">
@@ -2185,7 +2185,7 @@
         <v>103.7986266013015</v>
       </c>
       <c r="B221" t="n">
-        <v>97629.7265625</v>
+        <v>84945.9140625</v>
       </c>
     </row>
     <row r="222">
@@ -2193,7 +2193,7 @@
         <v>42.66608835781876</v>
       </c>
       <c r="B222" t="n">
-        <v>11631831</v>
+        <v>10380133</v>
       </c>
     </row>
     <row r="223">
@@ -2201,7 +2201,7 @@
         <v>215.9669959054709</v>
       </c>
       <c r="B223" t="n">
-        <v>25.16630935668945</v>
+        <v>61.93893051147461</v>
       </c>
     </row>
     <row r="224">
@@ -2209,7 +2209,7 @@
         <v>141.6654595688979</v>
       </c>
       <c r="B224" t="n">
-        <v>14749.1494140625</v>
+        <v>10306.5087890625</v>
       </c>
     </row>
     <row r="225">
@@ -2217,7 +2217,7 @@
         <v>111.384878620613</v>
       </c>
       <c r="B225" t="n">
-        <v>68403.7890625</v>
+        <v>55839.13671875</v>
       </c>
     </row>
     <row r="226">
@@ -2225,7 +2225,7 @@
         <v>200.9025042077379</v>
       </c>
       <c r="B226" t="n">
-        <v>131.7572021484375</v>
+        <v>200.0052337646484</v>
       </c>
     </row>
     <row r="227">
@@ -2233,7 +2233,7 @@
         <v>64.10143913402678</v>
       </c>
       <c r="B227" t="n">
-        <v>809437.0625</v>
+        <v>804381</v>
       </c>
     </row>
     <row r="228">
@@ -2241,7 +2241,7 @@
         <v>130.5129297392371</v>
       </c>
       <c r="B228" t="n">
-        <v>26695.3125</v>
+        <v>19387.841796875</v>
       </c>
     </row>
     <row r="229">
@@ -2249,7 +2249,7 @@
         <v>125.2835133984645</v>
       </c>
       <c r="B229" t="n">
-        <v>34433.64453125</v>
+        <v>25889.78125</v>
       </c>
     </row>
     <row r="230">
@@ -2257,7 +2257,7 @@
         <v>192.0229157626965</v>
       </c>
       <c r="B230" t="n">
-        <v>308.7180480957031</v>
+        <v>401.3612365722656</v>
       </c>
     </row>
     <row r="231">
@@ -2265,7 +2265,7 @@
         <v>117.8987570640804</v>
       </c>
       <c r="B231" t="n">
-        <v>49470.83984375</v>
+        <v>38948.55078125</v>
       </c>
     </row>
     <row r="232">
@@ -2273,7 +2273,7 @@
         <v>162.4159286332318</v>
       </c>
       <c r="B232" t="n">
-        <v>2894.061767578125</v>
+        <v>3471.2021484375</v>
       </c>
     </row>
     <row r="233">
@@ -2281,7 +2281,7 @@
         <v>208.6355292509445</v>
       </c>
       <c r="B233" t="n">
-        <v>56.32739639282227</v>
+        <v>109.4734420776367</v>
       </c>
     </row>
     <row r="234">
@@ -2289,7 +2289,7 @@
         <v>224.1420351832661</v>
       </c>
       <c r="B234" t="n">
-        <v>13.37657070159912</v>
+        <v>41.30549240112305</v>
       </c>
     </row>
     <row r="235">
@@ -2297,7 +2297,7 @@
         <v>120.562263164514</v>
       </c>
       <c r="B235" t="n">
-        <v>43329.921875</v>
+        <v>33614.04296875</v>
       </c>
     </row>
     <row r="236">
@@ -2305,7 +2305,7 @@
         <v>102.0983773477591</v>
       </c>
       <c r="B236" t="n">
-        <v>105732.7421875</v>
+        <v>93320.7734375</v>
       </c>
     </row>
     <row r="237">
@@ -2313,7 +2313,7 @@
         <v>169.6303247181462</v>
       </c>
       <c r="B237" t="n">
-        <v>1750.821166992188</v>
+        <v>2269.07470703125</v>
       </c>
     </row>
     <row r="238">
@@ -2321,7 +2321,7 @@
         <v>92.64156328137325</v>
       </c>
       <c r="B238" t="n">
-        <v>164743.6875</v>
+        <v>157437.53125</v>
       </c>
     </row>
     <row r="239">
@@ -2329,7 +2329,7 @@
         <v>173.1078995637023</v>
       </c>
       <c r="B239" t="n">
-        <v>1340.775512695312</v>
+        <v>1763.240966796875</v>
       </c>
     </row>
     <row r="240">
@@ -2337,7 +2337,7 @@
         <v>116.7951555489059</v>
       </c>
       <c r="B240" t="n">
-        <v>52278.45703125</v>
+        <v>41399.75</v>
       </c>
     </row>
     <row r="241">
@@ -2345,7 +2345,7 @@
         <v>207.2104134419902</v>
       </c>
       <c r="B241" t="n">
-        <v>65.87698364257812</v>
+        <v>122.2934112548828</v>
       </c>
     </row>
     <row r="242">
@@ -2353,7 +2353,7 @@
         <v>138.6897313262243</v>
       </c>
       <c r="B242" t="n">
-        <v>17930.03125</v>
+        <v>12285.400390625</v>
       </c>
     </row>
     <row r="243">
@@ -2361,7 +2361,7 @@
         <v>87.15712940455944</v>
       </c>
       <c r="B243" t="n">
-        <v>213061.53125</v>
+        <v>213221.59375</v>
       </c>
     </row>
     <row r="244">
@@ -2369,7 +2369,7 @@
         <v>109.747022055017</v>
       </c>
       <c r="B244" t="n">
-        <v>73864.59375</v>
+        <v>61133.15625</v>
       </c>
     </row>
     <row r="245">
@@ -2377,7 +2377,7 @@
         <v>193.7313456113075</v>
       </c>
       <c r="B245" t="n">
-        <v>270.3677368164062</v>
+        <v>351.1387939453125</v>
       </c>
     </row>
     <row r="246">
@@ -2385,7 +2385,7 @@
         <v>182.5303784110089</v>
       </c>
       <c r="B246" t="n">
-        <v>645.118408203125</v>
+        <v>843.555419921875</v>
       </c>
     </row>
     <row r="247">
@@ -2393,7 +2393,7 @@
         <v>44.60057216576749</v>
       </c>
       <c r="B247" t="n">
-        <v>9771519</v>
+        <v>8715415</v>
       </c>
     </row>
     <row r="248">
@@ -2401,7 +2401,7 @@
         <v>226.046128873272</v>
       </c>
       <c r="B248" t="n">
-        <v>11.69115447998047</v>
+        <v>38.17525863647461</v>
       </c>
     </row>
     <row r="249">
@@ -2409,7 +2409,7 @@
         <v>33.47332461150475</v>
       </c>
       <c r="B249" t="n">
-        <v>26626814</v>
+        <v>23820702</v>
       </c>
     </row>
     <row r="250">
@@ -2417,7 +2417,7 @@
         <v>221.389080123334</v>
       </c>
       <c r="B250" t="n">
-        <v>16.25196647644043</v>
+        <v>46.82542037963867</v>
       </c>
     </row>
     <row r="251">
@@ -2425,7 +2425,7 @@
         <v>127.11801426026</v>
       </c>
       <c r="B251" t="n">
-        <v>31492.150390625</v>
+        <v>23391.990234375</v>
       </c>
     </row>
     <row r="252">
@@ -2433,7 +2433,7 @@
         <v>135.1127462755375</v>
       </c>
       <c r="B252" t="n">
-        <v>21340.146484375</v>
+        <v>15033.2529296875</v>
       </c>
     </row>
     <row r="253">
@@ -2441,7 +2441,7 @@
         <v>190.2918604822213</v>
       </c>
       <c r="B253" t="n">
-        <v>353.1272277832031</v>
+        <v>459.5797729492188</v>
       </c>
     </row>
     <row r="254">
@@ -2449,7 +2449,7 @@
         <v>79.13317305317267</v>
       </c>
       <c r="B254" t="n">
-        <v>310401.15625</v>
+        <v>332313</v>
       </c>
     </row>
     <row r="255">
@@ -2457,7 +2457,7 @@
         <v>160.5488846418035</v>
       </c>
       <c r="B255" t="n">
-        <v>3284.213134765625</v>
+        <v>3862.18017578125</v>
       </c>
     </row>
     <row r="256">
@@ -2465,7 +2465,7 @@
         <v>205.1094784136914</v>
       </c>
       <c r="B256" t="n">
-        <v>82.98492431640625</v>
+        <v>143.9813079833984</v>
       </c>
     </row>
     <row r="257">
@@ -2473,7 +2473,7 @@
         <v>54.79534465025021</v>
       </c>
       <c r="B257" t="n">
-        <v>2783994</v>
+        <v>2558352.75</v>
       </c>
     </row>
     <row r="258">
@@ -2481,7 +2481,7 @@
         <v>148.7915681082776</v>
       </c>
       <c r="B258" t="n">
-        <v>8111.16748046875</v>
+        <v>7105.12255859375</v>
       </c>
     </row>
     <row r="259">
@@ -2489,7 +2489,7 @@
         <v>229.7367103651724</v>
       </c>
       <c r="B259" t="n">
-        <v>9.796977996826172</v>
+        <v>34.2577018737793</v>
       </c>
     </row>
     <row r="260">
@@ -2497,7 +2497,7 @@
         <v>66.24192393139936</v>
       </c>
       <c r="B260" t="n">
-        <v>675770.4375</v>
+        <v>692414.8125</v>
       </c>
     </row>
     <row r="261">
@@ -2505,7 +2505,7 @@
         <v>76.4391955747808</v>
       </c>
       <c r="B261" t="n">
-        <v>353053.5625</v>
+        <v>385700.15625</v>
       </c>
     </row>
     <row r="262">
@@ -2513,7 +2513,7 @@
         <v>105.7532767099348</v>
       </c>
       <c r="B262" t="n">
-        <v>89078.5859375</v>
+        <v>76242.375</v>
       </c>
     </row>
     <row r="263">
@@ -2521,7 +2521,7 @@
         <v>156.8836515784944</v>
       </c>
       <c r="B263" t="n">
-        <v>4290.7392578125</v>
+        <v>4749.06201171875</v>
       </c>
     </row>
     <row r="264">
@@ -2529,7 +2529,7 @@
         <v>99.87502289272837</v>
       </c>
       <c r="B264" t="n">
-        <v>117352.5</v>
+        <v>105530.4765625</v>
       </c>
     </row>
     <row r="265">
@@ -2537,7 +2537,7 @@
         <v>158.3164643185314</v>
       </c>
       <c r="B265" t="n">
-        <v>3860.80224609375</v>
+        <v>4380.39111328125</v>
       </c>
     </row>
     <row r="266">
@@ -2545,7 +2545,7 @@
         <v>59.1500295850548</v>
       </c>
       <c r="B266" t="n">
-        <v>1397523.25</v>
+        <v>1334451.5</v>
       </c>
     </row>
     <row r="267">
@@ -2553,7 +2553,7 @@
         <v>217.5922766801848</v>
       </c>
       <c r="B267" t="n">
-        <v>21.25840759277344</v>
+        <v>55.71443557739258</v>
       </c>
     </row>
     <row r="268">
@@ -2561,7 +2561,7 @@
         <v>71.47845682941541</v>
       </c>
       <c r="B268" t="n">
-        <v>475293</v>
+        <v>508412.625</v>
       </c>
     </row>
     <row r="269">
@@ -2569,7 +2569,7 @@
         <v>94.31762446101135</v>
       </c>
       <c r="B269" t="n">
-        <v>152290.890625</v>
+        <v>143500.421875</v>
       </c>
     </row>
     <row r="270">
@@ -2577,7 +2577,7 @@
         <v>198.3610644500947</v>
       </c>
       <c r="B270" t="n">
-        <v>174.205810546875</v>
+        <v>244.4932098388672</v>
       </c>
     </row>
     <row r="271">
@@ -2585,7 +2585,7 @@
         <v>98.10661307376968</v>
       </c>
       <c r="B271" t="n">
-        <v>127498.8984375</v>
+        <v>116372.6015625</v>
       </c>
     </row>
     <row r="272">
@@ -2593,7 +2593,7 @@
         <v>47.82736478191461</v>
       </c>
       <c r="B272" t="n">
-        <v>7306525</v>
+        <v>6499330</v>
       </c>
     </row>
     <row r="273">
@@ -2601,7 +2601,7 @@
         <v>122.514213676154</v>
       </c>
       <c r="B273" t="n">
-        <v>39402.546875</v>
+        <v>30174.4609375</v>
       </c>
     </row>
     <row r="274">
@@ -2609,7 +2609,7 @@
         <v>66.82307448372424</v>
       </c>
       <c r="B274" t="n">
-        <v>648098.8125</v>
+        <v>667799.375</v>
       </c>
     </row>
     <row r="275">
@@ -2617,7 +2617,7 @@
         <v>82.28448999528204</v>
       </c>
       <c r="B275" t="n">
-        <v>267757.71875</v>
+        <v>279164</v>
       </c>
     </row>
     <row r="276">
@@ -2625,7 +2625,7 @@
         <v>54.23209207656455</v>
       </c>
       <c r="B276" t="n">
-        <v>3043559.25</v>
+        <v>2783043.5</v>
       </c>
     </row>
     <row r="277">
@@ -2633,7 +2633,7 @@
         <v>90.30501580630896</v>
       </c>
       <c r="B277" t="n">
-        <v>183820.84375</v>
+        <v>179153.90625</v>
       </c>
     </row>
     <row r="278">
@@ -2641,7 +2641,7 @@
         <v>181.5942395467398</v>
       </c>
       <c r="B278" t="n">
-        <v>693.754150390625</v>
+        <v>907.6659545898438</v>
       </c>
     </row>
     <row r="279">
@@ -2649,7 +2649,7 @@
         <v>184.9052390083162</v>
       </c>
       <c r="B279" t="n">
-        <v>536.4907836914062</v>
+        <v>700.5039672851562</v>
       </c>
     </row>
     <row r="280">
@@ -2657,7 +2657,7 @@
         <v>164.8260703564691</v>
       </c>
       <c r="B280" t="n">
-        <v>2458.155029296875</v>
+        <v>3011.61767578125</v>
       </c>
     </row>
     <row r="281">
@@ -2665,7 +2665,7 @@
         <v>48.70131375408127</v>
       </c>
       <c r="B281" t="n">
-        <v>6753328</v>
+        <v>5981783.5</v>
       </c>
     </row>
     <row r="282">
@@ -2673,7 +2673,7 @@
         <v>73.29437496396767</v>
       </c>
       <c r="B282" t="n">
-        <v>424640.8125</v>
+        <v>459104.4375</v>
       </c>
     </row>
     <row r="283">
@@ -2681,7 +2681,7 @@
         <v>150.9273597807658</v>
       </c>
       <c r="B283" t="n">
-        <v>6783.5517578125</v>
+        <v>6442.49560546875</v>
       </c>
     </row>
     <row r="284">
@@ -2689,7 +2689,7 @@
         <v>77.04898983543568</v>
       </c>
       <c r="B284" t="n">
-        <v>342642</v>
+        <v>372910.1875</v>
       </c>
     </row>
     <row r="285">
@@ -2697,7 +2697,7 @@
         <v>114.8875785509233</v>
       </c>
       <c r="B285" t="n">
-        <v>57512.37890625</v>
+        <v>46005.86328125</v>
       </c>
     </row>
     <row r="286">
@@ -2705,7 +2705,7 @@
         <v>196.3483126611968</v>
       </c>
       <c r="B286" t="n">
-        <v>217.3299560546875</v>
+        <v>286.5508728027344</v>
       </c>
     </row>
     <row r="287">
@@ -2713,7 +2713,7 @@
         <v>39.96327488091406</v>
       </c>
       <c r="B287" t="n">
-        <v>14838746</v>
+        <v>13251625</v>
       </c>
     </row>
     <row r="288">
@@ -2721,7 +2721,7 @@
         <v>127.9649884057697</v>
       </c>
       <c r="B288" t="n">
-        <v>30220.18359375</v>
+        <v>22321.599609375</v>
       </c>
     </row>
     <row r="289">
@@ -2729,7 +2729,7 @@
         <v>167.0483587243739</v>
       </c>
       <c r="B289" t="n">
-        <v>2102.508056640625</v>
+        <v>2641.961669921875</v>
       </c>
     </row>
     <row r="290">
@@ -2737,7 +2737,7 @@
         <v>232.592747305985</v>
       </c>
       <c r="B290" t="n">
-        <v>9.002533912658691</v>
+        <v>31.87275695800781</v>
       </c>
     </row>
     <row r="291">
@@ -2745,7 +2745,7 @@
         <v>199.4360799423602</v>
       </c>
       <c r="B291" t="n">
-        <v>154.795654296875</v>
+        <v>224.5799865722656</v>
       </c>
     </row>
     <row r="292">
@@ -2753,7 +2753,7 @@
         <v>177.8225282811744</v>
       </c>
       <c r="B292" t="n">
-        <v>929.7876586914062</v>
+        <v>1219.26318359375</v>
       </c>
     </row>
     <row r="293">
@@ -2761,7 +2761,7 @@
         <v>40.76222669489226</v>
       </c>
       <c r="B293" t="n">
-        <v>13808204</v>
+        <v>12328654</v>
       </c>
     </row>
     <row r="294">
@@ -2769,7 +2769,7 @@
         <v>57.50345968560517</v>
       </c>
       <c r="B294" t="n">
-        <v>1813558.5</v>
+        <v>1706784.5</v>
       </c>
     </row>
     <row r="295">
@@ -2777,7 +2777,7 @@
         <v>136.774431728005</v>
       </c>
       <c r="B295" t="n">
-        <v>19682.001953125</v>
+        <v>13709.6025390625</v>
       </c>
     </row>
     <row r="296">
@@ -2785,7 +2785,7 @@
         <v>96.35177166870113</v>
       </c>
       <c r="B296" t="n">
-        <v>138434.984375</v>
+        <v>128232.4375</v>
       </c>
     </row>
     <row r="297">
@@ -2793,7 +2793,7 @@
         <v>34.80863056204315</v>
       </c>
       <c r="B297" t="n">
-        <v>23608860</v>
+        <v>21113126</v>
       </c>
     </row>
     <row r="298">
@@ -2801,7 +2801,7 @@
         <v>86.08340985066506</v>
       </c>
       <c r="B298" t="n">
-        <v>224064.359375</v>
+        <v>226266.109375</v>
       </c>
     </row>
     <row r="299">
@@ -2809,7 +2809,7 @@
         <v>171.8661407837238</v>
       </c>
       <c r="B299" t="n">
-        <v>1476.475219726562</v>
+        <v>1943.164672851562</v>
       </c>
     </row>
     <row r="300">
@@ -2817,7 +2817,7 @@
         <v>145.424942423417</v>
       </c>
       <c r="B300" t="n">
-        <v>10750.8935546875</v>
+        <v>8290.6826171875</v>
       </c>
     </row>
     <row r="301">
@@ -2825,7 +2825,7 @@
         <v>30.07731725909613</v>
       </c>
       <c r="B301" t="n">
-        <v>36156792</v>
+        <v>32375944</v>
       </c>
     </row>
     <row r="302">
@@ -2833,7 +2833,7 @@
         <v>202.1228148230764</v>
       </c>
       <c r="B302" t="n">
-        <v>21814.46875</v>
+        <v>15784.392578125</v>
       </c>
     </row>
     <row r="303">
@@ -2841,7 +2841,7 @@
         <v>248.3156686859416</v>
       </c>
       <c r="B303" t="n">
-        <v>2973.30810546875</v>
+        <v>1674.90234375</v>
       </c>
     </row>
     <row r="304">
@@ -2849,7 +2849,7 @@
         <v>287.9271194674773</v>
       </c>
       <c r="B304" t="n">
-        <v>282.242919921875</v>
+        <v>229.6935729980469</v>
       </c>
     </row>
     <row r="305">
@@ -2857,7 +2857,7 @@
         <v>219.0292789628152</v>
       </c>
       <c r="B305" t="n">
-        <v>12966.7490234375</v>
+        <v>7524.90625</v>
       </c>
     </row>
     <row r="306">
@@ -2865,7 +2865,7 @@
         <v>165.521733723482</v>
       </c>
       <c r="B306" t="n">
-        <v>50784.74609375</v>
+        <v>46990.640625</v>
       </c>
     </row>
     <row r="307">
@@ -2873,7 +2873,7 @@
         <v>294.8147499083752</v>
       </c>
       <c r="B307" t="n">
-        <v>185.7525177001953</v>
+        <v>167.8366851806641</v>
       </c>
     </row>
     <row r="308">
@@ -2881,7 +2881,7 @@
         <v>97.03435397216592</v>
       </c>
       <c r="B308" t="n">
-        <v>707804.1875</v>
+        <v>794592.6875</v>
       </c>
     </row>
     <row r="309">
@@ -2889,7 +2889,7 @@
         <v>80.251317350192</v>
       </c>
       <c r="B309" t="n">
-        <v>2008188.5</v>
+        <v>1972752.25</v>
       </c>
     </row>
     <row r="310">
@@ -2897,7 +2897,7 @@
         <v>110.4920475635838</v>
       </c>
       <c r="B310" t="n">
-        <v>399372.75</v>
+        <v>449142.125</v>
       </c>
     </row>
     <row r="311">
@@ -2905,7 +2905,7 @@
         <v>217.2302664673518</v>
       </c>
       <c r="B311" t="n">
-        <v>13766.771484375</v>
+        <v>8172.904296875</v>
       </c>
     </row>
     <row r="312">
@@ -2913,7 +2913,7 @@
         <v>277.1471575642466</v>
       </c>
       <c r="B312" t="n">
-        <v>550.2083129882812</v>
+        <v>386.4542846679688</v>
       </c>
     </row>
     <row r="313">
@@ -2921,7 +2921,7 @@
         <v>118.1402935680915</v>
       </c>
       <c r="B313" t="n">
-        <v>288490.59375</v>
+        <v>305844.59375</v>
       </c>
     </row>
     <row r="314">
@@ -2929,7 +2929,7 @@
         <v>243.0478011575689</v>
       </c>
       <c r="B314" t="n">
-        <v>4074.03662109375</v>
+        <v>2203.58642578125</v>
       </c>
     </row>
     <row r="315">
@@ -2937,7 +2937,7 @@
         <v>304.7362249125831</v>
       </c>
       <c r="B315" t="n">
-        <v>76.29835510253906</v>
+        <v>94.22177124023438</v>
       </c>
     </row>
     <row r="316">
@@ -2945,7 +2945,7 @@
         <v>136.0185424400076</v>
       </c>
       <c r="B316" t="n">
-        <v>134883.59375</v>
+        <v>122580.890625</v>
       </c>
     </row>
     <row r="317">
@@ -2953,7 +2953,7 @@
         <v>258.3775707869457</v>
       </c>
       <c r="B317" t="n">
-        <v>1640.4228515625</v>
+        <v>991.8029174804688</v>
       </c>
     </row>
     <row r="318">
@@ -2961,7 +2961,7 @@
         <v>193.0906281228841</v>
       </c>
       <c r="B318" t="n">
-        <v>26886.36328125</v>
+        <v>21803.357421875</v>
       </c>
     </row>
     <row r="319">
@@ -2969,7 +2969,7 @@
         <v>210.9865961079592</v>
       </c>
       <c r="B319" t="n">
-        <v>16780.591796875</v>
+        <v>10667.78515625</v>
       </c>
     </row>
     <row r="320">
@@ -2977,7 +2977,7 @@
         <v>285.6120311959277</v>
       </c>
       <c r="B320" t="n">
-        <v>327.0295104980469</v>
+        <v>255.5817413330078</v>
       </c>
     </row>
     <row r="321">
@@ -2985,7 +2985,7 @@
         <v>159.4594995339895</v>
       </c>
       <c r="B321" t="n">
-        <v>59974.0859375</v>
+        <v>54188.453125</v>
       </c>
     </row>
     <row r="322">
@@ -2993,7 +2993,7 @@
         <v>87.48536532279425</v>
       </c>
       <c r="B322" t="n">
-        <v>1178981.5</v>
+        <v>1246736.375</v>
       </c>
     </row>
     <row r="323">
@@ -3001,7 +3001,7 @@
         <v>291.52045264532</v>
       </c>
       <c r="B323" t="n">
-        <v>224.674072265625</v>
+        <v>194.8594512939453</v>
       </c>
     </row>
     <row r="324">
@@ -3009,7 +3009,7 @@
         <v>204.0418544708589</v>
       </c>
       <c r="B324" t="n">
-        <v>20863.650390625</v>
+        <v>14395.759765625</v>
       </c>
     </row>
     <row r="325">
@@ -3017,7 +3017,7 @@
         <v>168.3911411226828</v>
       </c>
       <c r="B325" t="n">
-        <v>47531.9609375</v>
+        <v>43925.32421875</v>
       </c>
     </row>
     <row r="326">
@@ -3025,7 +3025,7 @@
         <v>273.784337338646</v>
       </c>
       <c r="B326" t="n">
-        <v>676.9481811523438</v>
+        <v>452.9225769042969</v>
       </c>
     </row>
     <row r="327">
@@ -3033,7 +3033,7 @@
         <v>112.7221845022321</v>
       </c>
       <c r="B327" t="n">
-        <v>363239.09375</v>
+        <v>403493.8125</v>
       </c>
     </row>
     <row r="328">
@@ -3041,7 +3041,7 @@
         <v>190.9114708516259</v>
       </c>
       <c r="B328" t="n">
-        <v>28272.45703125</v>
+        <v>23570.681640625</v>
       </c>
     </row>
     <row r="329">
@@ -3049,7 +3049,7 @@
         <v>184.7546397372707</v>
       </c>
       <c r="B329" t="n">
-        <v>32587.140625</v>
+        <v>29160.830078125</v>
       </c>
     </row>
     <row r="330">
@@ -3057,7 +3057,7 @@
         <v>263.3299916031862</v>
       </c>
       <c r="B330" t="n">
-        <v>1239.716186523438</v>
+        <v>770.1409301757812</v>
       </c>
     </row>
     <row r="331">
@@ -3065,7 +3065,7 @@
         <v>176.060228237277</v>
       </c>
       <c r="B331" t="n">
-        <v>39824.69921875</v>
+        <v>36678.5859375</v>
       </c>
     </row>
     <row r="332">
@@ -3073,7 +3073,7 @@
         <v>228.4723310761853</v>
       </c>
       <c r="B332" t="n">
-        <v>8898.1611328125</v>
+        <v>4652.0947265625</v>
       </c>
     </row>
     <row r="333">
@@ -3081,7 +3081,7 @@
         <v>282.8887815235335</v>
       </c>
       <c r="B333" t="n">
-        <v>388.3168029785156</v>
+        <v>292.7032775878906</v>
       </c>
     </row>
     <row r="334">
@@ -3089,7 +3089,7 @@
         <v>301.1453004116329</v>
       </c>
       <c r="B334" t="n">
-        <v>121.5553359985352</v>
+        <v>116.8898162841797</v>
       </c>
     </row>
     <row r="335">
@@ -3097,7 +3097,7 @@
         <v>179.1960958301033</v>
       </c>
       <c r="B335" t="n">
-        <v>37045.47265625</v>
+        <v>34071.82421875</v>
       </c>
     </row>
     <row r="336">
@@ -3105,7 +3105,7 @@
         <v>157.4577182979553</v>
       </c>
       <c r="B336" t="n">
-        <v>63591.22265625</v>
+        <v>56799.6796875</v>
       </c>
     </row>
     <row r="337">
@@ -3113,7 +3113,7 @@
         <v>236.9661696601526</v>
       </c>
       <c r="B337" t="n">
-        <v>5860.5595703125</v>
+        <v>3018.460205078125</v>
       </c>
     </row>
     <row r="338">
@@ -3121,7 +3121,7 @@
         <v>146.3237784292482</v>
       </c>
       <c r="B338" t="n">
-        <v>88047.671875</v>
+        <v>73794.5625</v>
       </c>
     </row>
     <row r="339">
@@ -3129,7 +3129,7 @@
         <v>241.0604776319014</v>
       </c>
       <c r="B339" t="n">
-        <v>4588.041015625</v>
+        <v>2443.85986328125</v>
       </c>
     </row>
     <row r="340">
@@ -3137,7 +3137,7 @@
         <v>174.760907681463</v>
       </c>
       <c r="B340" t="n">
-        <v>41036.484375</v>
+        <v>37816.26953125</v>
       </c>
     </row>
     <row r="341">
@@ -3145,7 +3145,7 @@
         <v>281.2109274797239</v>
       </c>
       <c r="B341" t="n">
-        <v>429.9444580078125</v>
+        <v>318.2990112304688</v>
       </c>
     </row>
     <row r="342">
@@ -3153,7 +3153,7 @@
         <v>200.5383934651797</v>
       </c>
       <c r="B342" t="n">
-        <v>22632.052734375</v>
+        <v>16704.70703125</v>
       </c>
     </row>
     <row r="343">
@@ -3161,7 +3161,7 @@
         <v>139.8667035021441</v>
       </c>
       <c r="B343" t="n">
-        <v>114523</v>
+        <v>100682.5</v>
       </c>
     </row>
     <row r="344">
@@ -3169,7 +3169,7 @@
         <v>166.4628176527595</v>
       </c>
       <c r="B344" t="n">
-        <v>49694.09765625</v>
+        <v>45962.44140625</v>
       </c>
     </row>
     <row r="345">
@@ -3177,7 +3177,7 @@
         <v>265.3414042280734</v>
       </c>
       <c r="B345" t="n">
-        <v>1106.422485351562</v>
+        <v>695.3659057617188</v>
       </c>
     </row>
     <row r="346">
@@ -3185,7 +3185,7 @@
         <v>252.1539930762808</v>
       </c>
       <c r="B346" t="n">
-        <v>2363.606689453125</v>
+        <v>1371.450317382812</v>
       </c>
     </row>
     <row r="347">
@@ -3193,7 +3193,7 @@
         <v>89.76292161643512</v>
       </c>
       <c r="B347" t="n">
-        <v>997160.3125</v>
+        <v>1118567.5</v>
       </c>
     </row>
     <row r="348">
@@ -3201,7 +3201,7 @@
         <v>303.3870770290104</v>
       </c>
       <c r="B348" t="n">
-        <v>90.88795471191406</v>
+        <v>102.1708908081055</v>
       </c>
     </row>
     <row r="349">
@@ -3209,7 +3209,7 @@
         <v>76.66230397674337</v>
       </c>
       <c r="B349" t="n">
-        <v>2545098</v>
+        <v>2477683.5</v>
       </c>
     </row>
     <row r="350">
@@ -3217,7 +3217,7 @@
         <v>297.9041204663185</v>
       </c>
       <c r="B350" t="n">
-        <v>155.3998565673828</v>
+        <v>142.0765228271484</v>
       </c>
     </row>
     <row r="351">
@@ -3225,7 +3225,7 @@
         <v>186.9144815339835</v>
       </c>
       <c r="B351" t="n">
-        <v>31003.330078125</v>
+        <v>27100.255859375</v>
       </c>
     </row>
     <row r="352">
@@ -3233,7 +3233,7 @@
         <v>196.3270453107128</v>
       </c>
       <c r="B352" t="n">
-        <v>24952.15625</v>
+        <v>19420.162109375</v>
       </c>
     </row>
     <row r="353">
@@ -3241,7 +3241,7 @@
         <v>261.291941022206</v>
       </c>
       <c r="B353" t="n">
-        <v>1391.165283203125</v>
+        <v>854.11181640625</v>
       </c>
     </row>
     <row r="354">
@@ -3249,7 +3249,7 @@
         <v>130.419732577441</v>
       </c>
       <c r="B354" t="n">
-        <v>171142.140625</v>
+        <v>163219.984375</v>
       </c>
     </row>
     <row r="355">
@@ -3257,7 +3257,7 @@
         <v>226.2741747640417</v>
       </c>
       <c r="B355" t="n">
-        <v>9873.7802734375</v>
+        <v>5203.14794921875</v>
       </c>
     </row>
     <row r="356">
@@ -3265,7 +3265,7 @@
         <v>278.7374005488851</v>
       </c>
       <c r="B356" t="n">
-        <v>499.5860595703125</v>
+        <v>359.1246032714844</v>
       </c>
     </row>
     <row r="357">
@@ -3273,7 +3273,7 @@
         <v>101.7656936938563</v>
       </c>
       <c r="B357" t="n">
-        <v>578809.375</v>
+        <v>650187.8125</v>
       </c>
     </row>
     <row r="358">
@@ -3281,7 +3281,7 @@
         <v>212.4317480881346</v>
       </c>
       <c r="B358" t="n">
-        <v>16029.0361328125</v>
+        <v>10030.31640625</v>
       </c>
     </row>
     <row r="359">
@@ -3289,7 +3289,7 @@
         <v>307.7321674709848</v>
       </c>
       <c r="B359" t="n">
-        <v>51.73329544067383</v>
+        <v>78.71162414550781</v>
       </c>
     </row>
     <row r="360">
@@ -3297,7 +3297,7 @@
         <v>115.2422751856832</v>
       </c>
       <c r="B360" t="n">
-        <v>326326.125</v>
+        <v>354704.09375</v>
       </c>
     </row>
     <row r="361">
@@ -3305,7 +3305,7 @@
         <v>127.2479896372174</v>
       </c>
       <c r="B361" t="n">
-        <v>195853.625</v>
+        <v>191963.171875</v>
       </c>
     </row>
     <row r="362">
@@ -3313,7 +3313,7 @@
         <v>161.7607985360752</v>
       </c>
       <c r="B362" t="n">
-        <v>56069.21484375</v>
+        <v>51334.70703125</v>
       </c>
     </row>
     <row r="363">
@@ -3321,7 +3321,7 @@
         <v>221.9589281867896</v>
       </c>
       <c r="B363" t="n">
-        <v>11615.189453125</v>
+        <v>6482.005859375</v>
       </c>
     </row>
     <row r="364">
@@ -3329,7 +3329,7 @@
         <v>154.840061375089</v>
       </c>
       <c r="B364" t="n">
-        <v>68652.15625</v>
+        <v>60404.9609375</v>
       </c>
     </row>
     <row r="365">
@@ -3337,7 +3337,7 @@
         <v>223.6458441797131</v>
       </c>
       <c r="B365" t="n">
-        <v>10901.4716796875</v>
+        <v>5948.384765625</v>
       </c>
     </row>
     <row r="366">
@@ -3345,7 +3345,7 @@
         <v>106.8926635032362</v>
       </c>
       <c r="B366" t="n">
-        <v>465426.875</v>
+        <v>523179.625</v>
       </c>
     </row>
     <row r="367">
@@ -3353,7 +3353,7 @@
         <v>293.43397006127</v>
       </c>
       <c r="B367" t="n">
-        <v>201.1701812744141</v>
+        <v>178.6741943359375</v>
       </c>
     </row>
     <row r="368">
@@ -3361,7 +3361,7 @@
         <v>121.407484948478</v>
       </c>
       <c r="B368" t="n">
-        <v>251069.578125</v>
+        <v>258783.5625</v>
       </c>
     </row>
     <row r="369">
@@ -3369,7 +3369,7 @@
         <v>148.2970819392216</v>
       </c>
       <c r="B369" t="n">
-        <v>83116.3203125</v>
+        <v>70449.359375</v>
       </c>
     </row>
     <row r="370">
@@ -3377,7 +3377,7 @@
         <v>270.7921840359688</v>
       </c>
       <c r="B370" t="n">
-        <v>812.9168090820312</v>
+        <v>527.24072265625</v>
       </c>
     </row>
     <row r="371">
@@ -3385,7 +3385,7 @@
         <v>152.7580315869067</v>
       </c>
       <c r="B371" t="n">
-        <v>72962.3984375</v>
+        <v>63435.2265625</v>
       </c>
     </row>
     <row r="372">
@@ -3393,7 +3393,7 @@
         <v>93.56197219570706</v>
       </c>
       <c r="B372" t="n">
-        <v>820426.375</v>
+        <v>933422.9375</v>
       </c>
     </row>
     <row r="373">
@@ -3401,7 +3401,7 @@
         <v>181.4942164731368</v>
       </c>
       <c r="B373" t="n">
-        <v>35132.69921875</v>
+        <v>32279.7890625</v>
       </c>
     </row>
     <row r="374">
@@ -3409,7 +3409,7 @@
         <v>115.9264903197472</v>
       </c>
       <c r="B374" t="n">
-        <v>316968.53125</v>
+        <v>342507.34375</v>
       </c>
     </row>
     <row r="375">
@@ -3417,7 +3417,7 @@
         <v>134.1299221925037</v>
       </c>
       <c r="B375" t="n">
-        <v>146163.453125</v>
+        <v>135010.859375</v>
       </c>
     </row>
     <row r="376">
@@ -3425,7 +3425,7 @@
         <v>101.1025506689129</v>
       </c>
       <c r="B376" t="n">
-        <v>595361.5</v>
+        <v>668726.0625</v>
       </c>
     </row>
     <row r="377">
@@ -3433,7 +3433,7 @@
         <v>143.572854185087</v>
       </c>
       <c r="B377" t="n">
-        <v>97824.4765625</v>
+        <v>83299.1328125</v>
       </c>
     </row>
     <row r="378">
@@ -3441,7 +3441,7 @@
         <v>251.0518339611324</v>
       </c>
       <c r="B378" t="n">
-        <v>2524.602783203125</v>
+        <v>1452.47021484375</v>
       </c>
     </row>
     <row r="379">
@@ -3449,7 +3449,7 @@
         <v>254.9500251121614</v>
       </c>
       <c r="B379" t="n">
-        <v>1999.739501953125</v>
+        <v>1185.615478515625</v>
       </c>
     </row>
     <row r="380">
@@ -3457,7 +3457,7 @@
         <v>231.309901195806</v>
       </c>
       <c r="B380" t="n">
-        <v>7770.1259765625</v>
+        <v>4026.131591796875</v>
       </c>
     </row>
     <row r="381">
@@ -3465,7 +3465,7 @@
         <v>94.59091230557016</v>
       </c>
       <c r="B381" t="n">
-        <v>785303.6875</v>
+        <v>888780.1875</v>
       </c>
     </row>
     <row r="382">
@@ -3473,7 +3473,7 @@
         <v>123.5454484502101</v>
       </c>
       <c r="B382" t="n">
-        <v>229250.640625</v>
+        <v>231980.671875</v>
       </c>
     </row>
     <row r="383">
@@ -3481,7 +3481,7 @@
         <v>214.9463133409394</v>
       </c>
       <c r="B383" t="n">
-        <v>14800.7041015625</v>
+        <v>9010.642578125</v>
       </c>
     </row>
     <row r="384">
@@ -3489,7 +3489,7 @@
         <v>127.9659283196059</v>
       </c>
       <c r="B384" t="n">
-        <v>189965.4375</v>
+        <v>185042.71875</v>
       </c>
     </row>
     <row r="385">
@@ -3497,7 +3497,7 @@
         <v>172.5150300062361</v>
       </c>
       <c r="B385" t="n">
-        <v>43218.55078125</v>
+        <v>39866.65234375</v>
       </c>
     </row>
     <row r="386">
@@ -3505,7 +3505,7 @@
         <v>268.4224792674381</v>
       </c>
       <c r="B386" t="n">
-        <v>929.4957885742188</v>
+        <v>594.6578979492188</v>
       </c>
     </row>
     <row r="387">
@@ -3513,7 +3513,7 @@
         <v>84.30321935725675</v>
       </c>
       <c r="B387" t="n">
-        <v>1490224.25</v>
+        <v>1525233.25</v>
       </c>
     </row>
     <row r="388">
@@ -3521,7 +3521,7 @@
         <v>187.9116629462706</v>
       </c>
       <c r="B388" t="n">
-        <v>30298.291015625</v>
+        <v>26198.666015625</v>
       </c>
     </row>
     <row r="389">
@@ -3529,7 +3529,7 @@
         <v>233.9263029655233</v>
       </c>
       <c r="B389" t="n">
-        <v>6857.177734375</v>
+        <v>3523.86865234375</v>
       </c>
     </row>
     <row r="390">
@@ -3537,7 +3537,7 @@
         <v>311.0947104308642</v>
       </c>
       <c r="B390" t="n">
-        <v>33.49744415283203</v>
+        <v>64.32331848144531</v>
       </c>
     </row>
     <row r="391">
@@ -3545,7 +3545,7 @@
         <v>272.0578489591438</v>
       </c>
       <c r="B391" t="n">
-        <v>756.7625732421875</v>
+        <v>494.4216918945312</v>
       </c>
     </row>
     <row r="392">
@@ -3553,7 +3553,7 @@
         <v>246.6112257247711</v>
       </c>
       <c r="B392" t="n">
-        <v>3292.285888671875</v>
+        <v>1830.367065429688</v>
       </c>
     </row>
     <row r="393">
@@ -3561,7 +3561,7 @@
         <v>85.24386188151304</v>
       </c>
       <c r="B393" t="n">
-        <v>1390513.25</v>
+        <v>1436803.125</v>
       </c>
     </row>
     <row r="394">
@@ -3569,7 +3569,7 @@
         <v>104.9540814267144</v>
       </c>
       <c r="B394" t="n">
-        <v>505420.5</v>
+        <v>567989.9375</v>
       </c>
     </row>
     <row r="395">
@@ -3577,7 +3577,7 @@
         <v>198.2834236193697</v>
       </c>
       <c r="B395" t="n">
-        <v>23848.755859375</v>
+        <v>18107.73046875</v>
       </c>
     </row>
     <row r="396">
@@ -3585,7 +3585,7 @@
         <v>150.6919765131795</v>
       </c>
       <c r="B396" t="n">
-        <v>77500.953125</v>
+        <v>66592.421875</v>
       </c>
     </row>
     <row r="397">
@@ -3593,7 +3593,7 @@
         <v>78.23442076525747</v>
       </c>
       <c r="B397" t="n">
-        <v>2329659.25</v>
+        <v>2242292.5</v>
       </c>
     </row>
     <row r="398">
@@ -3601,7 +3601,7 @@
         <v>138.6025643465052</v>
       </c>
       <c r="B398" t="n">
-        <v>120847.78125</v>
+        <v>107406.640625</v>
       </c>
     </row>
     <row r="399">
@@ -3609,7 +3609,7 @@
         <v>239.5984982072595</v>
       </c>
       <c r="B399" t="n">
-        <v>5007.12353515625</v>
+        <v>2637.188232421875</v>
       </c>
     </row>
     <row r="400">
@@ -3617,7 +3617,7 @@
         <v>208.468065639421</v>
       </c>
       <c r="B400" t="n">
-        <v>18175.552734375</v>
+        <v>11877.125</v>
       </c>
     </row>
     <row r="401">
@@ -3625,7 +3625,7 @@
         <v>72.6640291465547</v>
       </c>
       <c r="B401" t="n">
-        <v>3147974</v>
+        <v>3193772.25</v>
       </c>
     </row>
     <row r="402">
@@ -3633,7 +3633,7 @@
         <v>251.8430654888082</v>
       </c>
       <c r="B402" t="n">
-        <v>4892.6826171875</v>
+        <v>4040.157958984375</v>
       </c>
     </row>
     <row r="403">
@@ -3641,7 +3641,7 @@
         <v>308.0781854946882</v>
       </c>
       <c r="B403" t="n">
-        <v>502.4470825195312</v>
+        <v>331.0744018554688</v>
       </c>
     </row>
     <row r="404">
@@ -3649,7 +3649,7 @@
         <v>356.3011139788151</v>
       </c>
       <c r="B404" t="n">
-        <v>17.2804012298584</v>
+        <v>19.2348575592041</v>
       </c>
     </row>
     <row r="405">
@@ -3657,7 +3657,7 @@
         <v>272.4249728677246</v>
       </c>
       <c r="B405" t="n">
-        <v>2397.9619140625</v>
+        <v>1987.048583984375</v>
       </c>
     </row>
     <row r="406">
@@ -3665,7 +3665,7 @@
         <v>207.284957126612</v>
       </c>
       <c r="B406" t="n">
-        <v>30132.8125</v>
+        <v>24549.5078125</v>
       </c>
     </row>
     <row r="407">
@@ -3673,7 +3673,7 @@
         <v>364.6861062884464</v>
       </c>
       <c r="B407" t="n">
-        <v>10.77310752868652</v>
+        <v>11.9102029800415</v>
       </c>
     </row>
     <row r="408">
@@ -3681,7 +3681,7 @@
         <v>123.9085104009484</v>
       </c>
       <c r="B408" t="n">
-        <v>715755.125</v>
+        <v>735849.25</v>
       </c>
     </row>
     <row r="409">
@@ -3689,7 +3689,7 @@
         <v>103.4768635210722</v>
       </c>
       <c r="B409" t="n">
-        <v>3184898.75</v>
+        <v>3858263.75</v>
       </c>
     </row>
     <row r="410">
@@ -3697,7 +3697,7 @@
         <v>140.2918890153653</v>
       </c>
       <c r="B410" t="n">
-        <v>242358.125</v>
+        <v>351946.65625</v>
       </c>
     </row>
     <row r="411">
@@ -3705,7 +3705,7 @@
         <v>270.2348574036574</v>
       </c>
       <c r="B411" t="n">
-        <v>2581.6318359375</v>
+        <v>2141.10595703125</v>
       </c>
     </row>
     <row r="412">
@@ -3713,7 +3713,7 @@
         <v>343.1776024268621</v>
       </c>
       <c r="B412" t="n">
-        <v>38.72473907470703</v>
+        <v>40.59657669067383</v>
       </c>
     </row>
     <row r="413">
@@ -3721,7 +3721,7 @@
         <v>149.6028537194478</v>
       </c>
       <c r="B413" t="n">
-        <v>182260.921875</v>
+        <v>232778</v>
       </c>
     </row>
     <row r="414">
@@ -3729,7 +3729,7 @@
         <v>301.6650904407958</v>
       </c>
       <c r="B414" t="n">
-        <v>682.9107055664062</v>
+        <v>494.8292846679688</v>
       </c>
     </row>
     <row r="415">
@@ -3737,7 +3737,7 @@
         <v>376.7644970099493</v>
       </c>
       <c r="B415" t="n">
-        <v>6.066814422607422</v>
+        <v>8.828098297119141</v>
       </c>
     </row>
     <row r="416">
@@ -3745,7 +3745,7 @@
         <v>171.3678105630307</v>
       </c>
       <c r="B416" t="n">
-        <v>110423.6796875</v>
+        <v>103758.2578125</v>
       </c>
     </row>
     <row r="417">
@@ -3753,7 +3753,7 @@
         <v>320.327531980558</v>
       </c>
       <c r="B417" t="n">
-        <v>214.0157623291016</v>
+        <v>154.1288146972656</v>
       </c>
     </row>
     <row r="418">
@@ -3761,7 +3761,7 @@
         <v>240.8472931879944</v>
       </c>
       <c r="B418" t="n">
-        <v>7206.7021484375</v>
+        <v>6408.16748046875</v>
       </c>
     </row>
     <row r="419">
@@ -3769,7 +3769,7 @@
         <v>262.6338212568117</v>
       </c>
       <c r="B419" t="n">
-        <v>3350.089111328125</v>
+        <v>2774.537353515625</v>
       </c>
     </row>
     <row r="420">
@@ -3777,7 +3777,7 @@
         <v>353.4827285384763</v>
       </c>
       <c r="B420" t="n">
-        <v>20.36434936523438</v>
+        <v>22.73114204406738</v>
       </c>
     </row>
     <row r="421">
@@ -3785,7 +3785,7 @@
         <v>199.9048011362083</v>
       </c>
       <c r="B421" t="n">
-        <v>41000.6796875</v>
+        <v>32899.66015625</v>
       </c>
     </row>
     <row r="422">
@@ -3793,7 +3793,7 @@
         <v>112.2835840816873</v>
       </c>
       <c r="B422" t="n">
-        <v>1665955.75</v>
+        <v>1640385</v>
       </c>
     </row>
     <row r="423">
@@ -3801,7 +3801,7 @@
         <v>360.6756330998245</v>
       </c>
       <c r="B423" t="n">
-        <v>13.44127559661865</v>
+        <v>14.79998874664307</v>
       </c>
     </row>
     <row r="424">
@@ -3809,7 +3809,7 @@
         <v>254.17930185146</v>
       </c>
       <c r="B424" t="n">
-        <v>4506.21044921875</v>
+        <v>3712.754150390625</v>
       </c>
     </row>
     <row r="425">
@@ -3817,7 +3817,7 @@
         <v>210.7781699495056</v>
       </c>
       <c r="B425" t="n">
-        <v>25007.421875</v>
+        <v>21490.654296875</v>
       </c>
     </row>
     <row r="426">
@@ -3825,7 +3825,7 @@
         <v>339.0837094730673</v>
       </c>
       <c r="B426" t="n">
-        <v>50.49997711181641</v>
+        <v>50.06795120239258</v>
       </c>
     </row>
     <row r="427">
@@ -3833,7 +3833,7 @@
         <v>143.0068548139008</v>
       </c>
       <c r="B427" t="n">
-        <v>215997.78125</v>
+        <v>311456.375</v>
       </c>
     </row>
     <row r="428">
@@ -3841,7 +3841,7 @@
         <v>238.1943899700054</v>
       </c>
       <c r="B428" t="n">
-        <v>7912.5224609375</v>
+        <v>7162.54296875</v>
       </c>
     </row>
     <row r="429">
@@ -3849,7 +3849,7 @@
         <v>230.6990718067335</v>
       </c>
       <c r="B429" t="n">
-        <v>10302.9794921875</v>
+        <v>9826.5625</v>
       </c>
     </row>
     <row r="430">
@@ -3857,7 +3857,7 @@
         <v>326.3566026187934</v>
       </c>
       <c r="B430" t="n">
-        <v>122.9808654785156</v>
+        <v>105.9633178710938</v>
       </c>
     </row>
     <row r="431">
@@ -3865,7 +3865,7 @@
         <v>220.1145065938077</v>
       </c>
       <c r="B431" t="n">
-        <v>14887.7041015625</v>
+        <v>15058.64453125</v>
       </c>
     </row>
     <row r="432">
@@ -3873,7 +3873,7 @@
         <v>283.9209321863163</v>
       </c>
       <c r="B432" t="n">
-        <v>1577.616333007812</v>
+        <v>1362.427368164062</v>
       </c>
     </row>
     <row r="433">
@@ -3881,7 +3881,7 @@
         <v>350.1674479414448</v>
       </c>
       <c r="B433" t="n">
-        <v>24.54349136352539</v>
+        <v>27.83650207519531</v>
       </c>
     </row>
     <row r="434">
@@ -3889,7 +3889,7 @@
         <v>372.3929102090453</v>
       </c>
       <c r="B434" t="n">
-        <v>7.169820308685303</v>
+        <v>9.259944915771484</v>
       </c>
     </row>
     <row r="435">
@@ -3897,7 +3897,7 @@
         <v>223.9321077086611</v>
       </c>
       <c r="B435" t="n">
-        <v>13055.3623046875</v>
+        <v>13020.4619140625</v>
       </c>
     </row>
     <row r="436">
@@ -3905,7 +3905,7 @@
         <v>197.4678352720058</v>
       </c>
       <c r="B436" t="n">
-        <v>45344.60546875</v>
+        <v>36996.61328125</v>
       </c>
     </row>
     <row r="437">
@@ -3913,7 +3913,7 @@
         <v>294.2613201930413</v>
       </c>
       <c r="B437" t="n">
-        <v>971.28173828125</v>
+        <v>789.4290771484375</v>
       </c>
     </row>
     <row r="438">
@@ -3921,7 +3921,7 @@
         <v>183.913391406862</v>
       </c>
       <c r="B438" t="n">
-        <v>78683.390625</v>
+        <v>65125.30859375</v>
       </c>
     </row>
     <row r="439">
@@ -3929,7 +3929,7 @@
         <v>299.2457253743247</v>
       </c>
       <c r="B439" t="n">
-        <v>766.7302856445312</v>
+        <v>576.4266967773438</v>
       </c>
     </row>
     <row r="440">
@@ -3937,7 +3937,7 @@
         <v>218.5327154449164</v>
       </c>
       <c r="B440" t="n">
-        <v>15720.3134765625</v>
+        <v>15993.947265625</v>
       </c>
     </row>
     <row r="441">
@@ -3945,7 +3945,7 @@
         <v>348.1248306182958</v>
       </c>
       <c r="B441" t="n">
-        <v>27.86907768249512</v>
+        <v>31.30109786987305</v>
       </c>
     </row>
     <row r="442">
@@ -3953,7 +3953,7 @@
         <v>249.9141929955494</v>
       </c>
       <c r="B442" t="n">
-        <v>5236.6064453125</v>
+        <v>4380.669921875</v>
       </c>
     </row>
     <row r="443">
@@ -3961,7 +3961,7 @@
         <v>176.0525568178008</v>
       </c>
       <c r="B443" t="n">
-        <v>99386.265625</v>
+        <v>87194.921875</v>
       </c>
     </row>
     <row r="444">
@@ -3969,7 +3969,7 @@
         <v>208.430631473896</v>
       </c>
       <c r="B444" t="n">
-        <v>28611.46484375</v>
+        <v>23501.064453125</v>
       </c>
     </row>
     <row r="445">
@@ -3977,7 +3977,7 @@
         <v>328.8052937232158</v>
       </c>
       <c r="B445" t="n">
-        <v>99.39373779296875</v>
+        <v>88.9110107421875</v>
       </c>
     </row>
     <row r="446">
@@ -3985,7 +3985,7 @@
         <v>312.7509565980503</v>
       </c>
       <c r="B446" t="n">
-        <v>401.7745666503906</v>
+        <v>246.9004364013672</v>
       </c>
     </row>
     <row r="447">
@@ -3993,7 +3993,7 @@
         <v>115.0562781411034</v>
       </c>
       <c r="B447" t="n">
-        <v>1358493.625</v>
+        <v>1253138.625</v>
       </c>
     </row>
     <row r="448">
@@ -4001,7 +4001,7 @@
         <v>375.1220461372748</v>
       </c>
       <c r="B448" t="n">
-        <v>6.405162811279297</v>
+        <v>8.942108154296875</v>
       </c>
     </row>
     <row r="449">
@@ -4009,7 +4009,7 @@
         <v>99.1076033242944</v>
       </c>
       <c r="B449" t="n">
-        <v>4392609.5</v>
+        <v>5897624</v>
       </c>
     </row>
     <row r="450">
@@ -4017,7 +4017,7 @@
         <v>368.4471019737171</v>
       </c>
       <c r="B450" t="n">
-        <v>8.842477798461914</v>
+        <v>10.45206260681152</v>
       </c>
     </row>
     <row r="451">
@@ -4025,7 +4025,7 @@
         <v>233.3284603912197</v>
       </c>
       <c r="B451" t="n">
-        <v>9391.6953125</v>
+        <v>8787.759765625</v>
       </c>
     </row>
     <row r="452">
@@ -4033,7 +4033,7 @@
         <v>244.7873032485755</v>
       </c>
       <c r="B452" t="n">
-        <v>6272.931640625</v>
+        <v>5431.86962890625</v>
       </c>
     </row>
     <row r="453">
@@ -4041,7 +4041,7 @@
         <v>323.8754825013891</v>
       </c>
       <c r="B453" t="n">
-        <v>154.3139038085938</v>
+        <v>123.675178527832</v>
       </c>
     </row>
     <row r="454">
@@ -4049,7 +4049,7 @@
         <v>164.5518267434068</v>
       </c>
       <c r="B454" t="n">
-        <v>128707.5078125</v>
+        <v>133634.4375</v>
       </c>
     </row>
     <row r="455">
@@ -4057,7 +4057,7 @@
         <v>281.2448995607493</v>
       </c>
       <c r="B455" t="n">
-        <v>1785.926025390625</v>
+        <v>1487.255004882812</v>
       </c>
     </row>
     <row r="456">
@@ -4065,7 +4065,7 @@
         <v>345.1135621609184</v>
       </c>
       <c r="B456" t="n">
-        <v>34.076171875</v>
+        <v>36.69743728637695</v>
       </c>
     </row>
     <row r="457">
@@ -4073,7 +4073,7 @@
         <v>129.6684372032138</v>
       </c>
       <c r="B457" t="n">
-        <v>474203.0625</v>
+        <v>567776.0625</v>
       </c>
     </row>
     <row r="458">
@@ -4081,7 +4081,7 @@
         <v>264.3931473913945</v>
       </c>
       <c r="B458" t="n">
-        <v>3152.107177734375</v>
+        <v>2613.000732421875</v>
       </c>
     </row>
     <row r="459">
@@ -4089,7 +4089,7 @@
         <v>380.4117535705119</v>
       </c>
       <c r="B459" t="n">
-        <v>5.378019332885742</v>
+        <v>8.580101013183594</v>
       </c>
     </row>
     <row r="460">
@@ -4097,7 +4097,7 @@
         <v>146.0748099229377</v>
       </c>
       <c r="B460" t="n">
-        <v>197907.625</v>
+        <v>271277.9375</v>
       </c>
     </row>
     <row r="461">
@@ -4105,7 +4105,7 @@
         <v>160.6905510274532</v>
       </c>
       <c r="B461" t="n">
-        <v>140694.546875</v>
+        <v>154231.90625</v>
       </c>
     </row>
     <row r="462">
@@ -4113,7 +4113,7 @@
         <v>202.7063995378984</v>
       </c>
       <c r="B462" t="n">
-        <v>36520.94140625</v>
+        <v>29227.470703125</v>
       </c>
     </row>
     <row r="463">
@@ -4121,7 +4121,7 @@
         <v>275.9915240094757</v>
       </c>
       <c r="B463" t="n">
-        <v>2149.653076171875</v>
+        <v>1766.547729492188</v>
       </c>
     </row>
     <row r="464">
@@ -4129,7 +4129,7 @@
         <v>194.2811031504395</v>
       </c>
       <c r="B464" t="n">
-        <v>51953.953125</v>
+        <v>43133.59765625</v>
       </c>
     </row>
     <row r="465">
@@ -4137,7 +4137,7 @@
         <v>278.0451733376491</v>
       </c>
       <c r="B465" t="n">
-        <v>2014.185913085938</v>
+        <v>1651.610595703125</v>
       </c>
     </row>
     <row r="466">
@@ -4145,7 +4145,7 @@
         <v>135.9100035578915</v>
       </c>
       <c r="B466" t="n">
-        <v>314035.5</v>
+        <v>428694.84375</v>
       </c>
     </row>
     <row r="467">
@@ -4153,7 +4153,7 @@
         <v>363.0051467046507</v>
       </c>
       <c r="B467" t="n">
-        <v>11.80122470855713</v>
+        <v>12.86511325836182</v>
       </c>
     </row>
     <row r="468">
@@ -4161,7 +4161,7 @@
         <v>153.580328241885</v>
       </c>
       <c r="B468" t="n">
-        <v>166098.609375</v>
+        <v>200823.03125</v>
       </c>
     </row>
     <row r="469">
@@ -4169,7 +4169,7 @@
         <v>186.3156885245247</v>
       </c>
       <c r="B469" t="n">
-        <v>72780.8515625</v>
+        <v>59568.6484375</v>
       </c>
     </row>
     <row r="470">
@@ -4177,7 +4177,7 @@
         <v>335.4410659474784</v>
       </c>
       <c r="B470" t="n">
-        <v>63.03043365478516</v>
+        <v>60.35936737060547</v>
       </c>
     </row>
     <row r="471">
@@ -4185,7 +4185,7 @@
         <v>191.746442803585</v>
       </c>
       <c r="B471" t="n">
-        <v>58432.375</v>
+        <v>48689.16015625</v>
       </c>
     </row>
     <row r="472">
@@ -4193,7 +4193,7 @@
         <v>119.6812373581288</v>
       </c>
       <c r="B472" t="n">
-        <v>968561.875</v>
+        <v>890096.625</v>
       </c>
     </row>
     <row r="473">
@@ -4201,7 +4201,7 @@
         <v>226.729836780189</v>
       </c>
       <c r="B473" t="n">
-        <v>11848.8603515625</v>
+        <v>11631.89453125</v>
       </c>
     </row>
     <row r="474">
@@ -4209,7 +4209,7 @@
         <v>146.907772534171</v>
       </c>
       <c r="B474" t="n">
-        <v>194096.734375</v>
+        <v>261294.046875</v>
       </c>
     </row>
     <row r="475">
@@ -4217,7 +4217,7 @@
         <v>169.0686067385773</v>
       </c>
       <c r="B475" t="n">
-        <v>116281.0234375</v>
+        <v>113004.0234375</v>
       </c>
     </row>
     <row r="476">
@@ -4225,7 +4225,7 @@
         <v>128.8611277501225</v>
       </c>
       <c r="B476" t="n">
-        <v>502158.09375</v>
+        <v>588790</v>
       </c>
     </row>
     <row r="477">
@@ -4233,7 +4233,7 @@
         <v>180.5644198222799</v>
       </c>
       <c r="B477" t="n">
-        <v>89377.78125</v>
+        <v>73747.2578125</v>
       </c>
     </row>
     <row r="478">
@@ -4241,7 +4241,7 @@
         <v>311.4091895297078</v>
       </c>
       <c r="B478" t="n">
-        <v>428.4162902832031</v>
+        <v>268.4142761230469</v>
       </c>
     </row>
     <row r="479">
@@ -4249,7 +4249,7 @@
         <v>316.154842349401</v>
       </c>
       <c r="B479" t="n">
-        <v>314.410888671875</v>
+        <v>199.7437591552734</v>
       </c>
     </row>
     <row r="480">
@@ -4257,7 +4257,7 @@
         <v>287.3753863466005</v>
       </c>
       <c r="B480" t="n">
-        <v>1346.595581054688</v>
+        <v>1201.985717773438</v>
       </c>
     </row>
     <row r="481">
@@ -4265,7 +4265,7 @@
         <v>120.9338677049957</v>
       </c>
       <c r="B481" t="n">
-        <v>885525.875</v>
+        <v>841292.0625</v>
       </c>
     </row>
     <row r="482">
@@ -4273,7 +4273,7 @@
         <v>156.1830822186153</v>
       </c>
       <c r="B482" t="n">
-        <v>156306.78125</v>
+        <v>182325.5625</v>
       </c>
     </row>
     <row r="483">
@@ -4281,7 +4281,7 @@
         <v>267.4543758483738</v>
       </c>
       <c r="B483" t="n">
-        <v>2835.213134765625</v>
+        <v>2354.017578125</v>
       </c>
     </row>
     <row r="484">
@@ -4289,7 +4289,7 @@
         <v>161.5645686424038</v>
       </c>
       <c r="B484" t="n">
-        <v>137853.15625</v>
+        <v>149307.5625</v>
       </c>
     </row>
     <row r="485">
@@ -4297,7 +4297,7 @@
         <v>215.7985868942134</v>
       </c>
       <c r="B485" t="n">
-        <v>17270.794921875</v>
+        <v>17749.6328125</v>
       </c>
     </row>
     <row r="486">
@@ -4305,7 +4305,7 @@
         <v>332.5561904549953</v>
       </c>
       <c r="B486" t="n">
-        <v>75.12224578857422</v>
+        <v>70.64445495605469</v>
       </c>
     </row>
     <row r="487">
@@ -4313,7 +4313,7 @@
         <v>108.4096437362936</v>
       </c>
       <c r="B487" t="n">
-        <v>2215442.25</v>
+        <v>2389674.75</v>
       </c>
     </row>
     <row r="488">
@@ -4321,7 +4321,7 @@
         <v>234.5424277411062</v>
       </c>
       <c r="B488" t="n">
-        <v>8998.611328125</v>
+        <v>8348.4033203125</v>
       </c>
     </row>
     <row r="489">
@@ -4329,7 +4329,7 @@
         <v>290.5605904463613</v>
       </c>
       <c r="B489" t="n">
-        <v>1157.385375976562</v>
+        <v>992.9971313476562</v>
       </c>
     </row>
     <row r="490">
@@ -4337,7 +4337,7 @@
         <v>384.5053089813795</v>
       </c>
       <c r="B490" t="n">
-        <v>4.724777698516846</v>
+        <v>8.311628341674805</v>
       </c>
     </row>
     <row r="491">
@@ -4345,7 +4345,7 @@
         <v>336.9818847731192</v>
       </c>
       <c r="B491" t="n">
-        <v>57.39080810546875</v>
+        <v>55.75914001464844</v>
       </c>
     </row>
     <row r="492">
@@ -4353,7 +4353,7 @@
         <v>306.0031988582454</v>
       </c>
       <c r="B492" t="n">
-        <v>554.8955078125</v>
+        <v>376.8229064941406</v>
       </c>
     </row>
     <row r="493">
@@ -4361,7 +4361,7 @@
         <v>109.5547807176809</v>
       </c>
       <c r="B493" t="n">
-        <v>2036413.75</v>
+        <v>2138159</v>
       </c>
     </row>
     <row r="494">
@@ -4369,7 +4369,7 @@
         <v>133.5499762679973</v>
       </c>
       <c r="B494" t="n">
-        <v>366992.125</v>
+        <v>476747.53125</v>
       </c>
     </row>
     <row r="495">
@@ -4377,7 +4377,7 @@
         <v>247.1689956482448</v>
       </c>
       <c r="B495" t="n">
-        <v>5768.1923828125</v>
+        <v>4915.3701171875</v>
       </c>
     </row>
     <row r="496">
@@ -4385,7 +4385,7 @@
         <v>189.2312300532594</v>
       </c>
       <c r="B496" t="n">
-        <v>65659.484375</v>
+        <v>53457.74609375</v>
       </c>
     </row>
     <row r="497">
@@ -4393,7 +4393,7 @@
         <v>101.0214962508455</v>
       </c>
       <c r="B497" t="n">
-        <v>3815584.5</v>
+        <v>4897262</v>
       </c>
     </row>
     <row r="498">
@@ -4401,7 +4401,7 @@
         <v>174.5135954595672</v>
       </c>
       <c r="B498" t="n">
-        <v>102884.8671875</v>
+        <v>92321.71875</v>
       </c>
     </row>
     <row r="499">
@@ -4409,7 +4409,7 @@
         <v>297.4659135308101</v>
       </c>
       <c r="B499" t="n">
-        <v>834.3624877929688</v>
+        <v>644.9254760742188</v>
       </c>
     </row>
     <row r="500">
@@ -4417,7 +4417,7 @@
         <v>259.5677655513734</v>
       </c>
       <c r="B500" t="n">
-        <v>3728.708984375</v>
+        <v>3081.645263671875</v>
       </c>
     </row>
     <row r="501">
@@ -4425,7 +4425,7 @@
         <v>94.24010876421259</v>
       </c>
       <c r="B501" t="n">
-        <v>6284506.5</v>
+        <v>9460747</v>
       </c>
     </row>
     <row r="502">
@@ -4433,7 +4433,7 @@
         <v>133.0385461033778</v>
       </c>
       <c r="B502" t="n">
-        <v>1997.205078125</v>
+        <v>2075.6513671875</v>
       </c>
     </row>
     <row r="503">
@@ -4441,7 +4441,7 @@
         <v>155.5158483817144</v>
       </c>
       <c r="B503" t="n">
-        <v>198.4052124023438</v>
+        <v>262.2675476074219</v>
       </c>
     </row>
     <row r="504">
@@ -4449,7 +4449,7 @@
         <v>174.7906599260126</v>
       </c>
       <c r="B504" t="n">
-        <v>20.74684143066406</v>
+        <v>43.7078742980957</v>
       </c>
     </row>
     <row r="505">
@@ -4457,7 +4457,7 @@
         <v>141.2651801635925</v>
       </c>
       <c r="B505" t="n">
-        <v>875.4957885742188</v>
+        <v>999.2322998046875</v>
       </c>
     </row>
     <row r="506">
@@ -4465,7 +4465,7 @@
         <v>115.2285712957623</v>
       </c>
       <c r="B506" t="n">
-        <v>12185.4921875</v>
+        <v>10338.095703125</v>
       </c>
     </row>
     <row r="507">
@@ -4473,7 +4473,7 @@
         <v>178.1421599623849</v>
       </c>
       <c r="B507" t="n">
-        <v>15.65546226501465</v>
+        <v>33.99728012084961</v>
       </c>
     </row>
     <row r="508">
@@ -4481,7 +4481,7 @@
         <v>81.90282048825244</v>
       </c>
       <c r="B508" t="n">
-        <v>573952.375</v>
+        <v>504552.21875</v>
       </c>
     </row>
     <row r="509">
@@ -4489,7 +4489,7 @@
         <v>73.73624588300241</v>
       </c>
       <c r="B509" t="n">
-        <v>2051636.5</v>
+        <v>2451460</v>
       </c>
     </row>
     <row r="510">
@@ -4497,7 +4497,7 @@
         <v>88.45129328280109</v>
       </c>
       <c r="B510" t="n">
-        <v>206664.625</v>
+        <v>142041.046875</v>
       </c>
     </row>
     <row r="511">
@@ -4505,7 +4505,7 @@
         <v>140.3897861517161</v>
       </c>
       <c r="B511" t="n">
-        <v>955.8003540039062</v>
+        <v>1080.0673828125</v>
       </c>
     </row>
     <row r="512">
@@ -4513,7 +4513,7 @@
         <v>169.5451632314977</v>
       </c>
       <c r="B512" t="n">
-        <v>33.93331527709961</v>
+        <v>70.75759124755859</v>
       </c>
     </row>
     <row r="513">
@@ -4521,7 +4521,7 @@
         <v>92.17290654040066</v>
       </c>
       <c r="B513" t="n">
-        <v>130595.484375</v>
+        <v>88224.6640625</v>
       </c>
     </row>
     <row r="514">
@@ -4529,7 +4529,7 @@
         <v>152.9525200550215</v>
       </c>
       <c r="B514" t="n">
-        <v>272.2733764648438</v>
+        <v>334.3241577148438</v>
       </c>
     </row>
     <row r="515">
@@ -4537,7 +4537,7 @@
         <v>182.9699195413577</v>
       </c>
       <c r="B515" t="n">
-        <v>11.0269079208374</v>
+        <v>25.74192047119141</v>
       </c>
     </row>
     <row r="516">
@@ -4545,7 +4545,7 @@
         <v>100.8724080973816</v>
       </c>
       <c r="B516" t="n">
-        <v>53343.296875</v>
+        <v>39365.921875</v>
       </c>
     </row>
     <row r="517">
@@ -4553,7 +4553,7 @@
         <v>160.4119393591353</v>
       </c>
       <c r="B517" t="n">
-        <v>108.9051284790039</v>
+        <v>165.4351196289062</v>
       </c>
     </row>
     <row r="518">
@@ -4561,7 +4561,7 @@
         <v>128.6435115099901</v>
       </c>
       <c r="B518" t="n">
-        <v>3102.934814453125</v>
+        <v>3064.80419921875</v>
       </c>
     </row>
     <row r="519">
@@ -4569,7 +4569,7 @@
         <v>137.3516351335739</v>
       </c>
       <c r="B519" t="n">
-        <v>1296.104125976562</v>
+        <v>1414.819580078125</v>
       </c>
     </row>
     <row r="520">
@@ -4577,7 +4577,7 @@
         <v>173.664145010196</v>
       </c>
       <c r="B520" t="n">
-        <v>22.81749153137207</v>
+        <v>48.44565200805664</v>
       </c>
     </row>
     <row r="521">
@@ -4585,7 +4585,7 @@
         <v>112.2787065663861</v>
       </c>
       <c r="B521" t="n">
-        <v>16504.513671875</v>
+        <v>13575.5576171875</v>
       </c>
     </row>
     <row r="522">
@@ -4593,7 +4593,7 @@
         <v>77.25631163730485</v>
       </c>
       <c r="B522" t="n">
-        <v>1184791.125</v>
+        <v>1240256.75</v>
       </c>
     </row>
     <row r="523">
@@ -4601,7 +4601,7 @@
         <v>176.5391649277803</v>
       </c>
       <c r="B523" t="n">
-        <v>17.89880561828613</v>
+        <v>37.95672225952148</v>
       </c>
     </row>
     <row r="524">
@@ -4609,7 +4609,7 @@
         <v>133.972344962729</v>
       </c>
       <c r="B524" t="n">
-        <v>1818.72705078125</v>
+        <v>1910.368774414062</v>
       </c>
     </row>
     <row r="525">
@@ -4617,7 +4617,7 @@
         <v>116.624816214143</v>
       </c>
       <c r="B525" t="n">
-        <v>10555.50390625</v>
+        <v>9089.9482421875</v>
       </c>
     </row>
     <row r="526">
@@ -4625,7 +4625,7 @@
         <v>167.9088251316061</v>
       </c>
       <c r="B526" t="n">
-        <v>42.09847640991211</v>
+        <v>82.24904632568359</v>
       </c>
     </row>
     <row r="527">
@@ -4633,7 +4633,7 @@
         <v>89.53647113825244</v>
       </c>
       <c r="B527" t="n">
-        <v>174606.984375</v>
+        <v>115545.1640625</v>
       </c>
     </row>
     <row r="528">
@@ -4641,7 +4641,7 @@
         <v>127.5831402057291</v>
       </c>
       <c r="B528" t="n">
-        <v>3450.949462890625</v>
+        <v>3366.292236328125</v>
       </c>
     </row>
     <row r="529">
@@ -4649,7 +4649,7 @@
         <v>124.5872449002589</v>
       </c>
       <c r="B529" t="n">
-        <v>4659.86767578125</v>
+        <v>4414.15771484375</v>
       </c>
     </row>
     <row r="530">
@@ -4657,7 +4657,7 @@
         <v>162.8217722745607</v>
       </c>
       <c r="B530" t="n">
-        <v>81.23932647705078</v>
+        <v>132.1062927246094</v>
       </c>
     </row>
     <row r="531">
@@ -4665,7 +4665,7 @@
         <v>120.3565706925605</v>
       </c>
       <c r="B531" t="n">
-        <v>7191.083984375</v>
+        <v>6479.373046875</v>
       </c>
     </row>
     <row r="532">
@@ -4673,7 +4673,7 @@
         <v>145.8601406181346</v>
       </c>
       <c r="B532" t="n">
-        <v>552.3316040039062</v>
+        <v>654.4302368164062</v>
       </c>
     </row>
     <row r="533">
@@ -4681,7 +4681,7 @@
         <v>172.339019997407</v>
       </c>
       <c r="B533" t="n">
-        <v>25.54669189453125</v>
+        <v>54.72459411621094</v>
       </c>
     </row>
     <row r="534">
@@ -4689,7 +4689,7 @@
         <v>181.2225865944443</v>
       </c>
       <c r="B534" t="n">
-        <v>12.16575050354004</v>
+        <v>28.32556533813477</v>
       </c>
     </row>
     <row r="535">
@@ -4697,7 +4697,7 @@
         <v>121.8824743312066</v>
       </c>
       <c r="B535" t="n">
-        <v>6146.64453125</v>
+        <v>5641.755859375</v>
       </c>
     </row>
     <row r="536">
@@ -4705,7 +4705,7 @@
         <v>111.3046459016994</v>
       </c>
       <c r="B536" t="n">
-        <v>18243.58984375</v>
+        <v>14853.4326171875</v>
       </c>
     </row>
     <row r="537">
@@ -4713,7 +4713,7 @@
         <v>149.9932166545712</v>
       </c>
       <c r="B537" t="n">
-        <v>364.968505859375</v>
+        <v>442.4643859863281</v>
       </c>
     </row>
     <row r="538">
@@ -4721,7 +4721,7 @@
         <v>105.8869046051621</v>
       </c>
       <c r="B538" t="n">
-        <v>31849.40625</v>
+        <v>24723.138671875</v>
       </c>
     </row>
     <row r="539">
@@ -4729,7 +4729,7 @@
         <v>151.9854944682524</v>
       </c>
       <c r="B539" t="n">
-        <v>299.5333557128906</v>
+        <v>366.38720703125</v>
       </c>
     </row>
     <row r="540">
@@ -4737,7 +4737,7 @@
         <v>119.7243252596156</v>
       </c>
       <c r="B540" t="n">
-        <v>7674.2255859375</v>
+        <v>6861.892578125</v>
       </c>
     </row>
     <row r="541">
@@ -4745,7 +4745,7 @@
         <v>171.5225813198228</v>
       </c>
       <c r="B541" t="n">
-        <v>27.4507999420166</v>
+        <v>58.9918327331543</v>
       </c>
     </row>
     <row r="542">
@@ -4753,7 +4753,7 @@
         <v>132.2675714867537</v>
       </c>
       <c r="B542" t="n">
-        <v>2157.6904296875</v>
+        <v>2222.843017578125</v>
       </c>
     </row>
     <row r="543">
@@ -4761,7 +4761,7 @@
         <v>102.7449115730524</v>
       </c>
       <c r="B543" t="n">
-        <v>43998.93359375</v>
+        <v>33089.125</v>
       </c>
     </row>
     <row r="544">
@@ -4769,7 +4769,7 @@
         <v>115.6864998751579</v>
       </c>
       <c r="B544" t="n">
-        <v>11624.923828125</v>
+        <v>9909.9853515625</v>
       </c>
     </row>
     <row r="545">
@@ -4777,7 +4777,7 @@
         <v>163.8005195437871</v>
       </c>
       <c r="B545" t="n">
-        <v>72.16514587402344</v>
+        <v>120.5712509155273</v>
       </c>
     </row>
     <row r="546">
@@ -4785,7 +4785,7 @@
         <v>157.3835653627889</v>
       </c>
       <c r="B546" t="n">
-        <v>157.5769195556641</v>
+        <v>219.9811859130859</v>
       </c>
     </row>
     <row r="547">
@@ -4793,7 +4793,7 @@
         <v>78.36456360675609</v>
       </c>
       <c r="B547" t="n">
-        <v>996703.875</v>
+        <v>1000800.75</v>
       </c>
     </row>
     <row r="548">
@@ -4801,7 +4801,7 @@
         <v>182.3134282821844</v>
       </c>
       <c r="B548" t="n">
-        <v>11.44577598571777</v>
+        <v>26.67934989929199</v>
       </c>
     </row>
     <row r="549">
@@ -4809,7 +4809,7 @@
         <v>71.98984288492201</v>
       </c>
       <c r="B549" t="n">
-        <v>2694049.75</v>
+        <v>3437437.75</v>
       </c>
     </row>
     <row r="550">
@@ -4817,7 +4817,7 @@
         <v>179.6454382851929</v>
       </c>
       <c r="B550" t="n">
-        <v>13.7647008895874</v>
+        <v>30.8869686126709</v>
       </c>
     </row>
     <row r="551">
@@ -4825,7 +4825,7 @@
         <v>125.6382173533189</v>
       </c>
       <c r="B551" t="n">
-        <v>4193.88720703125</v>
+        <v>4012.72216796875</v>
       </c>
     </row>
     <row r="552">
@@ -4833,7 +4833,7 @@
         <v>130.2183422759262</v>
       </c>
       <c r="B552" t="n">
-        <v>2649.773193359375</v>
+        <v>2666.14501953125</v>
       </c>
     </row>
     <row r="553">
@@ -4841,7 +4841,7 @@
         <v>161.8300630568702</v>
       </c>
       <c r="B553" t="n">
-        <v>91.63497924804688</v>
+        <v>144.9203033447266</v>
       </c>
     </row>
     <row r="554">
@@ -4849,7 +4849,7 @@
         <v>98.1480442368276</v>
       </c>
       <c r="B554" t="n">
-        <v>70593.9921875</v>
+        <v>50684.53515625</v>
       </c>
     </row>
     <row r="555">
@@ -4857,7 +4857,7 @@
         <v>144.7905244383296</v>
       </c>
       <c r="B555" t="n">
-        <v>614.8487548828125</v>
+        <v>724.1940307617188</v>
       </c>
     </row>
     <row r="556">
@@ -4865,7 +4865,7 @@
         <v>170.3189706339985</v>
       </c>
       <c r="B556" t="n">
-        <v>31.23179626464844</v>
+        <v>65.89712524414062</v>
       </c>
     </row>
     <row r="557">
@@ -4873,7 +4873,7 @@
         <v>84.20507601508473</v>
       </c>
       <c r="B557" t="n">
-        <v>400788.96875</v>
+        <v>323123.0625</v>
       </c>
     </row>
     <row r="558">
@@ -4881,7 +4881,7 @@
         <v>138.0548416943327</v>
       </c>
       <c r="B558" t="n">
-        <v>1207.883544921875</v>
+        <v>1329.114990234375</v>
       </c>
     </row>
     <row r="559">
@@ -4889,7 +4889,7 @@
         <v>184.4277360835798</v>
       </c>
       <c r="B559" t="n">
-        <v>10.12639617919922</v>
+        <v>24.02238845825195</v>
       </c>
     </row>
     <row r="560">
@@ -4897,7 +4897,7 @@
         <v>90.76273960455923</v>
       </c>
       <c r="B560" t="n">
-        <v>151094.390625</v>
+        <v>100554.2421875</v>
       </c>
     </row>
     <row r="561">
@@ -4905,7 +4905,7 @@
         <v>96.60468376318738</v>
       </c>
       <c r="B561" t="n">
-        <v>82737.640625</v>
+        <v>58485.83984375</v>
       </c>
     </row>
     <row r="562">
@@ -4913,7 +4913,7 @@
         <v>113.3985116655965</v>
       </c>
       <c r="B562" t="n">
-        <v>14709.0751953125</v>
+        <v>12241.734375</v>
       </c>
     </row>
     <row r="563">
@@ -4921,7 +4921,7 @@
         <v>142.6907385707925</v>
       </c>
       <c r="B563" t="n">
-        <v>758.906005859375</v>
+        <v>880.3414306640625</v>
       </c>
     </row>
     <row r="564">
@@ -4929,7 +4929,7 @@
         <v>110.0309019998629</v>
       </c>
       <c r="B564" t="n">
-        <v>20797.142578125</v>
+        <v>16733.41796875</v>
       </c>
     </row>
     <row r="565">
@@ -4937,7 +4937,7 @@
         <v>143.5115867652701</v>
       </c>
       <c r="B565" t="n">
-        <v>698.95703125</v>
+        <v>817.4367065429688</v>
       </c>
     </row>
     <row r="566">
@@ -4945,7 +4945,7 @@
         <v>86.69984393999917</v>
       </c>
       <c r="B566" t="n">
-        <v>271590.25</v>
+        <v>199364.703125</v>
       </c>
     </row>
     <row r="567">
@@ -4953,7 +4953,7 @@
         <v>177.4702766859076</v>
       </c>
       <c r="B567" t="n">
-        <v>16.54525947570801</v>
+        <v>35.54868698120117</v>
       </c>
     </row>
     <row r="568">
@@ -4961,7 +4961,7 @@
         <v>93.76271193489177</v>
       </c>
       <c r="B568" t="n">
-        <v>110826.4453125</v>
+        <v>76127.6953125</v>
       </c>
     </row>
     <row r="569">
@@ -4969,7 +4969,7 @@
         <v>106.8471080949108</v>
       </c>
       <c r="B569" t="n">
-        <v>28854.412109375</v>
+        <v>22590.046875</v>
       </c>
     </row>
     <row r="570">
@@ -4977,7 +4977,7 @@
         <v>166.4528524297015</v>
       </c>
       <c r="B570" t="n">
-        <v>51.06191635131836</v>
+        <v>94.12700653076172</v>
       </c>
     </row>
     <row r="571">
@@ -4985,7 +4985,7 @@
         <v>109.0177926336304</v>
       </c>
       <c r="B571" t="n">
-        <v>23081.072265625</v>
+        <v>18410.140625</v>
       </c>
     </row>
     <row r="572">
@@ -4993,7 +4993,7 @@
         <v>80.21317007074495</v>
       </c>
       <c r="B572" t="n">
-        <v>747029.5</v>
+        <v>699754.0625</v>
       </c>
     </row>
     <row r="573">
@@ -5001,7 +5001,7 @@
         <v>123.0007328505634</v>
       </c>
       <c r="B573" t="n">
-        <v>5478.84423828125</v>
+        <v>5097.4794921875</v>
       </c>
     </row>
     <row r="574">
@@ -5009,7 +5009,7 @@
         <v>91.09567660900211</v>
       </c>
       <c r="B574" t="n">
-        <v>145982.0625</v>
+        <v>97496.25</v>
       </c>
     </row>
     <row r="575">
@@ -5017,7 +5017,7 @@
         <v>99.95341122574084</v>
       </c>
       <c r="B575" t="n">
-        <v>58631.08203125</v>
+        <v>42869.0625</v>
       </c>
     </row>
     <row r="576">
@@ -5025,7 +5025,7 @@
         <v>83.88239263488752</v>
       </c>
       <c r="B576" t="n">
-        <v>421478.03125</v>
+        <v>343950.28125</v>
       </c>
     </row>
     <row r="577">
@@ -5033,7 +5033,7 @@
         <v>104.5483132298732</v>
       </c>
       <c r="B577" t="n">
-        <v>36550.265625</v>
+        <v>27991.935546875</v>
       </c>
     </row>
     <row r="578">
@@ -5041,7 +5041,7 @@
         <v>156.8472580875649</v>
       </c>
       <c r="B578" t="n">
-        <v>168.3039245605469</v>
+        <v>231.3671417236328</v>
       </c>
     </row>
     <row r="579">
@@ -5049,7 +5049,7 @@
         <v>158.7441060524155</v>
       </c>
       <c r="B579" t="n">
-        <v>133.4781188964844</v>
+        <v>193.5464172363281</v>
       </c>
     </row>
     <row r="580">
@@ -5057,7 +5057,7 @@
         <v>147.2408936130467</v>
       </c>
       <c r="B580" t="n">
-        <v>480.9329833984375</v>
+        <v>574.2161254882812</v>
       </c>
     </row>
     <row r="581">
@@ -5065,7 +5065,7 @@
         <v>80.71384920055922</v>
       </c>
       <c r="B581" t="n">
-        <v>690907.375</v>
+        <v>635120.25</v>
       </c>
     </row>
     <row r="582">
@@ -5073,7 +5073,7 @@
         <v>94.80303847611714</v>
       </c>
       <c r="B582" t="n">
-        <v>99580.9140625</v>
+        <v>69124.578125</v>
       </c>
     </row>
     <row r="583">
@@ -5081,7 +5081,7 @@
         <v>139.2784215028825</v>
       </c>
       <c r="B583" t="n">
-        <v>1068.446533203125</v>
+        <v>1192.179443359375</v>
       </c>
     </row>
     <row r="584">
@@ -5089,7 +5089,7 @@
         <v>96.95403054373628</v>
       </c>
       <c r="B584" t="n">
-        <v>79817.9453125</v>
+        <v>56620.91796875</v>
       </c>
     </row>
     <row r="585">
@@ -5097,7 +5097,7 @@
         <v>118.6314880095918</v>
       </c>
       <c r="B585" t="n">
-        <v>8587.126953125</v>
+        <v>7577.05419921875</v>
       </c>
     </row>
     <row r="586">
@@ -5105,7 +5105,7 @@
         <v>165.2997612924705</v>
       </c>
       <c r="B586" t="n">
-        <v>59.34841537475586</v>
+        <v>104.8243713378906</v>
       </c>
     </row>
     <row r="587">
@@ -5113,7 +5113,7 @@
         <v>75.70788908316869</v>
       </c>
       <c r="B587" t="n">
-        <v>1508470.75</v>
+        <v>1673701.875</v>
       </c>
     </row>
     <row r="588">
@@ -5121,7 +5121,7 @@
         <v>126.1234427974289</v>
       </c>
       <c r="B588" t="n">
-        <v>3994.7626953125</v>
+        <v>3839.92041015625</v>
       </c>
     </row>
     <row r="589">
@@ -5129,7 +5129,7 @@
         <v>148.5140267611761</v>
       </c>
       <c r="B589" t="n">
-        <v>423.30712890625</v>
+        <v>508.9960327148438</v>
       </c>
     </row>
     <row r="590">
@@ -5137,7 +5137,7 @@
         <v>186.0639392668142</v>
       </c>
       <c r="B590" t="n">
-        <v>9.400259017944336</v>
+        <v>22.51187324523926</v>
       </c>
     </row>
     <row r="591">
@@ -5145,7 +5145,7 @@
         <v>167.0687211341065</v>
       </c>
       <c r="B591" t="n">
-        <v>47.07228088378906</v>
+        <v>88.86806488037109</v>
       </c>
     </row>
     <row r="592">
@@ -5153,7 +5153,7 @@
         <v>154.6864716177641</v>
       </c>
       <c r="B592" t="n">
-        <v>219.8202667236328</v>
+        <v>283.6966247558594</v>
       </c>
     </row>
     <row r="593">
@@ -5161,7 +5161,7 @@
         <v>76.16560287622281</v>
       </c>
       <c r="B593" t="n">
-        <v>1404527</v>
+        <v>1531796.875</v>
       </c>
     </row>
     <row r="594">
@@ -5169,7 +5169,7 @@
         <v>85.75653579422607</v>
       </c>
       <c r="B594" t="n">
-        <v>314641.5625</v>
+        <v>239302.25</v>
       </c>
     </row>
     <row r="595">
@@ -5177,7 +5177,7 @@
         <v>131.1703100141614</v>
       </c>
       <c r="B595" t="n">
-        <v>2408.585205078125</v>
+        <v>2450.50732421875</v>
       </c>
     </row>
     <row r="596">
@@ -5185,7 +5185,7 @@
         <v>108.0124565148939</v>
       </c>
       <c r="B596" t="n">
-        <v>25595.298828125</v>
+        <v>20240.044921875</v>
       </c>
     </row>
     <row r="597">
@@ -5193,7 +5193,7 @@
         <v>72.75483013548647</v>
       </c>
       <c r="B597" t="n">
-        <v>2391026.5</v>
+        <v>2964324.5</v>
       </c>
     </row>
     <row r="598">
@@ -5201,7 +5201,7 @@
         <v>102.1297853024926</v>
       </c>
       <c r="B598" t="n">
-        <v>46872.43359375</v>
+        <v>35032.0859375</v>
       </c>
     </row>
     <row r="599">
@@ -5209,7 +5209,7 @@
         <v>151.2740997241661</v>
       </c>
       <c r="B599" t="n">
-        <v>321.3141784667969</v>
+        <v>391.9207763671875</v>
       </c>
     </row>
     <row r="600">
@@ -5217,7 +5217,7 @@
         <v>136.1261258631011</v>
       </c>
       <c r="B600" t="n">
-        <v>1465.537841796875</v>
+        <v>1577.599853515625</v>
       </c>
     </row>
     <row r="601">
@@ -5225,7 +5225,7 @@
         <v>70.04429450601435</v>
       </c>
       <c r="B601" t="n">
-        <v>3649244.25</v>
+        <v>5009378</v>
       </c>
     </row>
     <row r="602">
@@ -5233,7 +5233,7 @@
         <v>122.8379151633619</v>
       </c>
       <c r="B602" t="n">
-        <v>1554.421752929688</v>
+        <v>2352.380859375</v>
       </c>
     </row>
     <row r="603">
@@ -5241,7 +5241,7 @@
         <v>145.2436795880536</v>
       </c>
       <c r="B603" t="n">
-        <v>150.1192626953125</v>
+        <v>322.2461853027344</v>
       </c>
     </row>
     <row r="604">
@@ -5249,7 +5249,7 @@
         <v>164.4571457524564</v>
       </c>
       <c r="B604" t="n">
-        <v>20.59764671325684</v>
+        <v>53.43031311035156</v>
       </c>
     </row>
     <row r="605">
@@ -5257,7 +5257,7 @@
         <v>131.0383665555632</v>
       </c>
       <c r="B605" t="n">
-        <v>685.8751220703125</v>
+        <v>1154.00634765625</v>
       </c>
     </row>
     <row r="606">
@@ -5265,7 +5265,7 @@
         <v>105.0846236425317</v>
       </c>
       <c r="B606" t="n">
-        <v>9137.228515625</v>
+        <v>11553.8056640625</v>
       </c>
     </row>
     <row r="607">
@@ -5273,7 +5273,7 @@
         <v>167.7979790675237</v>
       </c>
       <c r="B607" t="n">
-        <v>17.08615875244141</v>
+        <v>39.29610443115234</v>
       </c>
     </row>
     <row r="608">
@@ -5281,7 +5281,7 @@
         <v>71.86493772903584</v>
       </c>
       <c r="B608" t="n">
-        <v>749961.75</v>
+        <v>557132.875</v>
       </c>
     </row>
     <row r="609">
@@ -5289,7 +5289,7 @@
         <v>63.7243546423255</v>
       </c>
       <c r="B609" t="n">
-        <v>2536177</v>
+        <v>2756434.5</v>
       </c>
     </row>
     <row r="610">
@@ -5297,7 +5297,7 @@
         <v>78.39256889043062</v>
       </c>
       <c r="B610" t="n">
-        <v>283954.03125</v>
+        <v>160456.9375</v>
       </c>
     </row>
     <row r="611">
@@ -5305,7 +5305,7 @@
         <v>130.1657586346477</v>
       </c>
       <c r="B611" t="n">
-        <v>748.2640991210938</v>
+        <v>1243.43017578125</v>
       </c>
     </row>
     <row r="612">
@@ -5313,7 +5313,7 @@
         <v>159.2283437471075</v>
       </c>
       <c r="B612" t="n">
-        <v>30.87244987487793</v>
+        <v>86.42396545410156</v>
       </c>
     </row>
     <row r="613">
@@ -5321,7 +5321,7 @@
         <v>82.1023374781829</v>
       </c>
       <c r="B613" t="n">
-        <v>161784.59375</v>
+        <v>106807.0078125</v>
       </c>
     </row>
     <row r="614">
@@ -5329,7 +5329,7 @@
         <v>142.6885094915793</v>
       </c>
       <c r="B614" t="n">
-        <v>205.1390991210938</v>
+        <v>410.4657897949219</v>
       </c>
     </row>
     <row r="615">
@@ -5337,7 +5337,7 @@
         <v>172.6103734770507</v>
       </c>
       <c r="B615" t="n">
-        <v>12.99786567687988</v>
+        <v>26.75187492370605</v>
       </c>
     </row>
     <row r="616">
@@ -5345,7 +5345,7 @@
         <v>90.77415138557585</v>
       </c>
       <c r="B616" t="n">
-        <v>46091.10546875</v>
+        <v>44433.72265625</v>
       </c>
     </row>
     <row r="617">
@@ -5353,7 +5353,7 @@
         <v>150.1241879196821</v>
       </c>
       <c r="B617" t="n">
-        <v>83.72150421142578</v>
+        <v>202.9840850830078</v>
       </c>
     </row>
     <row r="618">
@@ -5361,7 +5361,7 @@
         <v>118.4568685182436</v>
       </c>
       <c r="B618" t="n">
-        <v>2406.571044921875</v>
+        <v>3457.415771484375</v>
       </c>
     </row>
     <row r="619">
@@ -5369,7 +5369,7 @@
         <v>127.1372770510397</v>
       </c>
       <c r="B619" t="n">
-        <v>1012.228576660156</v>
+        <v>1618.279418945312</v>
       </c>
     </row>
     <row r="620">
@@ -5377,7 +5377,7 @@
         <v>163.3342161627692</v>
       </c>
       <c r="B620" t="n">
-        <v>22.02192687988281</v>
+        <v>59.24327087402344</v>
       </c>
     </row>
     <row r="621">
@@ -5385,7 +5385,7 @@
         <v>102.1441473614964</v>
       </c>
       <c r="B621" t="n">
-        <v>12263.2451171875</v>
+        <v>15079.72265625</v>
       </c>
     </row>
     <row r="622">
@@ -5393,7 +5393,7 @@
         <v>67.23321718613438</v>
       </c>
       <c r="B622" t="n">
-        <v>1500037.625</v>
+        <v>1370557</v>
       </c>
     </row>
     <row r="623">
@@ -5401,7 +5401,7 @@
         <v>166.2000858384098</v>
       </c>
       <c r="B623" t="n">
-        <v>18.57596206665039</v>
+        <v>45.51684188842773</v>
       </c>
     </row>
     <row r="624">
@@ -5409,7 +5409,7 @@
         <v>123.7687420483494</v>
       </c>
       <c r="B624" t="n">
-        <v>1416.5634765625</v>
+        <v>2169.37890625</v>
       </c>
     </row>
     <row r="625">
@@ -5417,7 +5417,7 @@
         <v>106.4764247729798</v>
       </c>
       <c r="B625" t="n">
-        <v>7952.59521484375</v>
+        <v>10185.3408203125</v>
       </c>
     </row>
     <row r="626">
@@ -5425,7 +5425,7 @@
         <v>157.5972135727069</v>
       </c>
       <c r="B626" t="n">
-        <v>36.92938613891602</v>
+        <v>100.4115371704102</v>
       </c>
     </row>
     <row r="627">
@@ -5433,7 +5433,7 @@
         <v>79.47429298200763</v>
       </c>
       <c r="B627" t="n">
-        <v>240949.25</v>
+        <v>139690.953125</v>
       </c>
     </row>
     <row r="628">
@@ -5441,7 +5441,7 @@
         <v>117.3998720267708</v>
       </c>
       <c r="B628" t="n">
-        <v>2674.224853515625</v>
+        <v>3796.5830078125</v>
       </c>
     </row>
     <row r="629">
@@ -5449,7 +5449,7 @@
         <v>114.4135116698119</v>
       </c>
       <c r="B629" t="n">
-        <v>3602.43994140625</v>
+        <v>4963.12548828125</v>
       </c>
     </row>
     <row r="630">
@@ -5457,7 +5457,7 @@
         <v>152.5263511302524</v>
       </c>
       <c r="B630" t="n">
-        <v>64.32872009277344</v>
+        <v>161.6836395263672</v>
       </c>
     </row>
     <row r="631">
@@ -5465,7 +5465,7 @@
         <v>110.1963023053826</v>
       </c>
       <c r="B631" t="n">
-        <v>5486.90478515625</v>
+        <v>7271.9072265625</v>
       </c>
     </row>
     <row r="632">
@@ -5473,7 +5473,7 @@
         <v>135.6187027636352</v>
       </c>
       <c r="B632" t="n">
-        <v>434.1740417480469</v>
+        <v>779.1402587890625</v>
       </c>
     </row>
     <row r="633">
@@ -5481,7 +5481,7 @@
         <v>162.0133085866661</v>
       </c>
       <c r="B633" t="n">
-        <v>24.29068374633789</v>
+        <v>66.89572143554688</v>
       </c>
     </row>
     <row r="634">
@@ -5489,7 +5489,7 @@
         <v>170.8686017156869</v>
       </c>
       <c r="B634" t="n">
-        <v>14.32947254180908</v>
+        <v>29.88467216491699</v>
       </c>
     </row>
     <row r="635">
@@ -5497,7 +5497,7 @@
         <v>111.717349495073</v>
       </c>
       <c r="B635" t="n">
-        <v>4714.3349609375</v>
+        <v>6335.9912109375</v>
       </c>
     </row>
     <row r="636">
@@ -5505,7 +5505,7 @@
         <v>101.1731868112455</v>
       </c>
       <c r="B636" t="n">
-        <v>13540.0546875</v>
+        <v>16465.99609375</v>
       </c>
     </row>
     <row r="637">
@@ -5513,7 +5513,7 @@
         <v>139.7386245796527</v>
       </c>
       <c r="B637" t="n">
-        <v>287.2708435058594</v>
+        <v>541.1166381835938</v>
       </c>
     </row>
     <row r="638">
@@ -5521,7 +5521,7 @@
         <v>95.77268840173973</v>
       </c>
       <c r="B638" t="n">
-        <v>23489.482421875</v>
+        <v>27057.91796875</v>
       </c>
     </row>
     <row r="639">
@@ -5529,7 +5529,7 @@
         <v>141.7245616289089</v>
       </c>
       <c r="B639" t="n">
-        <v>230.7856292724609</v>
+        <v>449.6987609863281</v>
       </c>
     </row>
     <row r="640">
@@ -5537,7 +5537,7 @@
         <v>109.5660691015161</v>
       </c>
       <c r="B640" t="n">
-        <v>5842.98095703125</v>
+        <v>7699.080078125</v>
       </c>
     </row>
     <row r="641">
@@ -5545,7 +5545,7 @@
         <v>161.1994683646218</v>
       </c>
       <c r="B641" t="n">
-        <v>25.82012557983398</v>
+        <v>72.09490203857422</v>
       </c>
     </row>
     <row r="642">
@@ -5553,7 +5553,7 @@
         <v>122.0693943051383</v>
       </c>
       <c r="B642" t="n">
-        <v>1678.295043945312</v>
+        <v>2515.049560546875</v>
       </c>
     </row>
     <row r="643">
@@ -5561,7 +5561,7 @@
         <v>92.64069529910998</v>
       </c>
       <c r="B643" t="n">
-        <v>35256.46875</v>
+        <v>36789.984375</v>
       </c>
     </row>
     <row r="644">
@@ -5569,7 +5569,7 @@
         <v>105.5410947860088</v>
       </c>
       <c r="B644" t="n">
-        <v>8730.44140625</v>
+        <v>11085.8330078125</v>
       </c>
     </row>
     <row r="645">
@@ -5577,7 +5577,7 @@
         <v>153.5019833691235</v>
       </c>
       <c r="B645" t="n">
-        <v>57.80007934570312</v>
+        <v>147.4145965576172</v>
       </c>
     </row>
     <row r="646">
@@ -5585,7 +5585,7 @@
         <v>147.1054522408281</v>
       </c>
       <c r="B646" t="n">
-        <v>119.5708389282227</v>
+        <v>270.1575012207031</v>
       </c>
     </row>
     <row r="647">
@@ -5593,7 +5593,7 @@
         <v>68.3379419544024</v>
       </c>
       <c r="B647" t="n">
-        <v>1271435.375</v>
+        <v>1099917</v>
       </c>
     </row>
     <row r="648">
@@ -5601,7 +5601,7 @@
         <v>171.955971613439</v>
       </c>
       <c r="B648" t="n">
-        <v>13.47074699401855</v>
+        <v>27.88804817199707</v>
       </c>
     </row>
     <row r="649">
@@ -5609,7 +5609,7 @@
         <v>61.98350987007375</v>
       </c>
       <c r="B649" t="n">
-        <v>3291049.75</v>
+        <v>3898491.75</v>
       </c>
     </row>
     <row r="650">
@@ -5617,7 +5617,7 @@
         <v>169.2964729503081</v>
       </c>
       <c r="B650" t="n">
-        <v>15.68027305603027</v>
+        <v>34.23713302612305</v>
       </c>
     </row>
     <row r="651">
@@ -5625,7 +5625,7 @@
         <v>115.461139223533</v>
       </c>
       <c r="B651" t="n">
-        <v>3244.914794921875</v>
+        <v>4513.69482421875</v>
       </c>
     </row>
     <row r="652">
@@ -5633,7 +5633,7 @@
         <v>120.0266871162845</v>
       </c>
       <c r="B652" t="n">
-        <v>2057.6845703125</v>
+        <v>3008.786865234375</v>
       </c>
     </row>
     <row r="653">
@@ -5641,7 +5641,7 @@
         <v>151.5377981965321</v>
       </c>
       <c r="B653" t="n">
-        <v>71.69626617431641</v>
+        <v>177.5511016845703</v>
       </c>
     </row>
     <row r="654">
@@ -5649,7 +5649,7 @@
         <v>88.05845827833193</v>
       </c>
       <c r="B654" t="n">
-        <v>68067.625</v>
+        <v>58478.0078125</v>
       </c>
     </row>
     <row r="655">
@@ -5657,7 +5657,7 @@
         <v>134.5524908200139</v>
       </c>
       <c r="B655" t="n">
-        <v>483.0354919433594</v>
+        <v>855.1332397460938</v>
       </c>
     </row>
     <row r="656">
@@ -5665,7 +5665,7 @@
         <v>159.9996883753829</v>
       </c>
       <c r="B656" t="n">
-        <v>28.45735549926758</v>
+        <v>80.5054931640625</v>
       </c>
     </row>
     <row r="657">
@@ -5673,7 +5673,7 @@
         <v>74.15986593442659</v>
       </c>
       <c r="B657" t="n">
-        <v>531946.8125</v>
+        <v>359665.8125</v>
       </c>
     </row>
     <row r="658">
@@ -5681,7 +5681,7 @@
         <v>127.8382455368106</v>
       </c>
       <c r="B658" t="n">
-        <v>943.85546875</v>
+        <v>1522.535278320312</v>
       </c>
     </row>
     <row r="659">
@@ -5689,7 +5689,7 @@
         <v>174.0635502691307</v>
       </c>
       <c r="B659" t="n">
-        <v>12.01506805419922</v>
+        <v>24.4238452911377</v>
       </c>
     </row>
     <row r="660">
@@ -5697,7 +5697,7 @@
         <v>80.6966586394726</v>
       </c>
       <c r="B660" t="n">
-        <v>200021.15625</v>
+        <v>123170.7265625</v>
       </c>
     </row>
     <row r="661">
@@ -5705,7 +5705,7 @@
         <v>86.52000981300645</v>
       </c>
       <c r="B661" t="n">
-        <v>84833.4140625</v>
+        <v>68322.5703125</v>
       </c>
     </row>
     <row r="662">
@@ -5713,7 +5713,7 @@
         <v>103.2603884897148</v>
       </c>
       <c r="B662" t="n">
-        <v>10961.23046875</v>
+        <v>13629.65234375</v>
       </c>
     </row>
     <row r="663">
@@ -5721,7 +5721,7 @@
         <v>132.4593878796456</v>
       </c>
       <c r="B663" t="n">
-        <v>595.213134765625</v>
+        <v>1022.888549804688</v>
       </c>
     </row>
     <row r="664">
@@ -5729,7 +5729,7 @@
         <v>99.90349681693327</v>
       </c>
       <c r="B664" t="n">
-        <v>15412.408203125</v>
+        <v>18490.15625</v>
       </c>
     </row>
     <row r="665">
@@ -5737,7 +5737,7 @@
         <v>133.2776235845427</v>
       </c>
       <c r="B665" t="n">
-        <v>548.5531616210938</v>
+        <v>954.260498046875</v>
       </c>
     </row>
     <row r="666">
@@ -5745,7 +5745,7 @@
         <v>76.64669383431134</v>
       </c>
       <c r="B666" t="n">
-        <v>367602.28125</v>
+        <v>223845.03125</v>
       </c>
     </row>
     <row r="667">
@@ -5753,7 +5753,7 @@
         <v>167.1282341743321</v>
       </c>
       <c r="B667" t="n">
-        <v>17.67353439331055</v>
+        <v>41.79264068603516</v>
       </c>
     </row>
     <row r="668">
@@ -5761,7 +5761,7 @@
         <v>83.68708304546581</v>
       </c>
       <c r="B668" t="n">
-        <v>127760.8046875</v>
+        <v>90989.953125</v>
       </c>
     </row>
     <row r="669">
@@ -5769,7 +5769,7 @@
         <v>96.72983587987864</v>
       </c>
       <c r="B669" t="n">
-        <v>21304.421875</v>
+        <v>24753.259765625</v>
       </c>
     </row>
     <row r="670">
@@ -5777,7 +5777,7 @@
         <v>156.1458747526076</v>
       </c>
       <c r="B670" t="n">
-        <v>43.24947357177734</v>
+        <v>114.8129501342773</v>
       </c>
     </row>
     <row r="671">
@@ -5785,7 +5785,7 @@
         <v>98.89361184429887</v>
       </c>
       <c r="B671" t="n">
-        <v>17084.83203125</v>
+        <v>20288.771484375</v>
       </c>
     </row>
     <row r="672">
@@ -5793,7 +5793,7 @@
         <v>70.18066491257591</v>
       </c>
       <c r="B672" t="n">
-        <v>964976.25</v>
+        <v>768147.5625</v>
       </c>
     </row>
     <row r="673">
@@ -5801,7 +5801,7 @@
         <v>112.8320489656923</v>
       </c>
       <c r="B673" t="n">
-        <v>4218.13671875</v>
+        <v>5727.51220703125</v>
       </c>
     </row>
     <row r="674">
@@ -5809,7 +5809,7 @@
         <v>81.0285360150329</v>
       </c>
       <c r="B674" t="n">
-        <v>190249.109375</v>
+        <v>119077.0546875</v>
       </c>
     </row>
     <row r="675">
@@ -5817,7 +5817,7 @@
         <v>89.85807937844459</v>
       </c>
       <c r="B675" t="n">
-        <v>52569.53125</v>
+        <v>48747.0390625</v>
       </c>
     </row>
     <row r="676">
@@ -5825,7 +5825,7 @@
         <v>73.83820954920151</v>
       </c>
       <c r="B676" t="n">
-        <v>558182.9375</v>
+        <v>382417.40625</v>
       </c>
     </row>
     <row r="677">
@@ -5833,7 +5833,7 @@
         <v>94.43835732213526</v>
       </c>
       <c r="B677" t="n">
-        <v>27236.63671875</v>
+        <v>30804.392578125</v>
       </c>
     </row>
     <row r="678">
@@ -5841,7 +5841,7 @@
         <v>146.5708518551092</v>
       </c>
       <c r="B678" t="n">
-        <v>127.6434478759766</v>
+        <v>284.1867065429688</v>
       </c>
     </row>
     <row r="679">
@@ -5849,7 +5849,7 @@
         <v>148.4616627773283</v>
       </c>
       <c r="B679" t="n">
-        <v>101.3084716796875</v>
+        <v>237.5956726074219</v>
       </c>
     </row>
     <row r="680">
@@ -5857,7 +5857,7 @@
         <v>136.9950612763071</v>
       </c>
       <c r="B680" t="n">
-        <v>378.2162475585938</v>
+        <v>689.8007202148438</v>
       </c>
     </row>
     <row r="681">
@@ -5865,7 +5865,7 @@
         <v>70.6797505455431</v>
       </c>
       <c r="B681" t="n">
-        <v>895524.3125</v>
+        <v>698413.875</v>
       </c>
     </row>
     <row r="682">
@@ -5873,7 +5873,7 @@
         <v>84.724098569785</v>
       </c>
       <c r="B682" t="n">
-        <v>109863.2734375</v>
+        <v>81930.4765625</v>
       </c>
     </row>
     <row r="683">
@@ -5881,7 +5881,7 @@
         <v>129.0579310936311</v>
       </c>
       <c r="B683" t="n">
-        <v>835.7120971679688</v>
+        <v>1369.2431640625</v>
       </c>
     </row>
     <row r="684">
@@ -5889,7 +5889,7 @@
         <v>86.86824473775749</v>
       </c>
       <c r="B684" t="n">
-        <v>80729.1875</v>
+        <v>65958.328125</v>
       </c>
     </row>
     <row r="685">
@@ -5897,7 +5897,7 @@
         <v>108.4767099926982</v>
       </c>
       <c r="B685" t="n">
-        <v>6513.83251953125</v>
+        <v>8497.4970703125</v>
       </c>
     </row>
     <row r="686">
@@ -5905,7 +5905,7 @@
         <v>154.9964535248698</v>
       </c>
       <c r="B686" t="n">
-        <v>49.06100082397461</v>
+        <v>127.9605712890625</v>
       </c>
     </row>
     <row r="687">
@@ -5913,7 +5913,7 @@
         <v>65.68972275124878</v>
       </c>
       <c r="B687" t="n">
-        <v>1889856</v>
+        <v>1863717.25</v>
       </c>
     </row>
     <row r="688">
@@ -5921,7 +5921,7 @@
         <v>115.9448203547901</v>
       </c>
       <c r="B688" t="n">
-        <v>3092.038330078125</v>
+        <v>4320.1611328125</v>
       </c>
     </row>
     <row r="689">
@@ -5929,7 +5929,7 @@
         <v>138.2641424607403</v>
       </c>
       <c r="B689" t="n">
-        <v>333.0336608886719</v>
+        <v>616.5302734375</v>
       </c>
     </row>
     <row r="690">
@@ -5937,7 +5937,7 @@
         <v>175.6945459562694</v>
       </c>
       <c r="B690" t="n">
-        <v>11.00212001800537</v>
+        <v>22.25283813476562</v>
       </c>
     </row>
     <row r="691">
@@ -5945,7 +5945,7 @@
         <v>156.7597833496699</v>
       </c>
       <c r="B691" t="n">
-        <v>40.46162033081055</v>
+        <v>108.4570007324219</v>
       </c>
     </row>
     <row r="692">
@@ -5953,7 +5953,7 @@
         <v>144.4169424573129</v>
       </c>
       <c r="B692" t="n">
-        <v>166.0787353515625</v>
+        <v>348.4898071289062</v>
       </c>
     </row>
     <row r="693">
@@ -5961,7 +5961,7 @@
         <v>66.14597979197856</v>
       </c>
       <c r="B693" t="n">
-        <v>1765114</v>
+        <v>1701855.625</v>
       </c>
     </row>
     <row r="694">
@@ -5969,7 +5969,7 @@
         <v>75.70638792783006</v>
       </c>
       <c r="B694" t="n">
-        <v>422443.53125</v>
+        <v>267806.53125</v>
       </c>
     </row>
     <row r="695">
@@ -5977,7 +5977,7 @@
         <v>120.9756250545959</v>
       </c>
       <c r="B695" t="n">
-        <v>1871.809326171875</v>
+        <v>2766.33349609375</v>
       </c>
     </row>
     <row r="696">
@@ -5985,7 +5985,7 @@
         <v>97.89147537947257</v>
       </c>
       <c r="B696" t="n">
-        <v>18923.724609375</v>
+        <v>22246.4375</v>
       </c>
     </row>
     <row r="697">
@@ -5993,7 +5993,7 @@
         <v>62.74606241805275</v>
       </c>
       <c r="B697" t="n">
-        <v>2936085.25</v>
+        <v>3349276.25</v>
       </c>
     </row>
     <row r="698">
@@ -6001,7 +6001,7 @@
         <v>92.0275267729704</v>
       </c>
       <c r="B698" t="n">
-        <v>38500.796875</v>
+        <v>39143.69921875</v>
       </c>
     </row>
     <row r="699">
@@ -6009,7 +6009,7 @@
         <v>141.0154310201027</v>
       </c>
       <c r="B699" t="n">
-        <v>252.3056640625</v>
+        <v>480.9356079101562</v>
       </c>
     </row>
     <row r="700">
@@ -6017,7 +6017,7 @@
         <v>125.9156681731383</v>
       </c>
       <c r="B700" t="n">
-        <v>1143.433349609375</v>
+        <v>1799.754516601562</v>
       </c>
     </row>
     <row r="701">
@@ -6025,7 +6025,7 @@
         <v>60.04415353118342</v>
       </c>
       <c r="B701" t="n">
-        <v>4399400.5</v>
+        <v>5735699.5</v>
       </c>
     </row>
     <row r="702">
@@ -6033,7 +6033,7 @@
         <v>177.9919202713117</v>
       </c>
       <c r="B702" t="n">
-        <v>15.35571765899658</v>
+        <v>1188.013061523438</v>
       </c>
     </row>
     <row r="703">
@@ -6041,7 +6041,7 @@
         <v>216.4979960868235</v>
       </c>
       <c r="B703" t="n">
-        <v>4.172751903533936</v>
+        <v>173.8671112060547</v>
       </c>
     </row>
     <row r="704">
@@ -6049,7 +6049,7 @@
         <v>249.5178552079854</v>
       </c>
       <c r="B704" t="n">
-        <v>2.473778963088989</v>
+        <v>62.48357772827148</v>
       </c>
     </row>
     <row r="705">
@@ -6057,7 +6057,7 @@
         <v>192.0850436767127</v>
       </c>
       <c r="B705" t="n">
-        <v>7.245807647705078</v>
+        <v>545.4349365234375</v>
       </c>
     </row>
     <row r="706">
@@ -6065,7 +6065,7 @@
         <v>147.4814866026166</v>
       </c>
       <c r="B706" t="n">
-        <v>446.1631469726562</v>
+        <v>6675.2373046875</v>
       </c>
     </row>
     <row r="707">
@@ -6073,7 +6073,7 @@
         <v>255.2593411255647</v>
       </c>
       <c r="B707" t="n">
-        <v>2.293404102325439</v>
+        <v>50.57870483398438</v>
       </c>
     </row>
     <row r="708">
@@ -6081,7 +6081,7 @@
         <v>90.39083260364436</v>
       </c>
       <c r="B708" t="n">
-        <v>164829.8125</v>
+        <v>615251.875</v>
       </c>
     </row>
     <row r="709">
@@ -6089,7 +6089,7 @@
         <v>76.40059760974711</v>
       </c>
       <c r="B709" t="n">
-        <v>1461400.25</v>
+        <v>4802697</v>
       </c>
     </row>
     <row r="710">
@@ -6097,7 +6097,7 @@
         <v>101.6090823197472</v>
       </c>
       <c r="B710" t="n">
-        <v>47701.14453125</v>
+        <v>233791.53125</v>
       </c>
     </row>
     <row r="711">
@@ -6105,7 +6105,7 @@
         <v>190.5853980443164</v>
       </c>
       <c r="B711" t="n">
-        <v>7.593099117279053</v>
+        <v>591.3854370117188</v>
       </c>
     </row>
     <row r="712">
@@ -6113,7 +6113,7 @@
         <v>240.5317459806483</v>
       </c>
       <c r="B712" t="n">
-        <v>2.84592080116272</v>
+        <v>82.49723815917969</v>
       </c>
     </row>
     <row r="713">
@@ -6121,7 +6121,7 @@
         <v>107.9846126426746</v>
       </c>
       <c r="B713" t="n">
-        <v>24760.3828125</v>
+        <v>134898.546875</v>
       </c>
     </row>
     <row r="714">
@@ -6129,7 +6129,7 @@
         <v>212.1067344636342</v>
       </c>
       <c r="B714" t="n">
-        <v>4.585569381713867</v>
+        <v>198.5608062744141</v>
       </c>
     </row>
     <row r="715">
@@ -6137,7 +6137,7 @@
         <v>263.5298210107847</v>
       </c>
       <c r="B715" t="n">
-        <v>2.082610607147217</v>
+        <v>38.86039733886719</v>
       </c>
     </row>
     <row r="716">
@@ -6145,7 +6145,7 @@
         <v>122.887809759578</v>
       </c>
       <c r="B716" t="n">
-        <v>5346.7021484375</v>
+        <v>37301.296875</v>
       </c>
     </row>
     <row r="717">
@@ -6153,7 +6153,7 @@
         <v>224.8855351269474</v>
       </c>
       <c r="B717" t="n">
-        <v>3.668194532394409</v>
+        <v>134.3794555664062</v>
       </c>
     </row>
     <row r="718">
@@ -6161,7 +6161,7 @@
         <v>170.4627455879294</v>
       </c>
       <c r="B718" t="n">
-        <v>30.09369087219238</v>
+        <v>1818.579345703125</v>
       </c>
     </row>
     <row r="719">
@@ -6169,7 +6169,7 @@
         <v>185.3807132474087</v>
       </c>
       <c r="B719" t="n">
-        <v>9.24629020690918</v>
+        <v>783.6744995117188</v>
       </c>
     </row>
     <row r="720">
@@ -6177,7 +6177,7 @@
         <v>247.5880120169035</v>
       </c>
       <c r="B720" t="n">
-        <v>2.541721105575562</v>
+        <v>66.32568359375</v>
       </c>
     </row>
     <row r="721">
@@ -6185,7 +6185,7 @@
         <v>142.4280458690133</v>
       </c>
       <c r="B721" t="n">
-        <v>740.47216796875</v>
+        <v>8913.9541015625</v>
       </c>
     </row>
     <row r="722">
@@ -6193,7 +6193,7 @@
         <v>82.4308550282004</v>
       </c>
       <c r="B722" t="n">
-        <v>570512.5</v>
+        <v>1766046.5</v>
       </c>
     </row>
     <row r="723">
@@ -6201,7 +6201,7 @@
         <v>252.5132354065584</v>
       </c>
       <c r="B723" t="n">
-        <v>2.375143051147461</v>
+        <v>55.90229034423828</v>
       </c>
     </row>
     <row r="724">
@@ -6209,7 +6209,7 @@
         <v>179.591619791715</v>
       </c>
       <c r="B724" t="n">
-        <v>13.37312412261963</v>
+        <v>1085.2626953125</v>
       </c>
     </row>
     <row r="725">
@@ -6217,7 +6217,7 @@
         <v>149.8734067725032</v>
       </c>
       <c r="B725" t="n">
-        <v>351.0381774902344</v>
+        <v>5826.24462890625</v>
       </c>
     </row>
     <row r="726">
@@ -6225,7 +6225,7 @@
         <v>237.728519946047</v>
       </c>
       <c r="B726" t="n">
-        <v>2.978539943695068</v>
+        <v>89.96706390380859</v>
       </c>
     </row>
     <row r="727">
@@ -6233,7 +6233,7 @@
         <v>103.4681106078348</v>
       </c>
       <c r="B727" t="n">
-        <v>39399.73828125</v>
+        <v>199154.90625</v>
       </c>
     </row>
     <row r="728">
@@ -6241,7 +6241,7 @@
         <v>168.6462136336557</v>
       </c>
       <c r="B728" t="n">
-        <v>37.67177200317383</v>
+        <v>2015.322998046875</v>
       </c>
     </row>
     <row r="729">
@@ -6249,7 +6249,7 @@
         <v>163.5139174915624</v>
       </c>
       <c r="B729" t="n">
-        <v>71.88800811767578</v>
+        <v>2693.94775390625</v>
       </c>
     </row>
     <row r="730">
@@ -6257,7 +6257,7 @@
         <v>229.0138423319235</v>
       </c>
       <c r="B730" t="n">
-        <v>3.436065673828125</v>
+        <v>118.0590286254883</v>
       </c>
     </row>
     <row r="731">
@@ -6265,7 +6265,7 @@
         <v>156.2663101152372</v>
       </c>
       <c r="B731" t="n">
-        <v>173.3051605224609</v>
+        <v>4058.67822265625</v>
       </c>
     </row>
     <row r="732">
@@ -6273,7 +6273,7 @@
         <v>199.9567132143156</v>
       </c>
       <c r="B732" t="n">
-        <v>5.954891681671143</v>
+        <v>358.2473754882812</v>
       </c>
     </row>
     <row r="733">
@@ -6281,7 +6281,7 @@
         <v>245.317928019472</v>
       </c>
       <c r="B733" t="n">
-        <v>2.634061336517334</v>
+        <v>71.14856719970703</v>
       </c>
     </row>
     <row r="734">
@@ -6289,7 +6289,7 @@
         <v>260.5364486702954</v>
       </c>
       <c r="B734" t="n">
-        <v>2.156251668930054</v>
+        <v>42.48640823364258</v>
       </c>
     </row>
     <row r="735">
@@ -6297,7 +6297,7 @@
         <v>158.8803498460416</v>
       </c>
       <c r="B735" t="n">
-        <v>126.0576629638672</v>
+        <v>3500.94775390625</v>
       </c>
     </row>
     <row r="736">
@@ -6305,7 +6305,7 @@
         <v>140.7593734750184</v>
       </c>
       <c r="B736" t="n">
-        <v>875.3045043945312</v>
+        <v>9807.2197265625</v>
       </c>
     </row>
     <row r="737">
@@ -6313,7 +6313,7 @@
         <v>207.0371242547318</v>
       </c>
       <c r="B737" t="n">
-        <v>5.12129020690918</v>
+        <v>245.7769012451172</v>
       </c>
     </row>
     <row r="738">
@@ -6321,7 +6321,7 @@
         <v>131.4781904162155</v>
       </c>
       <c r="B738" t="n">
-        <v>2219.427734375</v>
+        <v>17777.0546875</v>
       </c>
     </row>
     <row r="739">
@@ -6329,7 +6329,7 @@
         <v>210.4501139271226</v>
       </c>
       <c r="B739" t="n">
-        <v>4.752876758575439</v>
+        <v>208.7624206542969</v>
       </c>
     </row>
     <row r="740">
@@ -6337,7 +6337,7 @@
         <v>155.1832045773252</v>
       </c>
       <c r="B740" t="n">
-        <v>198.1272125244141</v>
+        <v>4315.0341796875</v>
       </c>
     </row>
     <row r="741">
@@ -6345,7 +6345,7 @@
         <v>243.9192793191752</v>
       </c>
       <c r="B741" t="n">
-        <v>2.693512439727783</v>
+        <v>74.2930908203125</v>
       </c>
     </row>
     <row r="742">
@@ -6353,7 +6353,7 @@
         <v>176.6711564771541</v>
       </c>
       <c r="B742" t="n">
-        <v>17.16763496398926</v>
+        <v>1280.143920898438</v>
       </c>
     </row>
     <row r="743">
@@ -6361,7 +6361,7 @@
         <v>126.0956128983239</v>
       </c>
       <c r="B743" t="n">
-        <v>3844.199951171875</v>
+        <v>28283.541015625</v>
       </c>
     </row>
     <row r="744">
@@ -6369,7 +6369,7 @@
         <v>148.2659683156776</v>
       </c>
       <c r="B744" t="n">
-        <v>412.4195861816406</v>
+        <v>6382.1767578125</v>
       </c>
     </row>
     <row r="745">
@@ -6377,7 +6377,7 @@
         <v>230.6905433917914</v>
       </c>
       <c r="B745" t="n">
-        <v>3.342396974563599</v>
+        <v>112.0108032226562</v>
       </c>
     </row>
     <row r="746">
@@ -6385,7 +6385,7 @@
         <v>219.6975994371102</v>
       </c>
       <c r="B746" t="n">
-        <v>3.970175743103027</v>
+        <v>157.8311004638672</v>
       </c>
     </row>
     <row r="747">
@@ -6393,7 +6393,7 @@
         <v>84.32941179582055</v>
       </c>
       <c r="B747" t="n">
-        <v>424279.625</v>
+        <v>1286894.25</v>
       </c>
     </row>
     <row r="748">
@@ -6401,7 +6401,7 @@
         <v>262.4051797222119</v>
       </c>
       <c r="B748" t="n">
-        <v>2.109979152679443</v>
+        <v>40.1849365234375</v>
       </c>
     </row>
     <row r="749">
@@ -6409,7 +6409,7 @@
         <v>73.40881837326228</v>
       </c>
       <c r="B749" t="n">
-        <v>2324939.75</v>
+        <v>7866784.5</v>
       </c>
     </row>
     <row r="750">
@@ -6417,7 +6417,7 @@
         <v>257.8346212171463</v>
       </c>
       <c r="B750" t="n">
-        <v>2.224953413009644</v>
+        <v>46.29771041870117</v>
       </c>
     </row>
     <row r="751">
@@ -6425,7 +6425,7 @@
         <v>165.3143481863326</v>
       </c>
       <c r="B751" t="n">
-        <v>58.20495223999023</v>
+        <v>2433.169189453125</v>
       </c>
     </row>
     <row r="752">
@@ -6433,7 +6433,7 @@
         <v>173.1606028360468</v>
       </c>
       <c r="B752" t="n">
-        <v>23.10358047485352</v>
+        <v>1561.260864257812</v>
       </c>
     </row>
     <row r="753">
@@ -6441,7 +6441,7 @@
         <v>227.3149360374553</v>
       </c>
       <c r="B753" t="n">
-        <v>3.533653020858765</v>
+        <v>124.5204238891602</v>
       </c>
     </row>
     <row r="754">
@@ -6449,7 +6449,7 @@
         <v>118.2206766639556</v>
       </c>
       <c r="B754" t="n">
-        <v>8640.724609375</v>
+        <v>55792.31640625</v>
       </c>
     </row>
     <row r="755">
@@ -6457,7 +6457,7 @@
         <v>198.1243437776701</v>
       </c>
       <c r="B755" t="n">
-        <v>6.197362422943115</v>
+        <v>394.9411010742188</v>
       </c>
     </row>
     <row r="756">
@@ -6465,7 +6465,7 @@
         <v>241.8573626466669</v>
       </c>
       <c r="B756" t="n">
-        <v>2.785278558731079</v>
+        <v>79.18408203125</v>
       </c>
     </row>
     <row r="757">
@@ -6473,7 +6473,7 @@
         <v>94.33484798258621</v>
       </c>
       <c r="B757" t="n">
-        <v>100795.65625</v>
+        <v>437839.53125</v>
       </c>
     </row>
     <row r="758">
@@ -6481,7 +6481,7 @@
         <v>186.5853829540861</v>
       </c>
       <c r="B758" t="n">
-        <v>8.70468807220459</v>
+        <v>733.8709106445312</v>
       </c>
     </row>
     <row r="759">
@@ -6489,7 +6489,7 @@
         <v>266.0272201027572</v>
       </c>
       <c r="B759" t="n">
-        <v>2.026015758514404</v>
+        <v>36.06148910522461</v>
       </c>
     </row>
     <row r="760">
@@ -6497,7 +6497,7 @@
         <v>105.5688425350505</v>
       </c>
       <c r="B760" t="n">
-        <v>31743.904296875</v>
+        <v>166149.859375</v>
       </c>
     </row>
     <row r="761">
@@ -6505,7 +6505,7 @@
         <v>115.5767314665851</v>
       </c>
       <c r="B761" t="n">
-        <v>11340.8486328125</v>
+        <v>70083.28125</v>
       </c>
     </row>
     <row r="762">
@@ -6513,7 +6513,7 @@
         <v>144.3463944107931</v>
       </c>
       <c r="B762" t="n">
-        <v>610.9255981445312</v>
+        <v>7987.11181640625</v>
       </c>
     </row>
     <row r="763">
@@ -6521,7 +6521,7 @@
         <v>194.5271810572287</v>
       </c>
       <c r="B763" t="n">
-        <v>6.713912963867188</v>
+        <v>478.2655944824219</v>
       </c>
     </row>
     <row r="764">
@@ -6529,7 +6529,7 @@
         <v>138.5773109371608</v>
       </c>
       <c r="B764" t="n">
-        <v>1089.334716796875</v>
+        <v>11111.7041015625</v>
       </c>
     </row>
     <row r="765">
@@ -6537,7 +6537,7 @@
         <v>195.9333837419719</v>
       </c>
       <c r="B765" t="n">
-        <v>6.506591320037842</v>
+        <v>443.7826232910156</v>
       </c>
     </row>
     <row r="766">
@@ -6545,7 +6545,7 @@
         <v>98.60865814313418</v>
       </c>
       <c r="B766" t="n">
-        <v>64945.078125</v>
+        <v>302845.5625</v>
       </c>
     </row>
     <row r="767">
@@ -6553,7 +6553,7 @@
         <v>254.1083316288359</v>
       </c>
       <c r="B767" t="n">
-        <v>2.325151205062866</v>
+        <v>52.61788177490234</v>
       </c>
     </row>
     <row r="768">
@@ -6561,7 +6561,7 @@
         <v>110.708123066396</v>
       </c>
       <c r="B768" t="n">
-        <v>18711.45703125</v>
+        <v>106656.65625</v>
       </c>
     </row>
     <row r="769">
@@ -6569,7 +6569,7 @@
         <v>133.1231239548019</v>
       </c>
       <c r="B769" t="n">
-        <v>1882.018432617188</v>
+        <v>15425.4775390625</v>
       </c>
     </row>
     <row r="770">
@@ -6577,7 +6577,7 @@
         <v>235.23427955409</v>
       </c>
       <c r="B770" t="n">
-        <v>3.101728200912476</v>
+        <v>97.18046569824219</v>
       </c>
     </row>
     <row r="771">
@@ -6585,7 +6585,7 @@
         <v>136.841743848972</v>
       </c>
       <c r="B771" t="n">
-        <v>1296.354614257812</v>
+        <v>12272.107421875</v>
       </c>
     </row>
     <row r="772">
@@ -6593,7 +6593,7 @@
         <v>87.49627674135296</v>
       </c>
       <c r="B772" t="n">
-        <v>258892.984375</v>
+        <v>789735.125</v>
       </c>
     </row>
     <row r="773">
@@ -6601,7 +6601,7 @@
         <v>160.7960489274742</v>
       </c>
       <c r="B773" t="n">
-        <v>100.4881286621094</v>
+        <v>3141.5068359375</v>
       </c>
     </row>
     <row r="774">
@@ -6609,7 +6609,7 @@
         <v>106.1392000172837</v>
       </c>
       <c r="B774" t="n">
-        <v>29935.41796875</v>
+        <v>158173.90625</v>
       </c>
     </row>
     <row r="775">
@@ -6617,7 +6617,7 @@
         <v>121.3134676621403</v>
       </c>
       <c r="B775" t="n">
-        <v>6286.46630859375</v>
+        <v>42727.90234375</v>
       </c>
     </row>
     <row r="776">
@@ -6625,7 +6625,7 @@
         <v>93.78205607951811</v>
       </c>
       <c r="B776" t="n">
-        <v>106723.1875</v>
+        <v>459220.375</v>
       </c>
     </row>
     <row r="777">
@@ -6633,7 +6633,7 @@
         <v>129.1850370678021</v>
       </c>
       <c r="B777" t="n">
-        <v>2797.77099609375</v>
+        <v>21666.0234375</v>
       </c>
     </row>
     <row r="778">
@@ -6641,7 +6641,7 @@
         <v>218.7788464504544</v>
       </c>
       <c r="B778" t="n">
-        <v>4.026188850402832</v>
+        <v>162.2781066894531</v>
       </c>
     </row>
     <row r="779">
@@ -6649,7 +6649,7 @@
         <v>222.0283543602818</v>
       </c>
       <c r="B779" t="n">
-        <v>3.831546783447266</v>
+        <v>146.9778289794922</v>
       </c>
     </row>
     <row r="780">
@@ -6657,7 +6657,7 @@
         <v>202.3220940258654</v>
       </c>
       <c r="B780" t="n">
-        <v>5.662737369537354</v>
+        <v>315.8741760253906</v>
       </c>
     </row>
     <row r="781">
@@ -6665,7 +6665,7 @@
         <v>88.35399482037947</v>
       </c>
       <c r="B781" t="n">
-        <v>226473.390625</v>
+        <v>733416.5625</v>
       </c>
     </row>
     <row r="782">
@@ -6673,7 +6673,7 @@
         <v>112.4903161504798</v>
       </c>
       <c r="B782" t="n">
-        <v>15577.73828125</v>
+        <v>91459.40625</v>
       </c>
     </row>
     <row r="783">
@@ -6681,7 +6681,7 @@
         <v>188.6815089166647</v>
       </c>
       <c r="B783" t="n">
-        <v>8.071369171142578</v>
+        <v>655.33984375</v>
       </c>
     </row>
     <row r="784">
@@ -6689,7 +6689,7 @@
         <v>116.1752006890542</v>
       </c>
       <c r="B784" t="n">
-        <v>10663.8623046875</v>
+        <v>66557.484375</v>
       </c>
     </row>
     <row r="785">
@@ -6697,7 +6697,7 @@
         <v>153.3110549090802</v>
       </c>
       <c r="B785" t="n">
-        <v>249.5947265625</v>
+        <v>4796.91845703125</v>
       </c>
     </row>
     <row r="786">
@@ -6705,7 +6705,7 @@
         <v>233.2589083906561</v>
       </c>
       <c r="B786" t="n">
-        <v>3.203843355178833</v>
+        <v>103.3415145874023</v>
       </c>
     </row>
     <row r="787">
@@ -6713,7 +6713,7 @@
         <v>79.77823793360004</v>
       </c>
       <c r="B787" t="n">
-        <v>862898.6875</v>
+        <v>2748239</v>
       </c>
     </row>
     <row r="788">
@@ -6721,7 +6721,7 @@
         <v>166.1455924124922</v>
       </c>
       <c r="B788" t="n">
-        <v>52.3802375793457</v>
+        <v>2321.44140625</v>
       </c>
     </row>
     <row r="789">
@@ -6729,7 +6729,7 @@
         <v>204.5031102758608</v>
       </c>
       <c r="B789" t="n">
-        <v>5.406304359436035</v>
+        <v>281.2590026855469</v>
       </c>
     </row>
     <row r="790">
@@ -6737,7 +6737,7 @@
         <v>268.8302150103768</v>
       </c>
       <c r="B790" t="n">
-        <v>1.966359615325928</v>
+        <v>33.1561393737793</v>
       </c>
     </row>
     <row r="791">
@@ -6745,7 +6745,7 @@
         <v>236.2893299658593</v>
       </c>
       <c r="B791" t="n">
-        <v>3.049009799957275</v>
+        <v>94.06127166748047</v>
       </c>
     </row>
     <row r="792">
@@ -6753,7 +6753,7 @@
         <v>215.0771830303085</v>
       </c>
       <c r="B792" t="n">
-        <v>4.300790786743164</v>
+        <v>181.5010681152344</v>
       </c>
     </row>
     <row r="793">
@@ -6761,7 +6761,7 @@
         <v>80.56235169417947</v>
       </c>
       <c r="B793" t="n">
-        <v>763558.0625</v>
+        <v>2411482.75</v>
       </c>
     </row>
     <row r="794">
@@ -6769,7 +6769,7 @@
         <v>96.99266817562209</v>
       </c>
       <c r="B794" t="n">
-        <v>76687.84375</v>
+        <v>348140.625</v>
       </c>
     </row>
     <row r="795">
@@ -6777,7 +6777,7 @@
         <v>174.7914276320338</v>
       </c>
       <c r="B795" t="n">
-        <v>20.12110328674316</v>
+        <v>1423.7158203125</v>
       </c>
     </row>
     <row r="796">
@@ -6785,7 +6785,7 @@
         <v>135.119493183444</v>
       </c>
       <c r="B796" t="n">
-        <v>1540.662231445312</v>
+        <v>13543.3251953125</v>
       </c>
     </row>
     <row r="797">
@@ -6793,7 +6793,7 @@
         <v>74.71932515487569</v>
       </c>
       <c r="B797" t="n">
-        <v>1897094.875</v>
+        <v>6337549.5</v>
       </c>
     </row>
     <row r="798">
@@ -6801,7 +6801,7 @@
         <v>125.0418343568876</v>
       </c>
       <c r="B798" t="n">
-        <v>4284.24267578125</v>
+        <v>30975.396484375</v>
       </c>
     </row>
     <row r="799">
@@ -6809,7 +6809,7 @@
         <v>209.2314169673481</v>
       </c>
       <c r="B799" t="n">
-        <v>4.881281852722168</v>
+        <v>218.6890563964844</v>
       </c>
     </row>
     <row r="800">
@@ -6817,7 +6817,7 @@
         <v>183.281281905645</v>
       </c>
       <c r="B800" t="n">
-        <v>10.45102405548096</v>
+        <v>880.88623046875</v>
       </c>
     </row>
     <row r="801">
@@ -6825,7 +6825,7 @@
         <v>70.0758813306721</v>
       </c>
       <c r="B801" t="n">
-        <v>3864661.5</v>
+        <v>13631657</v>
       </c>
     </row>
     <row r="802">
@@ -6833,7 +6833,7 @@
         <v>129.9397312460926</v>
       </c>
       <c r="B802" t="n">
-        <v>3378.89892578125</v>
+        <v>9917.01171875</v>
       </c>
     </row>
     <row r="803">
@@ -6841,7 +6841,7 @@
         <v>151.5373338974149</v>
       </c>
       <c r="B803" t="n">
-        <v>1134.6826171875</v>
+        <v>1671.109130859375</v>
       </c>
     </row>
     <row r="804">
@@ -6849,7 +6849,7 @@
         <v>170.0577824707335</v>
       </c>
       <c r="B804" t="n">
-        <v>291.4220275878906</v>
+        <v>399.5946960449219</v>
       </c>
     </row>
     <row r="805">
@@ -6857,7 +6857,7 @@
         <v>137.8443975352314</v>
       </c>
       <c r="B805" t="n">
-        <v>2282.3798828125</v>
+        <v>5167.60986328125</v>
       </c>
     </row>
     <row r="806">
@@ -6865,7 +6865,7 @@
         <v>112.8267897390655</v>
       </c>
       <c r="B806" t="n">
-        <v>19848.298828125</v>
+        <v>45921.08203125</v>
       </c>
     </row>
     <row r="807">
@@ -6873,7 +6873,7 @@
         <v>173.2781140378907</v>
       </c>
       <c r="B807" t="n">
-        <v>233.8048858642578</v>
+        <v>319.7610778808594</v>
       </c>
     </row>
     <row r="808">
@@ -6881,7 +6881,7 @@
         <v>80.80531691795773</v>
       </c>
       <c r="B808" t="n">
-        <v>1225163</v>
+        <v>1118551.5</v>
       </c>
     </row>
     <row r="809">
@@ -6889,7 +6889,7 @@
         <v>72.95835952233818</v>
       </c>
       <c r="B809" t="n">
-        <v>5403606</v>
+        <v>2465185</v>
       </c>
     </row>
     <row r="810">
@@ -6897,7 +6897,7 @@
         <v>87.09750054561511</v>
       </c>
       <c r="B810" t="n">
-        <v>387019.03125</v>
+        <v>593584.1875</v>
       </c>
     </row>
     <row r="811">
@@ -6905,7 +6905,7 @@
         <v>137.0032640309641</v>
       </c>
       <c r="B811" t="n">
-        <v>2376.531982421875</v>
+        <v>5538.7744140625</v>
       </c>
     </row>
     <row r="812">
@@ -6913,7 +6913,7 @@
         <v>165.017580051685</v>
       </c>
       <c r="B812" t="n">
-        <v>415.3606567382812</v>
+        <v>573.3338623046875</v>
       </c>
     </row>
     <row r="813">
@@ -6921,7 +6921,7 @@
         <v>90.6734601231573</v>
       </c>
       <c r="B813" t="n">
-        <v>231224.671875</v>
+        <v>414090.6875</v>
       </c>
     </row>
     <row r="814">
@@ -6929,7 +6929,7 @@
         <v>149.0743271727089</v>
       </c>
       <c r="B814" t="n">
-        <v>1334.537963867188</v>
+        <v>2047.272216796875</v>
       </c>
     </row>
     <row r="815">
@@ -6937,7 +6937,7 @@
         <v>177.9169284201337</v>
       </c>
       <c r="B815" t="n">
-        <v>170.2330322265625</v>
+        <v>238.7973937988281</v>
       </c>
     </row>
     <row r="816">
@@ -6945,7 +6945,7 @@
         <v>99.03248717923418</v>
       </c>
       <c r="B816" t="n">
-        <v>89658.09375</v>
+        <v>178456.765625</v>
       </c>
     </row>
     <row r="817">
@@ -6953,7 +6953,7 @@
         <v>156.2418053756036</v>
       </c>
       <c r="B817" t="n">
-        <v>798.8519287109375</v>
+        <v>1138.235717773438</v>
       </c>
     </row>
     <row r="818">
@@ -6961,7 +6961,7 @@
         <v>125.7167061867958</v>
       </c>
       <c r="B818" t="n">
-        <v>4951.81201171875</v>
+        <v>14175.5927734375</v>
       </c>
     </row>
     <row r="819">
@@ -6969,7 +6969,7 @@
         <v>134.0840178655652</v>
       </c>
       <c r="B819" t="n">
-        <v>2734.462646484375</v>
+        <v>7046.29296875</v>
       </c>
     </row>
     <row r="820">
@@ -6977,7 +6977,7 @@
         <v>168.9753562422068</v>
       </c>
       <c r="B820" t="n">
-        <v>313.7777099609375</v>
+        <v>431.8088989257812</v>
       </c>
     </row>
     <row r="821">
@@ -6985,7 +6985,7 @@
         <v>109.9923745805516</v>
       </c>
       <c r="B821" t="n">
-        <v>26984.22265625</v>
+        <v>60322.1171875</v>
       </c>
     </row>
     <row r="822">
@@ -6993,7 +6993,7 @@
         <v>76.34065961006816</v>
       </c>
       <c r="B822" t="n">
-        <v>2850276</v>
+        <v>1753503</v>
       </c>
     </row>
     <row r="823">
@@ -7001,7 +7001,7 @@
         <v>171.7378558084679</v>
       </c>
       <c r="B823" t="n">
-        <v>259.7833557128906</v>
+        <v>354.3440246582031</v>
       </c>
     </row>
     <row r="824">
@@ -7009,7 +7009,7 @@
         <v>130.8369837931637</v>
       </c>
       <c r="B824" t="n">
-        <v>3219.611328125</v>
+        <v>9209.7421875</v>
       </c>
     </row>
     <row r="825">
@@ -7017,7 +7017,7 @@
         <v>114.1683894816725</v>
       </c>
       <c r="B825" t="n">
-        <v>17162.76171875</v>
+        <v>40377.7890625</v>
       </c>
     </row>
     <row r="826">
@@ -7025,7 +7025,7 @@
         <v>163.4452837126025</v>
       </c>
       <c r="B826" t="n">
-        <v>466.9860229492188</v>
+        <v>641.6795654296875</v>
       </c>
     </row>
     <row r="827">
@@ -7033,7 +7033,7 @@
         <v>88.1402075323268</v>
       </c>
       <c r="B827" t="n">
-        <v>329875.1875</v>
+        <v>534417.25</v>
       </c>
     </row>
     <row r="828">
@@ -7041,7 +7041,7 @@
         <v>124.6978348912682</v>
       </c>
       <c r="B828" t="n">
-        <v>5520.0966796875</v>
+        <v>15509.150390625</v>
       </c>
     </row>
     <row r="829">
@@ -7049,7 +7049,7 @@
         <v>121.8191906664731</v>
       </c>
       <c r="B829" t="n">
-        <v>7515.435546875</v>
+        <v>19994.431640625</v>
       </c>
     </row>
     <row r="830">
@@ -7057,7 +7057,7 @@
         <v>158.557324076155</v>
       </c>
       <c r="B830" t="n">
-        <v>672.1636962890625</v>
+        <v>943.3203735351562</v>
       </c>
     </row>
     <row r="831">
@@ -7065,7 +7065,7 @@
         <v>117.7540933806156</v>
       </c>
       <c r="B831" t="n">
-        <v>11637.1572265625</v>
+        <v>28629.72265625</v>
       </c>
     </row>
     <row r="832">
@@ -7073,7 +7073,7 @@
         <v>142.2595239087992</v>
       </c>
       <c r="B832" t="n">
-        <v>1846.027709960938</v>
+        <v>3590.619140625</v>
       </c>
     </row>
     <row r="833">
@@ -7081,7 +7081,7 @@
         <v>167.7020929682094</v>
       </c>
       <c r="B833" t="n">
-        <v>342.2344360351562</v>
+        <v>473.0418701171875</v>
       </c>
     </row>
     <row r="834">
@@ -7089,7 +7089,7 @@
         <v>176.2379812662587</v>
       </c>
       <c r="B834" t="n">
-        <v>190.9507904052734</v>
+        <v>265.2162780761719</v>
       </c>
     </row>
     <row r="835">
@@ -7097,7 +7097,7 @@
         <v>119.2202773587279</v>
       </c>
       <c r="B835" t="n">
-        <v>9934.0556640625</v>
+        <v>25148.369140625</v>
       </c>
     </row>
     <row r="836">
@@ -7105,7 +7105,7 @@
         <v>109.0564359641785</v>
       </c>
       <c r="B836" t="n">
-        <v>29864.541015625</v>
+        <v>66074.8125</v>
       </c>
     </row>
     <row r="837">
@@ -7113,7 +7113,7 @@
         <v>146.2308427466783</v>
       </c>
       <c r="B837" t="n">
-        <v>1525.286865234375</v>
+        <v>2588.017578125</v>
       </c>
     </row>
     <row r="838">
@@ -7121,7 +7121,7 @@
         <v>103.8507301218433</v>
       </c>
       <c r="B838" t="n">
-        <v>52496.9140625</v>
+        <v>110034.2109375</v>
       </c>
     </row>
     <row r="839">
@@ -7129,7 +7129,7 @@
         <v>148.1451483007039</v>
       </c>
       <c r="B839" t="n">
-        <v>1394.09033203125</v>
+        <v>2210.238037109375</v>
       </c>
     </row>
     <row r="840">
@@ -7137,7 +7137,7 @@
         <v>117.146592290415</v>
       </c>
       <c r="B840" t="n">
-        <v>12428.9853515625</v>
+        <v>30347.09765625</v>
       </c>
     </row>
     <row r="841">
@@ -7145,7 +7145,7 @@
         <v>166.9176074490273</v>
       </c>
       <c r="B841" t="n">
-        <v>361.0382995605469</v>
+        <v>500.3834228515625</v>
       </c>
     </row>
     <row r="842">
@@ -7153,7 +7153,7 @@
         <v>129.1989304498977</v>
       </c>
       <c r="B842" t="n">
-        <v>3517.73193359375</v>
+        <v>10541.7216796875</v>
       </c>
     </row>
     <row r="843">
@@ -7161,7 +7161,7 @@
         <v>100.8317060325453</v>
       </c>
       <c r="B843" t="n">
-        <v>73118.78125</v>
+        <v>148884.5625</v>
       </c>
     </row>
     <row r="844">
@@ -7169,7 +7169,7 @@
         <v>113.2667962566628</v>
       </c>
       <c r="B844" t="n">
-        <v>18924.181640625</v>
+        <v>44024.01171875</v>
       </c>
     </row>
     <row r="845">
@@ -7177,7 +7177,7 @@
         <v>159.49776587629</v>
       </c>
       <c r="B845" t="n">
-        <v>626.6756591796875</v>
+        <v>874.0349731445312</v>
       </c>
     </row>
     <row r="846">
@@ -7185,7 +7185,7 @@
         <v>153.3319535863289</v>
       </c>
       <c r="B846" t="n">
-        <v>992.5115356445312</v>
+        <v>1441.320434570312</v>
       </c>
     </row>
     <row r="847">
@@ -7193,7 +7193,7 @@
         <v>77.40553765358774</v>
       </c>
       <c r="B847" t="n">
-        <v>2330375.5</v>
+        <v>1575205.25</v>
       </c>
     </row>
     <row r="848">
@@ -7201,7 +7201,7 @@
         <v>177.2861304184822</v>
       </c>
       <c r="B848" t="n">
-        <v>177.7395172119141</v>
+        <v>248.3994750976562</v>
       </c>
     </row>
     <row r="849">
@@ -7209,7 +7209,7 @@
         <v>71.2803059216634</v>
       </c>
       <c r="B849" t="n">
-        <v>7421765.5</v>
+        <v>2919488.5</v>
       </c>
     </row>
     <row r="850">
@@ -7217,7 +7217,7 @@
         <v>174.7225581926346</v>
       </c>
       <c r="B850" t="n">
-        <v>211.8078460693359</v>
+        <v>291.5626831054688</v>
       </c>
     </row>
     <row r="851">
@@ -7225,7 +7225,7 @@
         <v>122.8290309559172</v>
       </c>
       <c r="B851" t="n">
-        <v>6743.2734375</v>
+        <v>18289.73828125</v>
       </c>
     </row>
     <row r="852">
@@ -7233,7 +7233,7 @@
         <v>127.2299024193591</v>
       </c>
       <c r="B852" t="n">
-        <v>4213.95654296875</v>
+        <v>12403.669921875</v>
       </c>
     </row>
     <row r="853">
@@ -7241,7 +7241,7 @@
         <v>157.6044276224745</v>
       </c>
       <c r="B853" t="n">
-        <v>721.6417846679688</v>
+        <v>1019.127563476562</v>
       </c>
     </row>
     <row r="854">
@@ -7249,7 +7249,7 @@
         <v>96.41474740738545</v>
       </c>
       <c r="B854" t="n">
-        <v>120625.46875</v>
+        <v>232281.421875</v>
       </c>
     </row>
     <row r="855">
@@ -7257,7 +7257,7 @@
         <v>141.2317695566625</v>
       </c>
       <c r="B855" t="n">
-        <v>1939.497436523438</v>
+        <v>3908.203125</v>
       </c>
     </row>
     <row r="856">
@@ -7265,7 +7265,7 @@
         <v>165.7611027663291</v>
       </c>
       <c r="B856" t="n">
-        <v>392.9756164550781</v>
+        <v>543.5989379882812</v>
       </c>
     </row>
     <row r="857">
@@ -7273,7 +7273,7 @@
         <v>83.01746851224655</v>
       </c>
       <c r="B857" t="n">
-        <v>806666.3125</v>
+        <v>895186.125</v>
       </c>
     </row>
     <row r="858">
@@ -7281,7 +7281,7 @@
         <v>134.7597028607218</v>
       </c>
       <c r="B858" t="n">
-        <v>2647.097900390625</v>
+        <v>6664.4169921875</v>
       </c>
     </row>
     <row r="859">
@@ -7289,7 +7289,7 @@
         <v>179.3176900430167</v>
       </c>
       <c r="B859" t="n">
-        <v>155.5820159912109</v>
+        <v>218.7811584472656</v>
       </c>
     </row>
     <row r="860">
@@ -7297,7 +7297,7 @@
         <v>89.31848323246123</v>
       </c>
       <c r="B860" t="n">
-        <v>276133.5625</v>
+        <v>474627.59375</v>
       </c>
     </row>
     <row r="861">
@@ -7305,7 +7305,7 @@
         <v>94.9317898066611</v>
       </c>
       <c r="B861" t="n">
-        <v>142702.578125</v>
+        <v>269691.46875</v>
       </c>
     </row>
     <row r="862">
@@ -7313,7 +7313,7 @@
         <v>111.0683535961909</v>
       </c>
       <c r="B862" t="n">
-        <v>24014.58203125</v>
+        <v>54363.7734375</v>
       </c>
     </row>
     <row r="863">
@@ -7321,7 +7321,7 @@
         <v>139.2141635175411</v>
       </c>
       <c r="B863" t="n">
-        <v>2136.971435546875</v>
+        <v>4615.65625</v>
       </c>
     </row>
     <row r="864">
@@ -7329,7 +7329,7 @@
         <v>107.8325428861411</v>
       </c>
       <c r="B864" t="n">
-        <v>34099.7421875</v>
+        <v>74433.34375</v>
       </c>
     </row>
     <row r="865">
@@ -7337,7 +7337,7 @@
         <v>140.0028859772853</v>
       </c>
       <c r="B865" t="n">
-        <v>2057.488037109375</v>
+        <v>4325.01171875</v>
       </c>
     </row>
     <row r="866">
@@ -7345,7 +7345,7 @@
         <v>85.41459810023522</v>
       </c>
       <c r="B866" t="n">
-        <v>513380.3125</v>
+        <v>703200.6875</v>
       </c>
     </row>
     <row r="867">
@@ -7353,7 +7353,7 @@
         <v>172.632526420047</v>
       </c>
       <c r="B867" t="n">
-        <v>244.3613128662109</v>
+        <v>333.8068237304688</v>
       </c>
     </row>
     <row r="868">
@@ -7361,7 +7361,7 @@
         <v>92.2010449186085</v>
       </c>
       <c r="B868" t="n">
-        <v>194465.765625</v>
+        <v>355050.46875</v>
       </c>
     </row>
     <row r="869">
@@ -7369,7 +7369,7 @@
         <v>104.7733538948924</v>
       </c>
       <c r="B869" t="n">
-        <v>47502.328125</v>
+        <v>100490.2265625</v>
       </c>
     </row>
     <row r="870">
@@ -7377,7 +7377,7 @@
         <v>162.0462937672116</v>
       </c>
       <c r="B870" t="n">
-        <v>518.291259765625</v>
+        <v>714.58984375</v>
       </c>
     </row>
     <row r="871">
@@ -7385,7 +7385,7 @@
         <v>106.8590838267188</v>
       </c>
       <c r="B871" t="n">
-        <v>37893.203125</v>
+        <v>81854.9453125</v>
       </c>
     </row>
     <row r="872">
@@ -7393,7 +7393,7 @@
         <v>79.18179475835503</v>
       </c>
       <c r="B872" t="n">
-        <v>1665473</v>
+        <v>1317213.25</v>
       </c>
     </row>
     <row r="873">
@@ -7401,7 +7401,7 @@
         <v>120.2947703233841</v>
       </c>
       <c r="B873" t="n">
-        <v>8851.740234375</v>
+        <v>22873.421875</v>
       </c>
     </row>
     <row r="874">
@@ -7409,7 +7409,7 @@
         <v>89.63839000066844</v>
       </c>
       <c r="B874" t="n">
-        <v>263118.40625</v>
+        <v>459581.03125</v>
       </c>
     </row>
     <row r="875">
@@ -7417,7 +7417,7 @@
         <v>98.14945731089296</v>
       </c>
       <c r="B875" t="n">
-        <v>99095.3359375</v>
+        <v>195052.53125</v>
       </c>
     </row>
     <row r="876">
@@ -7425,7 +7425,7 @@
         <v>82.70741406970781</v>
       </c>
       <c r="B876" t="n">
-        <v>855221</v>
+        <v>923575.125</v>
       </c>
     </row>
     <row r="877">
@@ -7433,7 +7433,7 @@
         <v>102.5645275216388</v>
       </c>
       <c r="B877" t="n">
-        <v>60347.88671875</v>
+        <v>125045.4296875</v>
       </c>
     </row>
     <row r="878">
@@ -7441,7 +7441,7 @@
         <v>152.8166358989182</v>
       </c>
       <c r="B878" t="n">
-        <v>1031.407104492188</v>
+        <v>1503.863525390625</v>
       </c>
     </row>
     <row r="879">
@@ -7449,7 +7449,7 @@
         <v>154.6392464652359</v>
       </c>
       <c r="B879" t="n">
-        <v>900.2919921875</v>
+        <v>1296.247924804688</v>
       </c>
     </row>
     <row r="880">
@@ -7457,7 +7457,7 @@
         <v>143.5862380391011</v>
       </c>
       <c r="B880" t="n">
-        <v>1731.997802734375</v>
+        <v>3218.511962890625</v>
       </c>
     </row>
     <row r="881">
@@ -7465,7 +7465,7 @@
         <v>79.66287868771786</v>
       </c>
       <c r="B881" t="n">
-        <v>1520638.25</v>
+        <v>1254923</v>
       </c>
     </row>
     <row r="882">
@@ -7473,7 +7473,7 @@
         <v>93.20065594784954</v>
       </c>
       <c r="B882" t="n">
-        <v>173636.75</v>
+        <v>321050.375</v>
       </c>
     </row>
     <row r="883">
@@ -7481,7 +7481,7 @@
         <v>135.9353951297495</v>
       </c>
       <c r="B883" t="n">
-        <v>2501.67578125</v>
+        <v>6048.6328125</v>
       </c>
     </row>
     <row r="884">
@@ -7489,7 +7489,7 @@
         <v>95.26746411758965</v>
       </c>
       <c r="B884" t="n">
-        <v>137375.6875</v>
+        <v>260728.34375</v>
       </c>
     </row>
     <row r="885">
@@ -7497,7 +7497,7 @@
         <v>116.0965256767126</v>
       </c>
       <c r="B885" t="n">
-        <v>13926.783203125</v>
+        <v>33561.859375</v>
       </c>
     </row>
     <row r="886">
@@ -7505,7 +7505,7 @@
         <v>160.938331437289</v>
       </c>
       <c r="B886" t="n">
-        <v>562.8935546875</v>
+        <v>778.3347778320312</v>
       </c>
     </row>
     <row r="887">
@@ -7513,7 +7513,7 @@
         <v>74.85283804471912</v>
       </c>
       <c r="B887" t="n">
-        <v>3776465.25</v>
+        <v>2036914.625</v>
       </c>
     </row>
     <row r="888">
@@ -7521,7 +7521,7 @@
         <v>123.2952660142186</v>
       </c>
       <c r="B888" t="n">
-        <v>6414.0556640625</v>
+        <v>17552.55859375</v>
       </c>
     </row>
     <row r="889">
@@ -7529,7 +7529,7 @@
         <v>144.8095442666472</v>
       </c>
       <c r="B889" t="n">
-        <v>1633.114013671875</v>
+        <v>2909.694580078125</v>
       </c>
     </row>
     <row r="890">
@@ -7537,7 +7537,7 @@
         <v>180.8898567457079</v>
       </c>
       <c r="B890" t="n">
-        <v>144.1445465087891</v>
+        <v>198.3067626953125</v>
       </c>
     </row>
     <row r="891">
@@ -7545,7 +7545,7 @@
         <v>162.6380590688663</v>
       </c>
       <c r="B891" t="n">
-        <v>495.9347839355469</v>
+        <v>682.711669921875</v>
       </c>
     </row>
     <row r="892">
@@ -7553,7 +7553,7 @@
         <v>150.7404166528885</v>
       </c>
       <c r="B892" t="n">
-        <v>1204.182495117188</v>
+        <v>1784.569702148438</v>
       </c>
     </row>
     <row r="893">
@@ -7561,7 +7561,7 @@
         <v>75.29263818211994</v>
       </c>
       <c r="B893" t="n">
-        <v>3475074.5</v>
+        <v>1948671.625</v>
       </c>
     </row>
     <row r="894">
@@ -7569,7 +7569,7 @@
         <v>84.50820843398964</v>
       </c>
       <c r="B894" t="n">
-        <v>609041</v>
+        <v>770404.375</v>
       </c>
     </row>
     <row r="895">
@@ -7577,7 +7577,7 @@
         <v>128.1446127654979</v>
       </c>
       <c r="B895" t="n">
-        <v>3822.34814453125</v>
+        <v>11499.259765625</v>
       </c>
     </row>
     <row r="896">
@@ -7585,7 +7585,7 @@
         <v>105.8930937913211</v>
       </c>
       <c r="B896" t="n">
-        <v>42074.65625</v>
+        <v>90012.1953125</v>
       </c>
     </row>
     <row r="897">
@@ -7593,7 +7593,7 @@
         <v>72.01535368079516</v>
       </c>
       <c r="B897" t="n">
-        <v>6458548</v>
+        <v>2711004.75</v>
       </c>
     </row>
     <row r="898">
@@ -7601,7 +7601,7 @@
         <v>100.2406541079225</v>
       </c>
       <c r="B898" t="n">
-        <v>78184.7734375</v>
+        <v>158014.546875</v>
       </c>
     </row>
     <row r="899">
@@ -7609,7 +7609,7 @@
         <v>147.4615955851352</v>
       </c>
       <c r="B899" t="n">
-        <v>1439.587036132812</v>
+        <v>2338.34912109375</v>
       </c>
     </row>
     <row r="900">
@@ -7617,7 +7617,7 @@
         <v>132.9064716484334</v>
       </c>
       <c r="B900" t="n">
-        <v>2893.667724609375</v>
+        <v>7764.82568359375</v>
       </c>
     </row>
     <row r="901">
@@ -7625,7 +7625,7 @@
         <v>69.41090094119697</v>
       </c>
       <c r="B901" t="n">
-        <v>10546526</v>
+        <v>3503131.75</v>
       </c>
     </row>
     <row r="902">
@@ -7633,7 +7633,7 @@
         <v>189.3491798868479</v>
       </c>
       <c r="B902" t="n">
-        <v>27206.95703125</v>
+        <v>26561.056640625</v>
       </c>
     </row>
     <row r="903">
@@ -7641,7 +7641,7 @@
         <v>221.536670283776</v>
       </c>
       <c r="B903" t="n">
-        <v>4606.55078125</v>
+        <v>4933.59912109375</v>
       </c>
     </row>
     <row r="904">
@@ -7649,7 +7649,7 @@
         <v>249.1381948707651</v>
       </c>
       <c r="B904" t="n">
-        <v>881.1788330078125</v>
+        <v>1165.236572265625</v>
       </c>
     </row>
     <row r="905">
@@ -7657,7 +7657,7 @@
         <v>201.1297174946643</v>
       </c>
       <c r="B905" t="n">
-        <v>14685.40234375</v>
+        <v>14344.025390625</v>
       </c>
     </row>
     <row r="906">
@@ -7665,7 +7665,7 @@
         <v>163.8453010854245</v>
       </c>
       <c r="B906" t="n">
-        <v>103241.890625</v>
+        <v>100813.6953125</v>
       </c>
     </row>
     <row r="907">
@@ -7673,7 +7673,7 @@
         <v>253.9375419587833</v>
       </c>
       <c r="B907" t="n">
-        <v>658.9362182617188</v>
+        <v>906.7406005859375</v>
       </c>
     </row>
     <row r="908">
@@ -7681,7 +7681,7 @@
         <v>116.1228355153026</v>
       </c>
       <c r="B908" t="n">
-        <v>2665106</v>
+        <v>2421780.5</v>
       </c>
     </row>
     <row r="909">
@@ -7689,7 +7689,7 @@
         <v>104.4283030297194</v>
       </c>
       <c r="B909" t="n">
-        <v>8494367</v>
+        <v>9178121</v>
       </c>
     </row>
     <row r="910">
@@ -7697,7 +7697,7 @@
         <v>125.5002466734124</v>
       </c>
       <c r="B910" t="n">
-        <v>1083246</v>
+        <v>974929.3125</v>
       </c>
     </row>
     <row r="911">
@@ -7705,7 +7705,7 @@
         <v>199.8761535214665</v>
       </c>
       <c r="B911" t="n">
-        <v>15681.28515625</v>
+        <v>15315.9169921875</v>
       </c>
     </row>
     <row r="912">
@@ -7713,7 +7713,7 @@
         <v>241.6266451130995</v>
       </c>
       <c r="B912" t="n">
-        <v>1389.3671875</v>
+        <v>1725.461791992188</v>
       </c>
     </row>
     <row r="913">
@@ -7721,7 +7721,7 @@
         <v>130.829595787764</v>
       </c>
       <c r="B913" t="n">
-        <v>763412.1875</v>
+        <v>700538.1875</v>
       </c>
     </row>
     <row r="914">
@@ -7729,7 +7729,7 @@
         <v>217.8659848572993</v>
       </c>
       <c r="B914" t="n">
-        <v>5728.96533203125</v>
+        <v>5977.73583984375</v>
       </c>
     </row>
     <row r="915">
@@ -7737,7 +7737,7 @@
         <v>260.8508922871558</v>
       </c>
       <c r="B915" t="n">
-        <v>434.213134765625</v>
+        <v>631.9497680664062</v>
       </c>
     </row>
     <row r="916">
@@ -7745,7 +7745,7 @@
         <v>143.2872795149282</v>
       </c>
       <c r="B916" t="n">
-        <v>336917.84375</v>
+        <v>323847.59375</v>
       </c>
     </row>
     <row r="917">
@@ -7753,7 +7753,7 @@
         <v>228.5478711550705</v>
       </c>
       <c r="B917" t="n">
-        <v>3037.3466796875</v>
+        <v>3419.142333984375</v>
       </c>
     </row>
     <row r="918">
@@ -7761,7 +7761,7 @@
         <v>183.055491613359</v>
       </c>
       <c r="B918" t="n">
-        <v>37822.2890625</v>
+        <v>36914.24609375</v>
       </c>
     </row>
     <row r="919">
@@ -7769,7 +7769,7 @@
         <v>195.5255221374182</v>
       </c>
       <c r="B919" t="n">
-        <v>19691.578125</v>
+        <v>19229.119140625</v>
       </c>
     </row>
     <row r="920">
@@ -7777,7 +7777,7 @@
         <v>247.5250258353605</v>
       </c>
       <c r="B920" t="n">
-        <v>972.3028564453125</v>
+        <v>1267.73583984375</v>
       </c>
     </row>
     <row r="921">
@@ -7785,7 +7785,7 @@
         <v>159.6210956414935</v>
       </c>
       <c r="B921" t="n">
-        <v>128737.609375</v>
+        <v>125774.109375</v>
       </c>
     </row>
     <row r="922">
@@ -7793,7 +7793,7 @@
         <v>109.4690361773251</v>
       </c>
       <c r="B922" t="n">
-        <v>5153977</v>
+        <v>5168319.5</v>
       </c>
     </row>
     <row r="923">
@@ -7801,7 +7801,7 @@
         <v>251.6420535303349</v>
       </c>
       <c r="B923" t="n">
-        <v>757.0360107421875</v>
+        <v>1022.313171386719</v>
       </c>
     </row>
     <row r="924">
@@ -7809,7 +7809,7 @@
         <v>190.6863795848293</v>
       </c>
       <c r="B924" t="n">
-        <v>25367.7578125</v>
+        <v>24766.98828125</v>
       </c>
     </row>
     <row r="925">
@@ -7817,7 +7817,7 @@
         <v>165.8447234069125</v>
       </c>
       <c r="B925" t="n">
-        <v>93001.2265625</v>
+        <v>90804.21875</v>
       </c>
     </row>
     <row r="926">
@@ -7825,7 +7825,7 @@
         <v>239.2834094247514</v>
       </c>
       <c r="B926" t="n">
-        <v>1600.863403320312</v>
+        <v>1950.246948242188</v>
       </c>
     </row>
     <row r="927">
@@ -7833,7 +7833,7 @@
         <v>127.0542210502647</v>
       </c>
       <c r="B927" t="n">
-        <v>978172.75</v>
+        <v>885355.75</v>
       </c>
     </row>
     <row r="928">
@@ -7841,7 +7841,7 @@
         <v>181.5370402106755</v>
       </c>
       <c r="B928" t="n">
-        <v>40951.1015625</v>
+        <v>39965.3515625</v>
       </c>
     </row>
     <row r="929">
@@ -7849,7 +7849,7 @@
         <v>177.2469189950187</v>
       </c>
       <c r="B929" t="n">
-        <v>51258.7265625</v>
+        <v>50017.9375</v>
       </c>
     </row>
     <row r="930">
@@ -7857,7 +7857,7 @@
         <v>231.9987511967653</v>
       </c>
       <c r="B930" t="n">
-        <v>2474.377685546875</v>
+        <v>2854.543212890625</v>
       </c>
     </row>
     <row r="931">
@@ -7865,7 +7865,7 @@
         <v>171.1885947465582</v>
       </c>
       <c r="B931" t="n">
-        <v>70345.2421875</v>
+        <v>68663.9921875</v>
       </c>
     </row>
     <row r="932">
@@ -7873,7 +7873,7 @@
         <v>207.7096995438171</v>
       </c>
       <c r="B932" t="n">
-        <v>10392.939453125</v>
+        <v>10167.59765625</v>
       </c>
     </row>
     <row r="933">
@@ -7881,7 +7881,7 @@
         <v>245.6274471982221</v>
       </c>
       <c r="B933" t="n">
-        <v>1090.811645507812</v>
+        <v>1399.902099609375</v>
       </c>
     </row>
     <row r="934">
@@ -7889,7 +7889,7 @@
         <v>258.3487120098002</v>
       </c>
       <c r="B934" t="n">
-        <v>504.8159790039062</v>
+        <v>720.050537109375</v>
       </c>
     </row>
     <row r="935">
@@ -7897,7 +7897,7 @@
         <v>173.3736883181696</v>
       </c>
       <c r="B935" t="n">
-        <v>62755.703125</v>
+        <v>61248.91796875</v>
       </c>
     </row>
     <row r="936">
@@ -7905,7 +7905,7 @@
         <v>158.2262410498529</v>
       </c>
       <c r="B936" t="n">
-        <v>138469.796875</v>
+        <v>135341.828125</v>
       </c>
     </row>
     <row r="937">
@@ -7913,7 +7913,7 @@
         <v>213.6282632391053</v>
       </c>
       <c r="B937" t="n">
-        <v>7368.92236328125</v>
+        <v>7460.85595703125</v>
       </c>
     </row>
     <row r="938">
@@ -7921,7 +7921,7 @@
         <v>150.4680370716379</v>
       </c>
       <c r="B938" t="n">
-        <v>211304.5</v>
+        <v>208464.3125</v>
       </c>
     </row>
     <row r="939">
@@ -7929,7 +7929,7 @@
         <v>216.4812044952132</v>
       </c>
       <c r="B939" t="n">
-        <v>6220.1630859375</v>
+        <v>6426.7197265625</v>
       </c>
     </row>
     <row r="940">
@@ -7937,7 +7937,7 @@
         <v>170.283219468448</v>
       </c>
       <c r="B940" t="n">
-        <v>73752.4375</v>
+        <v>71993.5546875</v>
       </c>
     </row>
     <row r="941">
@@ -7945,7 +7945,7 @@
         <v>244.4583072467721</v>
       </c>
       <c r="B941" t="n">
-        <v>1170.719482421875</v>
+        <v>1488.106079101562</v>
       </c>
     </row>
     <row r="942">
@@ -7953,7 +7953,7 @@
         <v>188.2451444576149</v>
       </c>
       <c r="B942" t="n">
-        <v>28825.470703125</v>
+        <v>28139.787109375</v>
       </c>
     </row>
     <row r="943">
@@ -7961,7 +7961,7 @@
         <v>145.9687039534586</v>
       </c>
       <c r="B943" t="n">
-        <v>282527.21875</v>
+        <v>274727.34375</v>
       </c>
     </row>
     <row r="944">
@@ -7969,7 +7969,7 @@
         <v>164.5010546793948</v>
       </c>
       <c r="B944" t="n">
-        <v>99764.65625</v>
+        <v>97414.8203125</v>
       </c>
     </row>
     <row r="945">
@@ -7977,7 +7977,7 @@
         <v>233.4003170047585</v>
       </c>
       <c r="B945" t="n">
-        <v>2276.70849609375</v>
+        <v>2652.78466796875</v>
       </c>
     </row>
     <row r="946">
@@ -7985,7 +7985,7 @@
         <v>224.2112404634214</v>
       </c>
       <c r="B946" t="n">
-        <v>3929.84228515625</v>
+        <v>4289.58740234375</v>
       </c>
     </row>
     <row r="947">
@@ -7993,7 +7993,7 @@
         <v>111.0560526787879</v>
       </c>
       <c r="B947" t="n">
-        <v>4403779</v>
+        <v>4313478.5</v>
       </c>
     </row>
     <row r="948">
@@ -8001,7 +8001,7 @@
         <v>259.9107969928609</v>
       </c>
       <c r="B948" t="n">
-        <v>459.5003051757812</v>
+        <v>663.6021118164062</v>
       </c>
     </row>
     <row r="949">
@@ -8009,7 +8009,7 @@
         <v>101.9274544388253</v>
       </c>
       <c r="B949" t="n">
-        <v>10883903</v>
+        <v>12203635</v>
       </c>
     </row>
     <row r="950">
@@ -8017,7 +8017,7 @@
         <v>256.0902360846228</v>
       </c>
       <c r="B950" t="n">
-        <v>578.5216064453125</v>
+        <v>810.25732421875</v>
       </c>
     </row>
     <row r="951">
@@ -8025,7 +8025,7 @@
         <v>178.7519112454859</v>
       </c>
       <c r="B951" t="n">
-        <v>47377.890625</v>
+        <v>46231.95703125</v>
       </c>
     </row>
     <row r="952">
@@ -8033,7 +8033,7 @@
         <v>185.3106488171757</v>
       </c>
       <c r="B952" t="n">
-        <v>33611.08984375</v>
+        <v>32807.4609375</v>
       </c>
     </row>
     <row r="953">
@@ -8041,7 +8041,7 @@
         <v>230.5786238823001</v>
       </c>
       <c r="B953" t="n">
-        <v>2692.175048828125</v>
+        <v>3074.622314453125</v>
       </c>
     </row>
     <row r="954">
@@ -8049,7 +8049,7 @@
         <v>139.3859912502846</v>
       </c>
       <c r="B954" t="n">
-        <v>435280.90625</v>
+        <v>412071.96875</v>
       </c>
     </row>
     <row r="955">
@@ -8057,7 +8057,7 @@
         <v>206.1780094820141</v>
       </c>
       <c r="B955" t="n">
-        <v>11275.3173828125</v>
+        <v>11015.58203125</v>
       </c>
     </row>
     <row r="956">
@@ -8065,7 +8065,7 @@
         <v>242.7347370908932</v>
       </c>
       <c r="B956" t="n">
-        <v>1299.322875976562</v>
+        <v>1628.372802734375</v>
       </c>
     </row>
     <row r="957">
@@ -8073,7 +8073,7 @@
         <v>119.4196647674771</v>
       </c>
       <c r="B957" t="n">
-        <v>1922190</v>
+        <v>1663470</v>
       </c>
     </row>
     <row r="958">
@@ -8081,7 +8081,7 @@
         <v>196.5325137301458</v>
       </c>
       <c r="B958" t="n">
-        <v>18680.521484375</v>
+        <v>18242.708984375</v>
       </c>
     </row>
     <row r="959">
@@ -8089,7 +8089,7 @@
         <v>262.9384851562733</v>
       </c>
       <c r="B959" t="n">
-        <v>382.9266357421875</v>
+        <v>567.26513671875</v>
       </c>
     </row>
     <row r="960">
@@ -8097,7 +8097,7 @@
         <v>128.8102371412769</v>
       </c>
       <c r="B960" t="n">
-        <v>871650.5625</v>
+        <v>794003.1875</v>
       </c>
     </row>
     <row r="961">
@@ -8105,7 +8105,7 @@
         <v>137.1758994959832</v>
       </c>
       <c r="B961" t="n">
-        <v>503258.6875</v>
+        <v>472607.34375</v>
       </c>
     </row>
     <row r="962">
@@ -8113,7 +8113,7 @@
         <v>161.2246562214482</v>
       </c>
       <c r="B962" t="n">
-        <v>118391.3359375</v>
+        <v>115622.578125</v>
       </c>
     </row>
     <row r="963">
@@ -8121,7 +8121,7 @@
         <v>203.1711167237094</v>
       </c>
       <c r="B963" t="n">
-        <v>13197.17578125</v>
+        <v>12891.5126953125</v>
       </c>
     </row>
     <row r="964">
@@ -8129,7 +8129,7 @@
         <v>156.4022401488186</v>
       </c>
       <c r="B964" t="n">
-        <v>152314.8125</v>
+        <v>148959.609375</v>
       </c>
     </row>
     <row r="965">
@@ -8137,7 +8137,7 @@
         <v>204.3465711020824</v>
       </c>
       <c r="B965" t="n">
-        <v>12409.677734375</v>
+        <v>12122.865234375</v>
       </c>
     </row>
     <row r="966">
@@ -8145,7 +8145,7 @@
         <v>122.9921717183286</v>
       </c>
       <c r="B966" t="n">
-        <v>1348991.375</v>
+        <v>1144703.25</v>
       </c>
     </row>
     <row r="967">
@@ -8153,7 +8153,7 @@
         <v>252.9754053001366</v>
       </c>
       <c r="B967" t="n">
-        <v>698.4031372070312</v>
+        <v>953.501708984375</v>
       </c>
     </row>
     <row r="968">
@@ -8161,7 +8161,7 @@
         <v>133.1061966553639</v>
       </c>
       <c r="B968" t="n">
-        <v>657416.4375</v>
+        <v>608294.5</v>
       </c>
     </row>
     <row r="969">
@@ -8169,7 +8169,7 @@
         <v>151.8430481927532</v>
       </c>
       <c r="B969" t="n">
-        <v>193382.21875</v>
+        <v>191600.984375</v>
       </c>
     </row>
     <row r="970">
@@ -8177,7 +8177,7 @@
         <v>237.1984569344381</v>
       </c>
       <c r="B970" t="n">
-        <v>1815.967529296875</v>
+        <v>2174.87744140625</v>
       </c>
     </row>
     <row r="971">
@@ -8185,7 +8185,7 @@
         <v>154.9514678277971</v>
       </c>
       <c r="B971" t="n">
-        <v>164308.703125</v>
+        <v>160762.71875</v>
       </c>
     </row>
     <row r="972">
@@ -8193,7 +8193,7 @@
         <v>113.7032566034639</v>
       </c>
       <c r="B972" t="n">
-        <v>3387438.75</v>
+        <v>3190435.5</v>
       </c>
     </row>
     <row r="973">
@@ -8201,7 +8201,7 @@
         <v>174.9750341962187</v>
       </c>
       <c r="B973" t="n">
-        <v>57718.859375</v>
+        <v>56328.3671875</v>
       </c>
     </row>
     <row r="974">
@@ -8209,7 +8209,7 @@
         <v>129.287002835869</v>
       </c>
       <c r="B974" t="n">
-        <v>844787.1875</v>
+        <v>770868.0625</v>
       </c>
     </row>
     <row r="975">
@@ -8217,7 +8217,7 @@
         <v>141.9712762590902</v>
       </c>
       <c r="B975" t="n">
-        <v>367324.28125</v>
+        <v>351076.34375</v>
       </c>
     </row>
     <row r="976">
@@ -8225,7 +8225,7 @@
         <v>118.9575822598554</v>
       </c>
       <c r="B976" t="n">
-        <v>2012273.875</v>
+        <v>1753389.375</v>
       </c>
     </row>
     <row r="977">
@@ -8233,7 +8233,7 @@
         <v>148.5511746072731</v>
       </c>
       <c r="B977" t="n">
-        <v>239093.984375</v>
+        <v>234476.875</v>
       </c>
     </row>
     <row r="978">
@@ -8241,7 +8241,7 @@
         <v>223.4432485995707</v>
       </c>
       <c r="B978" t="n">
-        <v>4113.28369140625</v>
+        <v>4465.3779296875</v>
       </c>
     </row>
     <row r="979">
@@ -8249,7 +8249,7 @@
         <v>226.1595343396039</v>
       </c>
       <c r="B979" t="n">
-        <v>3500.34814453125</v>
+        <v>3874.037841796875</v>
       </c>
     </row>
     <row r="980">
@@ -8257,7 +8257,7 @@
         <v>209.6869374353544</v>
       </c>
       <c r="B980" t="n">
-        <v>9286.287109375</v>
+        <v>9168.73828125</v>
       </c>
     </row>
     <row r="981">
@@ -8265,7 +8265,7 @@
         <v>114.4202289733364</v>
       </c>
       <c r="B981" t="n">
-        <v>3155057</v>
+        <v>2940188.75</v>
       </c>
     </row>
     <row r="982">
@@ -8273,7 +8273,7 @@
         <v>134.5959439631462</v>
       </c>
       <c r="B982" t="n">
-        <v>596156.25</v>
+        <v>554611.625</v>
       </c>
     </row>
     <row r="983">
@@ -8281,7 +8281,7 @@
         <v>198.2846796640235</v>
       </c>
       <c r="B983" t="n">
-        <v>17043.537109375</v>
+        <v>16645.259765625</v>
       </c>
     </row>
     <row r="984">
@@ -8289,7 +8289,7 @@
         <v>137.6761639852388</v>
       </c>
       <c r="B984" t="n">
-        <v>486996.40625</v>
+        <v>458168.8125</v>
       </c>
     </row>
     <row r="985">
@@ -8297,7 +8297,7 @@
         <v>168.7182768407712</v>
       </c>
       <c r="B985" t="n">
-        <v>80036.109375</v>
+        <v>78133.8046875</v>
       </c>
     </row>
     <row r="986">
@@ -8305,7 +8305,7 @@
         <v>235.5472307576126</v>
       </c>
       <c r="B986" t="n">
-        <v>2004.09375</v>
+        <v>2371.0390625</v>
       </c>
     </row>
     <row r="987">
@@ -8313,7 +8313,7 @@
         <v>107.2516955252096</v>
       </c>
       <c r="B987" t="n">
-        <v>6420827</v>
+        <v>6653636.5</v>
       </c>
     </row>
     <row r="988">
@@ -8321,7 +8321,7 @@
         <v>179.4467539418751</v>
       </c>
       <c r="B988" t="n">
-        <v>45685.7734375</v>
+        <v>44582.03515625</v>
       </c>
     </row>
     <row r="989">
@@ -8329,7 +8329,7 @@
         <v>211.5100637372559</v>
       </c>
       <c r="B989" t="n">
-        <v>8353.9560546875</v>
+        <v>8334.8857421875</v>
       </c>
     </row>
     <row r="990">
@@ -8337,7 +8337,7 @@
         <v>265.2815276440072</v>
       </c>
       <c r="B990" t="n">
-        <v>332.5422058105469</v>
+        <v>502.5179748535156</v>
       </c>
     </row>
     <row r="991">
@@ -8345,7 +8345,7 @@
         <v>238.0803807419899</v>
       </c>
       <c r="B991" t="n">
-        <v>1721.660888671875</v>
+        <v>2076.839111328125</v>
       </c>
     </row>
     <row r="992">
@@ -8353,7 +8353,7 @@
         <v>220.3490029963713</v>
       </c>
       <c r="B992" t="n">
-        <v>4943.30517578125</v>
+        <v>5249.7666015625</v>
       </c>
     </row>
     <row r="993">
@@ -8361,7 +8361,7 @@
         <v>107.9071415452006</v>
       </c>
       <c r="B993" t="n">
-        <v>6016951.5</v>
+        <v>6174878.5</v>
       </c>
     </row>
     <row r="994">
@@ -8369,7 +8369,7 @@
         <v>121.6413547249264</v>
       </c>
       <c r="B994" t="n">
-        <v>1542265</v>
+        <v>1291487.375</v>
       </c>
     </row>
     <row r="995">
@@ -8377,7 +8377,7 @@
         <v>186.6738663444927</v>
       </c>
       <c r="B995" t="n">
-        <v>31296.330078125</v>
+        <v>30549.82421875</v>
       </c>
     </row>
     <row r="996">
@@ -8385,7 +8385,7 @@
         <v>153.5118267949537</v>
       </c>
       <c r="B996" t="n">
-        <v>177144.328125</v>
+        <v>173399.75</v>
       </c>
     </row>
     <row r="997">
@@ -8393,7 +8393,7 @@
         <v>103.0229159615831</v>
       </c>
       <c r="B997" t="n">
-        <v>9764034</v>
+        <v>10771795</v>
       </c>
     </row>
     <row r="998">
@@ -8401,7 +8401,7 @@
         <v>145.0878433109596</v>
       </c>
       <c r="B998" t="n">
-        <v>299349.90625</v>
+        <v>289980.28125</v>
       </c>
     </row>
     <row r="999">
@@ -8409,7 +8409,7 @@
         <v>215.4624874263161</v>
       </c>
       <c r="B999" t="n">
-        <v>6608.20654296875</v>
+        <v>6778.4033203125</v>
       </c>
     </row>
     <row r="1000">
@@ -8417,7 +8417,7 @@
         <v>193.770593214622</v>
       </c>
       <c r="B1000" t="n">
-        <v>21586.00390625</v>
+        <v>21077.572265625</v>
       </c>
     </row>
     <row r="1001">
@@ -8425,7 +8425,7 @@
         <v>99.14142971987114</v>
       </c>
       <c r="B1001" t="n">
-        <v>14345506</v>
+        <v>16762416</v>
       </c>
     </row>
   </sheetData>
